--- a/docs/fruitbasket_prices.xlsx
+++ b/docs/fruitbasket_prices.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="최신_소매" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="최신_도매" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="최근이력" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신_소매" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신_도매" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최근이력" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -511,7 +511,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>사과(홍로(10개))</t>
+          <t>사과(홍로)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -525,7 +525,9 @@
       <c r="E2" s="4" t="n">
         <v>-1.9</v>
       </c>
-      <c r="F2" s="4" t="n"/>
+      <c r="F2" s="4" t="n">
+        <v>4.3</v>
+      </c>
       <c r="G2" s="4" t="n">
         <v>0.4</v>
       </c>
@@ -549,7 +551,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>배(신고(10개))</t>
+          <t>배(신고)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -563,8 +565,12 @@
       <c r="E3" s="4" t="n">
         <v>0.6</v>
       </c>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
+      <c r="F3" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>-30</v>
+      </c>
       <c r="H3" s="4" t="n">
         <v>1.4</v>
       </c>
@@ -585,7 +591,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>바나나(수입(100g))</t>
+          <t>바나나(수입)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -599,7 +605,9 @@
       <c r="E4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="4" t="n"/>
+      <c r="F4" s="4" t="n">
+        <v>-1.8</v>
+      </c>
       <c r="G4" s="4" t="n">
         <v>-0.9</v>
       </c>
@@ -623,7 +631,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>파인애플(수입(1개))</t>
+          <t>파인애플(수입)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -637,7 +645,9 @@
       <c r="E5" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="F5" s="4" t="n"/>
+      <c r="F5" s="4" t="n">
+        <v>0.9</v>
+      </c>
       <c r="G5" s="4" t="n">
         <v>0.9</v>
       </c>
@@ -661,7 +671,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>레몬(수입(10개))</t>
+          <t>레몬(수입)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -675,7 +685,9 @@
       <c r="E6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="4" t="n"/>
+      <c r="F6" s="4" t="n">
+        <v>-5.7</v>
+      </c>
       <c r="G6" s="4" t="n">
         <v>-12.7</v>
       </c>
@@ -699,7 +711,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>망고(수입(1개))</t>
+          <t>망고(수입)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -713,7 +725,9 @@
       <c r="E7" s="4" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F7" s="4" t="n"/>
+      <c r="F7" s="4" t="n">
+        <v>-4.2</v>
+      </c>
       <c r="G7" s="4" t="n">
         <v>9.1</v>
       </c>
@@ -737,7 +751,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>블루베리(수입(냉동)(1kg))</t>
+          <t>블루베리(수입(냉동))</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -751,7 +765,9 @@
       <c r="E8" s="4" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F8" s="4" t="n"/>
+      <c r="F8" s="4" t="n">
+        <v>-0.9</v>
+      </c>
       <c r="G8" s="4" t="n">
         <v>0.3</v>
       </c>
@@ -767,7 +783,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>아보카도(수입(1개))</t>
+          <t>아보카도(수입)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -781,7 +797,9 @@
       <c r="E9" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="F9" s="4" t="n"/>
+      <c r="F9" s="4" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="G9" s="4" t="n">
         <v>8.5</v>
       </c>
@@ -805,7 +823,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>키위(골드(10개))</t>
+          <t>키위(골드)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -819,7 +837,9 @@
       <c r="E10" s="4" t="n">
         <v>-0.4</v>
       </c>
-      <c r="F10" s="4" t="n"/>
+      <c r="F10" s="4" t="n">
+        <v>11.2</v>
+      </c>
       <c r="G10" s="4" t="n">
         <v>2.1</v>
       </c>
@@ -835,7 +855,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>배추(여름(고랭지)(1포기))</t>
+          <t>배추(여름(고랭지))</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -849,7 +869,9 @@
       <c r="E11" s="4" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F11" s="4" t="n"/>
+      <c r="F11" s="4" t="n">
+        <v>2.7</v>
+      </c>
       <c r="G11" s="4" t="n">
         <v>3.9</v>
       </c>
@@ -873,7 +895,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>양배추(양배추(1포기))</t>
+          <t>양배추</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -887,7 +909,9 @@
       <c r="E12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="4" t="n"/>
+      <c r="F12" s="4" t="n">
+        <v>33.2</v>
+      </c>
       <c r="G12" s="4" t="n">
         <v>25.4</v>
       </c>
@@ -911,7 +935,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>시금치(시금치(100g))</t>
+          <t>시금치</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -925,7 +949,9 @@
       <c r="E13" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="F13" s="4" t="n"/>
+      <c r="F13" s="4" t="n">
+        <v>-32.3</v>
+      </c>
       <c r="G13" s="4" t="n">
         <v>-49.6</v>
       </c>
@@ -949,7 +975,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>상추(적(100g))</t>
+          <t>상추(적)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -963,7 +989,9 @@
       <c r="E14" s="4" t="n">
         <v>-2.4</v>
       </c>
-      <c r="F14" s="4" t="n"/>
+      <c r="F14" s="4" t="n">
+        <v>-35.5</v>
+      </c>
       <c r="G14" s="4" t="n">
         <v>-39.7</v>
       </c>
@@ -987,7 +1015,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>상추(청(100g))</t>
+          <t>상추(청)</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1001,7 +1029,9 @@
       <c r="E15" s="4" t="n">
         <v>-2.7</v>
       </c>
-      <c r="F15" s="4" t="n"/>
+      <c r="F15" s="4" t="n">
+        <v>-39.6</v>
+      </c>
       <c r="G15" s="4" t="n">
         <v>-42.4</v>
       </c>
@@ -1025,7 +1055,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>얼갈이배추(얼갈이배추(1kg))</t>
+          <t>얼갈이배추</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1039,7 +1069,9 @@
       <c r="E16" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="F16" s="4" t="n"/>
+      <c r="F16" s="4" t="n">
+        <v>-21.9</v>
+      </c>
       <c r="G16" s="4" t="n">
         <v>-33.2</v>
       </c>
@@ -1063,7 +1095,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>수박(수박(1개))</t>
+          <t>수박</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1077,7 +1109,9 @@
       <c r="E17" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="4" t="n"/>
+      <c r="F17" s="4" t="n">
+        <v>4.3</v>
+      </c>
       <c r="G17" s="4" t="n">
         <v>-0.1</v>
       </c>
@@ -1101,7 +1135,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>오이(가시계통(10개))</t>
+          <t>오이(가시계통)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1115,7 +1149,9 @@
       <c r="E18" s="4" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F18" s="4" t="n"/>
+      <c r="F18" s="4" t="n">
+        <v>-28.7</v>
+      </c>
       <c r="G18" s="4" t="n">
         <v>-24.6</v>
       </c>
@@ -1139,7 +1175,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>오이(다다기계통(10개))</t>
+          <t>오이(다다기계통)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1153,7 +1189,9 @@
       <c r="E19" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="F19" s="4" t="n"/>
+      <c r="F19" s="4" t="n">
+        <v>-28.3</v>
+      </c>
       <c r="G19" s="4" t="n">
         <v>-40</v>
       </c>
@@ -1177,7 +1215,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>오이(취청(10개))</t>
+          <t>오이(취청)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1191,7 +1229,9 @@
       <c r="E20" s="4" t="n">
         <v>-1.6</v>
       </c>
-      <c r="F20" s="4" t="n"/>
+      <c r="F20" s="4" t="n">
+        <v>-30.8</v>
+      </c>
       <c r="G20" s="4" t="n">
         <v>-32.4</v>
       </c>
@@ -1215,7 +1255,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>호박(애호박(1개))</t>
+          <t>호박(애호박)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1229,7 +1269,9 @@
       <c r="E21" s="4" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F21" s="4" t="n"/>
+      <c r="F21" s="4" t="n">
+        <v>-25.6</v>
+      </c>
       <c r="G21" s="4" t="n">
         <v>-47.8</v>
       </c>
@@ -1253,7 +1295,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>호박(쥬키니(1개))</t>
+          <t>호박(쥬키니)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1267,7 +1309,9 @@
       <c r="E22" s="4" t="n">
         <v>-0.4</v>
       </c>
-      <c r="F22" s="4" t="n"/>
+      <c r="F22" s="4" t="n">
+        <v>-29.1</v>
+      </c>
       <c r="G22" s="4" t="n">
         <v>-16.4</v>
       </c>
@@ -1291,7 +1335,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>토마토(토마토(1kg))</t>
+          <t>토마토</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1305,7 +1349,9 @@
       <c r="E23" s="4" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F23" s="4" t="n"/>
+      <c r="F23" s="4" t="n">
+        <v>3.9</v>
+      </c>
       <c r="G23" s="4" t="n">
         <v>22.8</v>
       </c>
@@ -1329,7 +1375,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>무(고랭지(1개))</t>
+          <t>무(고랭지)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1343,7 +1389,9 @@
       <c r="E24" s="4" t="n">
         <v>-12.1</v>
       </c>
-      <c r="F24" s="4" t="n"/>
+      <c r="F24" s="4" t="n">
+        <v>15.2</v>
+      </c>
       <c r="G24" s="4" t="n">
         <v>2.4</v>
       </c>
@@ -1367,7 +1415,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>당근(무세척(국산)(1kg))</t>
+          <t>당근(무세척(국산))</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1381,7 +1429,9 @@
       <c r="E25" s="4" t="n">
         <v>1.4</v>
       </c>
-      <c r="F25" s="4" t="n"/>
+      <c r="F25" s="4" t="n">
+        <v>12.4</v>
+      </c>
       <c r="G25" s="4" t="n">
         <v>12.1</v>
       </c>
@@ -1405,7 +1455,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>열무(열무(1kg))</t>
+          <t>열무</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1419,7 +1469,9 @@
       <c r="E26" s="4" t="n">
         <v>-4.2</v>
       </c>
-      <c r="F26" s="4" t="n"/>
+      <c r="F26" s="4" t="n">
+        <v>-24.5</v>
+      </c>
       <c r="G26" s="4" t="n">
         <v>-38.5</v>
       </c>
@@ -1443,7 +1495,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>건고추(화건(600g))</t>
+          <t>건고추(화건)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1457,7 +1509,9 @@
       <c r="E27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F27" s="4" t="n"/>
+      <c r="F27" s="4" t="n">
+        <v>2.3</v>
+      </c>
       <c r="G27" s="4" t="n">
         <v>1.2</v>
       </c>
@@ -1481,7 +1535,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>풋고추(풋고추(녹광 등)(100g))</t>
+          <t>풋고추(풋고추(녹광 등))</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1495,7 +1549,9 @@
       <c r="E28" s="4" t="n">
         <v>-1.4</v>
       </c>
-      <c r="F28" s="4" t="n"/>
+      <c r="F28" s="4" t="n">
+        <v>-17</v>
+      </c>
       <c r="G28" s="4" t="n">
         <v>3.3</v>
       </c>
@@ -1519,7 +1575,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>풋고추(꽈리고추(100g))</t>
+          <t>풋고추(꽈리고추)</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1533,7 +1589,9 @@
       <c r="E29" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="F29" s="4" t="n"/>
+      <c r="F29" s="4" t="n">
+        <v>-3.9</v>
+      </c>
       <c r="G29" s="4" t="n">
         <v>15.4</v>
       </c>
@@ -1557,7 +1615,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>풋고추(청양고추(100g))</t>
+          <t>풋고추(청양고추)</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1571,7 +1629,9 @@
       <c r="E30" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="F30" s="4" t="n"/>
+      <c r="F30" s="4" t="n">
+        <v>0.4</v>
+      </c>
       <c r="G30" s="4" t="n">
         <v>19.5</v>
       </c>
@@ -1595,7 +1655,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>풋고추(오이맛고추(100g))</t>
+          <t>풋고추(오이맛고추)</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1609,7 +1669,9 @@
       <c r="E31" s="4" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F31" s="4" t="n"/>
+      <c r="F31" s="4" t="n">
+        <v>-5.5</v>
+      </c>
       <c r="G31" s="4" t="n">
         <v>15.8</v>
       </c>
@@ -1633,7 +1695,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>붉은고추(붉은고추(100g))</t>
+          <t>붉은고추</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1647,7 +1709,9 @@
       <c r="E32" s="4" t="n">
         <v>0.8</v>
       </c>
-      <c r="F32" s="4" t="n"/>
+      <c r="F32" s="4" t="n">
+        <v>18.6</v>
+      </c>
       <c r="G32" s="4" t="n">
         <v>50.7</v>
       </c>
@@ -1671,7 +1735,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>양파(양파(1kg))</t>
+          <t>양파</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1685,7 +1749,9 @@
       <c r="E33" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F33" s="4" t="n"/>
+      <c r="F33" s="4" t="n">
+        <v>12.3</v>
+      </c>
       <c r="G33" s="4" t="n">
         <v>16.6</v>
       </c>
@@ -1709,7 +1775,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>파(대파(1kg))</t>
+          <t>파(대파)</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1723,7 +1789,9 @@
       <c r="E34" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="F34" s="4" t="n"/>
+      <c r="F34" s="4" t="n">
+        <v>5.1</v>
+      </c>
       <c r="G34" s="4" t="n">
         <v>10.6</v>
       </c>
@@ -1747,7 +1815,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>파(쪽파(1kg))</t>
+          <t>파(쪽파)</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1761,7 +1829,9 @@
       <c r="E35" s="4" t="n">
         <v>-2.6</v>
       </c>
-      <c r="F35" s="4" t="n"/>
+      <c r="F35" s="4" t="n">
+        <v>-16.5</v>
+      </c>
       <c r="G35" s="4" t="n">
         <v>-24.2</v>
       </c>
@@ -1785,7 +1855,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>생강(국산(1kg))</t>
+          <t>생강(국산)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1799,7 +1869,9 @@
       <c r="E36" s="4" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F36" s="4" t="n"/>
+      <c r="F36" s="4" t="n">
+        <v>-0.9</v>
+      </c>
       <c r="G36" s="4" t="n">
         <v>-1.8</v>
       </c>
@@ -1823,7 +1895,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>고춧가루(국산(1kg))</t>
+          <t>고춧가루(국산)</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1837,7 +1909,9 @@
       <c r="E37" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="F37" s="4" t="n"/>
+      <c r="F37" s="4" t="n">
+        <v>0.6</v>
+      </c>
       <c r="G37" s="4" t="n">
         <v>-0.4</v>
       </c>
@@ -1861,7 +1935,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>고춧가루(중국(1kg))</t>
+          <t>고춧가루(중국)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1875,7 +1949,9 @@
       <c r="E38" s="4" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F38" s="4" t="n"/>
+      <c r="F38" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="G38" s="4" t="n">
         <v>-0.1</v>
       </c>
@@ -1899,7 +1975,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>가지(가지(3개))</t>
+          <t>가지</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1913,7 +1989,9 @@
       <c r="E39" s="4" t="n">
         <v>-3.2</v>
       </c>
-      <c r="F39" s="4" t="n"/>
+      <c r="F39" s="4" t="n">
+        <v>-6.3</v>
+      </c>
       <c r="G39" s="4" t="n">
         <v>11.3</v>
       </c>
@@ -1929,7 +2007,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>미나리(미나리(100g))</t>
+          <t>미나리</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1943,7 +2021,9 @@
       <c r="E40" s="4" t="n">
         <v>-1.8</v>
       </c>
-      <c r="F40" s="4" t="n"/>
+      <c r="F40" s="4" t="n">
+        <v>-5.5</v>
+      </c>
       <c r="G40" s="4" t="n">
         <v>1.1</v>
       </c>
@@ -1967,7 +2047,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>깻잎(깻잎(50g))</t>
+          <t>깻잎</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1981,7 +2061,9 @@
       <c r="E41" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="F41" s="4" t="n"/>
+      <c r="F41" s="4" t="n">
+        <v>-19.8</v>
+      </c>
       <c r="G41" s="4" t="n">
         <v>-5.2</v>
       </c>
@@ -2005,7 +2087,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>부추(부추(100g))</t>
+          <t>부추</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2019,7 +2101,9 @@
       <c r="E42" s="4" t="n">
         <v>-3.8</v>
       </c>
-      <c r="F42" s="4" t="n"/>
+      <c r="F42" s="4" t="n">
+        <v>-1.6</v>
+      </c>
       <c r="G42" s="4" t="n">
         <v>1.7</v>
       </c>
@@ -2035,7 +2119,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>피망(청(100g))</t>
+          <t>피망(청)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2049,7 +2133,9 @@
       <c r="E43" s="4" t="n">
         <v>-1.9</v>
       </c>
-      <c r="F43" s="4" t="n"/>
+      <c r="F43" s="4" t="n">
+        <v>-23.3</v>
+      </c>
       <c r="G43" s="4" t="n">
         <v>17.5</v>
       </c>
@@ -2073,7 +2159,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>파프리카(파프리카(1개))</t>
+          <t>파프리카</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2087,7 +2173,9 @@
       <c r="E44" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="F44" s="4" t="n"/>
+      <c r="F44" s="4" t="n">
+        <v>-22.8</v>
+      </c>
       <c r="G44" s="4" t="n">
         <v>-3.3</v>
       </c>
@@ -2111,7 +2199,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>멜론(멜론(1개))</t>
+          <t>멜론</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2125,7 +2213,9 @@
       <c r="E45" s="4" t="n">
         <v>0.6</v>
       </c>
-      <c r="F45" s="4" t="n"/>
+      <c r="F45" s="4" t="n">
+        <v>5.1</v>
+      </c>
       <c r="G45" s="4" t="n">
         <v>5.5</v>
       </c>
@@ -2149,7 +2239,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>깐마늘(국산)(깐마늘(국산)(1kg))</t>
+          <t>깐마늘(국산)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2163,7 +2253,9 @@
       <c r="E46" s="4" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F46" s="4" t="n"/>
+      <c r="F46" s="4" t="n">
+        <v>-4.4</v>
+      </c>
       <c r="G46" s="4" t="n">
         <v>-7</v>
       </c>
@@ -2187,7 +2279,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>알배기배추(알배기배추(1포기))</t>
+          <t>알배기배추</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2201,7 +2293,9 @@
       <c r="E47" s="4" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F47" s="4" t="n"/>
+      <c r="F47" s="4" t="n">
+        <v>0.6</v>
+      </c>
       <c r="G47" s="4" t="n">
         <v>9</v>
       </c>
@@ -2225,7 +2319,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>브로콜리(브로콜리(국산)(1개))</t>
+          <t>브로콜리(브로콜리(국산))</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2239,7 +2333,9 @@
       <c r="E48" s="4" t="n">
         <v>-3.3</v>
       </c>
-      <c r="F48" s="4" t="n"/>
+      <c r="F48" s="4" t="n">
+        <v>-13.5</v>
+      </c>
       <c r="G48" s="4" t="n">
         <v>-7.6</v>
       </c>
@@ -2263,7 +2359,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>방울토마토(방울토마토(1kg))</t>
+          <t>방울토마토</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2277,7 +2373,9 @@
       <c r="E49" s="4" t="n">
         <v>-1.3</v>
       </c>
-      <c r="F49" s="4" t="n"/>
+      <c r="F49" s="4" t="n">
+        <v>11.7</v>
+      </c>
       <c r="G49" s="4" t="n">
         <v>22.6</v>
       </c>
@@ -2301,7 +2399,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>방울토마토(대추방울토마토(1kg))</t>
+          <t>방울토마토(대추방울토마토)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2315,7 +2413,9 @@
       <c r="E50" s="4" t="n">
         <v>-3.7</v>
       </c>
-      <c r="F50" s="4" t="n"/>
+      <c r="F50" s="4" t="n">
+        <v>10.2</v>
+      </c>
       <c r="G50" s="4" t="n">
         <v>42</v>
       </c>
@@ -2417,7 +2517,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>사과(홍로(10kg))</t>
+          <t>사과(홍로)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -2431,7 +2531,9 @@
       <c r="E2" s="4" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F2" s="4" t="n"/>
+      <c r="F2" s="4" t="n">
+        <v>-12.5</v>
+      </c>
       <c r="G2" s="4" t="n">
         <v>-24.5</v>
       </c>
@@ -2455,7 +2557,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>배(신고(15kg))</t>
+          <t>배(신고)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -2469,7 +2571,9 @@
       <c r="E3" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="F3" s="4" t="n"/>
+      <c r="F3" s="4" t="n">
+        <v>-12.1</v>
+      </c>
       <c r="G3" s="4" t="n"/>
       <c r="H3" s="4" t="n">
         <v>-10.9</v>
@@ -2491,7 +2595,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>바나나(수입(13kg))</t>
+          <t>바나나(수입)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -2505,7 +2609,9 @@
       <c r="E4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="4" t="n"/>
+      <c r="F4" s="4" t="n">
+        <v>-2.5</v>
+      </c>
       <c r="G4" s="4" t="n">
         <v>1.9</v>
       </c>
@@ -2529,7 +2635,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>파인애플(수입(12kg))</t>
+          <t>파인애플(수입)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -2543,7 +2649,9 @@
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="4" t="n"/>
+      <c r="F5" s="4" t="n">
+        <v>-0.2</v>
+      </c>
       <c r="G5" s="4" t="n">
         <v>2</v>
       </c>
@@ -2567,7 +2675,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>오렌지(네이블 호주(18kg))</t>
+          <t>오렌지(네이블 호주)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -2581,7 +2689,9 @@
       <c r="E6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="4" t="n"/>
+      <c r="F6" s="4" t="n">
+        <v>3.7</v>
+      </c>
       <c r="G6" s="4" t="n">
         <v>-1.7</v>
       </c>
@@ -2605,7 +2715,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>레몬(수입(17kg))</t>
+          <t>레몬(수입)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2619,7 +2729,9 @@
       <c r="E7" s="4" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F7" s="4" t="n"/>
+      <c r="F7" s="4" t="n">
+        <v>-5.4</v>
+      </c>
       <c r="G7" s="4" t="n">
         <v>-7.8</v>
       </c>
@@ -2643,7 +2755,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>망고(수입(5kg))</t>
+          <t>망고(수입)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2657,7 +2769,9 @@
       <c r="E8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="4" t="n"/>
+      <c r="F8" s="4" t="n">
+        <v>-4</v>
+      </c>
       <c r="G8" s="4" t="n">
         <v>5.2</v>
       </c>
@@ -2681,7 +2795,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>키위(골드(5.7kg))</t>
+          <t>키위(골드)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -2695,7 +2809,9 @@
       <c r="E9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="4" t="n"/>
+      <c r="F9" s="4" t="n">
+        <v>-1</v>
+      </c>
       <c r="G9" s="4" t="n">
         <v>-2</v>
       </c>
@@ -2711,7 +2827,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>배추(여름(고랭지)(10kg(그물망 3포기)))</t>
+          <t>배추(여름(고랭지))</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -2725,7 +2841,9 @@
       <c r="E10" s="4" t="n">
         <v>-3.7</v>
       </c>
-      <c r="F10" s="4" t="n"/>
+      <c r="F10" s="4" t="n">
+        <v>-20.5</v>
+      </c>
       <c r="G10" s="4" t="n">
         <v>10.1</v>
       </c>
@@ -2749,7 +2867,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>양배추(양배추(8kg))</t>
+          <t>양배추</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -2763,7 +2881,9 @@
       <c r="E11" s="4" t="n">
         <v>3.1</v>
       </c>
-      <c r="F11" s="4" t="n"/>
+      <c r="F11" s="4" t="n">
+        <v>5.4</v>
+      </c>
       <c r="G11" s="4" t="n">
         <v>48.2</v>
       </c>
@@ -2787,7 +2907,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>시금치(시금치(4kg))</t>
+          <t>시금치</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -2801,7 +2921,9 @@
       <c r="E12" s="4" t="n">
         <v>-11</v>
       </c>
-      <c r="F12" s="4" t="n"/>
+      <c r="F12" s="4" t="n">
+        <v>-47.6</v>
+      </c>
       <c r="G12" s="4" t="n">
         <v>-62.2</v>
       </c>
@@ -2825,7 +2947,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>상추(적(4kg))</t>
+          <t>상추(적)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -2839,7 +2961,9 @@
       <c r="E13" s="4" t="n">
         <v>-3.5</v>
       </c>
-      <c r="F13" s="4" t="n"/>
+      <c r="F13" s="4" t="n">
+        <v>-31.8</v>
+      </c>
       <c r="G13" s="4" t="n">
         <v>-76.09999999999999</v>
       </c>
@@ -2863,7 +2987,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>상추(청(4kg))</t>
+          <t>상추(청)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2877,7 +3001,9 @@
       <c r="E14" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="F14" s="4" t="n"/>
+      <c r="F14" s="4" t="n">
+        <v>-33.5</v>
+      </c>
       <c r="G14" s="4" t="n">
         <v>-76.59999999999999</v>
       </c>
@@ -2901,7 +3027,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>얼갈이배추(얼갈이배추(4kg))</t>
+          <t>얼갈이배추</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2915,7 +3041,9 @@
       <c r="E15" s="4" t="n">
         <v>-9.6</v>
       </c>
-      <c r="F15" s="4" t="n"/>
+      <c r="F15" s="4" t="n">
+        <v>-34.6</v>
+      </c>
       <c r="G15" s="4" t="n">
         <v>-61.1</v>
       </c>
@@ -2939,7 +3067,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>수박(수박(1개))</t>
+          <t>수박</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2953,7 +3081,9 @@
       <c r="E16" s="4" t="n">
         <v>-1.4</v>
       </c>
-      <c r="F16" s="4" t="n"/>
+      <c r="F16" s="4" t="n">
+        <v>-1.7</v>
+      </c>
       <c r="G16" s="4" t="n">
         <v>-5.3</v>
       </c>
@@ -2977,7 +3107,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>오이(가시계통(10kg))</t>
+          <t>오이(가시계통)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2991,7 +3121,9 @@
       <c r="E17" s="4" t="n">
         <v>-6.2</v>
       </c>
-      <c r="F17" s="4" t="n"/>
+      <c r="F17" s="4" t="n">
+        <v>-31.9</v>
+      </c>
       <c r="G17" s="4" t="n">
         <v>-54.1</v>
       </c>
@@ -3015,7 +3147,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>오이(다다기계통(50개))</t>
+          <t>오이(다다기계통)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -3029,7 +3161,9 @@
       <c r="E18" s="4" t="n">
         <v>1.5</v>
       </c>
-      <c r="F18" s="4" t="n"/>
+      <c r="F18" s="4" t="n">
+        <v>-23</v>
+      </c>
       <c r="G18" s="4" t="n">
         <v>-61.2</v>
       </c>
@@ -3053,7 +3187,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>오이(취청(50개))</t>
+          <t>오이(취청)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -3067,7 +3201,9 @@
       <c r="E19" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="F19" s="4" t="n"/>
+      <c r="F19" s="4" t="n">
+        <v>-30</v>
+      </c>
       <c r="G19" s="4" t="n">
         <v>-67.90000000000001</v>
       </c>
@@ -3091,7 +3227,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>호박(애호박(20개))</t>
+          <t>호박(애호박)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -3105,7 +3241,9 @@
       <c r="E20" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="F20" s="4" t="n"/>
+      <c r="F20" s="4" t="n">
+        <v>-46.5</v>
+      </c>
       <c r="G20" s="4" t="n">
         <v>-72.90000000000001</v>
       </c>
@@ -3129,7 +3267,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>호박(쥬키니(10kg))</t>
+          <t>호박(쥬키니)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -3143,7 +3281,9 @@
       <c r="E21" s="4" t="n">
         <v>-4.4</v>
       </c>
-      <c r="F21" s="4" t="n"/>
+      <c r="F21" s="4" t="n">
+        <v>-35.4</v>
+      </c>
       <c r="G21" s="4" t="n">
         <v>-68.90000000000001</v>
       </c>
@@ -3167,7 +3307,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>토마토(토마토(5kg))</t>
+          <t>토마토</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -3181,7 +3321,9 @@
       <c r="E22" s="4" t="n">
         <v>1.7</v>
       </c>
-      <c r="F22" s="4" t="n"/>
+      <c r="F22" s="4" t="n">
+        <v>-2.5</v>
+      </c>
       <c r="G22" s="4" t="n">
         <v>24</v>
       </c>
@@ -3205,7 +3347,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>무(고랭지(20kg))</t>
+          <t>무(고랭지)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3219,7 +3361,9 @@
       <c r="E23" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="F23" s="4" t="n"/>
+      <c r="F23" s="4" t="n">
+        <v>-1.7</v>
+      </c>
       <c r="G23" s="4" t="n">
         <v>16.4</v>
       </c>
@@ -3243,7 +3387,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>당근(무세척(국산)(20kg))</t>
+          <t>당근(무세척(국산))</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -3257,7 +3401,9 @@
       <c r="E24" s="4" t="n">
         <v>1.3</v>
       </c>
-      <c r="F24" s="4" t="n"/>
+      <c r="F24" s="4" t="n">
+        <v>2.3</v>
+      </c>
       <c r="G24" s="4" t="n">
         <v>11.3</v>
       </c>
@@ -3281,7 +3427,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>열무(열무(4kg))</t>
+          <t>열무</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -3295,7 +3441,9 @@
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F25" s="4" t="n"/>
+      <c r="F25" s="4" t="n">
+        <v>-29.5</v>
+      </c>
       <c r="G25" s="4" t="n">
         <v>-45.2</v>
       </c>
@@ -3319,7 +3467,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>건고추(화건(30kg))</t>
+          <t>건고추(화건)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3333,7 +3481,9 @@
       <c r="E26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F26" s="4" t="n"/>
+      <c r="F26" s="4" t="n">
+        <v>-1</v>
+      </c>
       <c r="G26" s="4" t="n">
         <v>-1.9</v>
       </c>
@@ -3357,7 +3507,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>풋고추(풋고추(녹광 등)(10kg))</t>
+          <t>풋고추(풋고추(녹광 등))</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -3371,7 +3521,9 @@
       <c r="E27" s="4" t="n">
         <v>-5.3</v>
       </c>
-      <c r="F27" s="4" t="n"/>
+      <c r="F27" s="4" t="n">
+        <v>-18.1</v>
+      </c>
       <c r="G27" s="4" t="n">
         <v>-11</v>
       </c>
@@ -3395,7 +3547,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>풋고추(꽈리고추(4kg))</t>
+          <t>풋고추(꽈리고추)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -3409,7 +3561,9 @@
       <c r="E28" s="4" t="n">
         <v>-8</v>
       </c>
-      <c r="F28" s="4" t="n"/>
+      <c r="F28" s="4" t="n">
+        <v>-42.8</v>
+      </c>
       <c r="G28" s="4" t="n">
         <v>-15.5</v>
       </c>
@@ -3433,7 +3587,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>풋고추(청양고추(10kg))</t>
+          <t>풋고추(청양고추)</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -3447,7 +3601,9 @@
       <c r="E29" s="4" t="n">
         <v>-6.3</v>
       </c>
-      <c r="F29" s="4" t="n"/>
+      <c r="F29" s="4" t="n">
+        <v>-6.9</v>
+      </c>
       <c r="G29" s="4" t="n">
         <v>-10.9</v>
       </c>
@@ -3471,7 +3627,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>풋고추(오이맛고추(10kg))</t>
+          <t>풋고추(오이맛고추)</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -3485,7 +3641,9 @@
       <c r="E30" s="4" t="n">
         <v>-4.7</v>
       </c>
-      <c r="F30" s="4" t="n"/>
+      <c r="F30" s="4" t="n">
+        <v>-26.9</v>
+      </c>
       <c r="G30" s="4" t="n">
         <v>9.5</v>
       </c>
@@ -3509,7 +3667,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>붉은고추(붉은고추(10kg))</t>
+          <t>붉은고추</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -3523,7 +3681,9 @@
       <c r="E31" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F31" s="4" t="n"/>
+      <c r="F31" s="4" t="n">
+        <v>0.8</v>
+      </c>
       <c r="G31" s="4" t="n">
         <v>124.3</v>
       </c>
@@ -3547,7 +3707,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>피마늘(한지(10kg))</t>
+          <t>피마늘(한지)</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3561,7 +3721,9 @@
       <c r="E32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F32" s="4" t="n"/>
+      <c r="F32" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="G32" s="4" t="n">
         <v>4.5</v>
       </c>
@@ -3585,7 +3747,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>피마늘(난지(대서)(10kg))</t>
+          <t>피마늘(난지(대서))</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3599,7 +3761,9 @@
       <c r="E33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F33" s="4" t="n"/>
+      <c r="F33" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="G33" s="4" t="n">
         <v>0</v>
       </c>
@@ -3623,7 +3787,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>양파(양파(15kg))</t>
+          <t>양파</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3637,7 +3801,9 @@
       <c r="E34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F34" s="4" t="n"/>
+      <c r="F34" s="4" t="n">
+        <v>0.6</v>
+      </c>
       <c r="G34" s="4" t="n">
         <v>1.4</v>
       </c>
@@ -3661,7 +3827,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>파(대파(1kg))</t>
+          <t>파(대파)</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3675,7 +3841,9 @@
       <c r="E35" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="F35" s="4" t="n"/>
+      <c r="F35" s="4" t="n">
+        <v>-6.3</v>
+      </c>
       <c r="G35" s="4" t="n">
         <v>-9.699999999999999</v>
       </c>
@@ -3699,7 +3867,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>파(쪽파(1kg))</t>
+          <t>파(쪽파)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3713,7 +3881,9 @@
       <c r="E36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F36" s="4" t="n"/>
+      <c r="F36" s="4" t="n">
+        <v>-9.199999999999999</v>
+      </c>
       <c r="G36" s="4" t="n">
         <v>-23.2</v>
       </c>
@@ -3737,7 +3907,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>생강(국산(10kg))</t>
+          <t>생강(국산)</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3751,7 +3921,9 @@
       <c r="E37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F37" s="4" t="n"/>
+      <c r="F37" s="4" t="n">
+        <v>-0.8</v>
+      </c>
       <c r="G37" s="4" t="n">
         <v>-2.2</v>
       </c>
@@ -3775,7 +3947,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>가지(가지(5kg))</t>
+          <t>가지</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3789,7 +3961,9 @@
       <c r="E38" s="4" t="n">
         <v>-0.6</v>
       </c>
-      <c r="F38" s="4" t="n"/>
+      <c r="F38" s="4" t="n">
+        <v>-47.5</v>
+      </c>
       <c r="G38" s="4" t="n">
         <v>-38.6</v>
       </c>
@@ -3805,7 +3979,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>미나리(미나리(8kg))</t>
+          <t>미나리</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3819,7 +3993,9 @@
       <c r="E39" s="4" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F39" s="4" t="n"/>
+      <c r="F39" s="4" t="n">
+        <v>-22.7</v>
+      </c>
       <c r="G39" s="4" t="n">
         <v>-16.5</v>
       </c>
@@ -3843,7 +4019,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>깻잎(깻잎(2kg))</t>
+          <t>깻잎</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3857,7 +4033,9 @@
       <c r="E40" s="4" t="n">
         <v>-8.1</v>
       </c>
-      <c r="F40" s="4" t="n"/>
+      <c r="F40" s="4" t="n">
+        <v>-44.2</v>
+      </c>
       <c r="G40" s="4" t="n">
         <v>-38.9</v>
       </c>
@@ -3881,7 +4059,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>부추(부추(4kg))</t>
+          <t>부추</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3895,7 +4073,9 @@
       <c r="E41" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="F41" s="4" t="n"/>
+      <c r="F41" s="4" t="n">
+        <v>-26.1</v>
+      </c>
       <c r="G41" s="4" t="n">
         <v>-10.8</v>
       </c>
@@ -3911,7 +4091,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>피망(청(10kg))</t>
+          <t>피망(청)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3925,7 +4105,9 @@
       <c r="E42" s="4" t="n">
         <v>-7.4</v>
       </c>
-      <c r="F42" s="4" t="n"/>
+      <c r="F42" s="4" t="n">
+        <v>-40.7</v>
+      </c>
       <c r="G42" s="4" t="n">
         <v>-20.7</v>
       </c>
@@ -3949,7 +4131,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>파프리카(파프리카(5kg))</t>
+          <t>파프리카</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3963,7 +4145,9 @@
       <c r="E43" s="4" t="n">
         <v>-2.6</v>
       </c>
-      <c r="F43" s="4" t="n"/>
+      <c r="F43" s="4" t="n">
+        <v>-24.9</v>
+      </c>
       <c r="G43" s="4" t="n">
         <v>-41.5</v>
       </c>
@@ -3987,7 +4171,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>멜론(멜론(8kg))</t>
+          <t>멜론</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -4001,7 +4185,9 @@
       <c r="E44" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F44" s="4" t="n"/>
+      <c r="F44" s="4" t="n">
+        <v>-0.3</v>
+      </c>
       <c r="G44" s="4" t="n">
         <v>9.4</v>
       </c>
@@ -4025,7 +4211,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>깐마늘(국산)(깐마늘(대서)(20kg))</t>
+          <t>깐마늘(국산)(깐마늘(대서))</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -4039,7 +4225,9 @@
       <c r="E45" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F45" s="4" t="n"/>
+      <c r="F45" s="4" t="n">
+        <v>-0.1</v>
+      </c>
       <c r="G45" s="4" t="n">
         <v>-0.1</v>
       </c>
@@ -4063,7 +4251,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>깐마늘(국산)(깐마늘(남도)(20kg))</t>
+          <t>깐마늘(국산)(깐마늘(남도))</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4077,7 +4265,9 @@
       <c r="E46" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F46" s="4" t="n"/>
+      <c r="F46" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="G46" s="4" t="n">
         <v>0</v>
       </c>
@@ -4101,7 +4291,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>알배기배추(알배기배추(8kg))</t>
+          <t>알배기배추</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4115,7 +4305,9 @@
       <c r="E47" s="4" t="n">
         <v>-1.6</v>
       </c>
-      <c r="F47" s="4" t="n"/>
+      <c r="F47" s="4" t="n">
+        <v>-45.2</v>
+      </c>
       <c r="G47" s="4" t="n">
         <v>-37.6</v>
       </c>
@@ -4139,7 +4331,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>브로콜리(브로콜리(국산)(8kg))</t>
+          <t>브로콜리(브로콜리(국산))</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4153,7 +4345,9 @@
       <c r="E48" s="4" t="n">
         <v>-9.1</v>
       </c>
-      <c r="F48" s="4" t="n"/>
+      <c r="F48" s="4" t="n">
+        <v>-40.6</v>
+      </c>
       <c r="G48" s="4" t="n">
         <v>-44</v>
       </c>
@@ -4177,7 +4371,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>방울토마토(대추방울토마토(3kg))</t>
+          <t>방울토마토(대추방울토마토)</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4191,7 +4385,9 @@
       <c r="E49" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="F49" s="4" t="n"/>
+      <c r="F49" s="4" t="n">
+        <v>-10.5</v>
+      </c>
       <c r="G49" s="4" t="n">
         <v>29.2</v>
       </c>

--- a/docs/fruitbasket_prices.xlsx
+++ b/docs/fruitbasket_prices.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신_소매" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신_도매" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최근이력" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자료출처" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,19 +437,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -464,40 +466,45 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>등급</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>단위</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>오늘 가격(원)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>전일 대비(%)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1주 전 대비(%)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>1개월 전 대비(%)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>1년 전 대비(%)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>평년 대비(%)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>가격 수준</t>
         </is>
@@ -516,28 +523,33 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>10개</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>23561</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="F2" s="4" t="n">
         <v>-1.9</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="G2" s="4" t="n">
         <v>4.3</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="H2" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="I2" s="4" t="n">
         <v>-12.4</v>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="J2" s="4" t="n">
         <v>-6.7</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -556,28 +568,33 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t>10개</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>31767</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="F3" s="4" t="n">
         <v>0.6</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="G3" s="4" t="n">
         <v>2.4</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="H3" s="4" t="n">
         <v>-30</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="I3" s="4" t="n">
         <v>1.4</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="J3" s="4" t="n">
         <v>-0.7</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -591,35 +608,40 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>바나나(수입)</t>
+          <t>포도(캠벨얼리)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>100g</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>328</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>0</v>
+          <t>L과</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1kg</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>7806</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-1.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.9</v>
+        <v>14.9</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-3.2</v>
+        <v>5.6</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>보통</t>
+        <v>4.5</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
         </is>
       </c>
     </row>
@@ -631,35 +653,40 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>파인애플(수입)</t>
+          <t>포도(거봉)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1개</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>7484</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>0.4</v>
+          <t>L과</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2kg</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>20048</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.9</v>
+        <v>12.8</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-7.7</v>
+        <v>11.2</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>보통</t>
+        <v>-3</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>-14</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
         </is>
       </c>
     </row>
@@ -671,33 +698,38 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>레몬(수입)</t>
+          <t>포도(샤인머스켓)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10개</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>7820</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>0</v>
+          <t>L과</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2kg</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>11624</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-5.7</v>
+        <v>-1.4</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-12.7</v>
+        <v>-9</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-20.1</v>
+        <v>-23</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-22.4</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+        <v>-21.4</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>-50</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -711,35 +743,40 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>망고(수입)</t>
+          <t>감귤(시설)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1개</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>7512</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>-0.2</v>
+          <t>M과</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10개</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>7043</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.2</v>
+        <v>-0</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>9.1</v>
+        <v>-3.7</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>37.1</v>
+        <v>-6.1</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>비쌈</t>
+        <v>-17</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>-16.1</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
         </is>
       </c>
     </row>
@@ -751,29 +788,42 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>블루베리(수입(냉동))</t>
+          <t>바나나(수입)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>11477</v>
-      </c>
-      <c r="E8" s="4" t="n">
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>100g</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>328</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="H8" s="4" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F8" s="4" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="n"/>
-      <c r="J8" s="2" t="n"/>
+      <c r="I8" s="4" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -783,35 +833,40 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>아보카도(수입)</t>
+          <t>파인애플(수입)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>1개</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
-        <v>1906</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>0.7</v>
+      <c r="E9" s="3" t="n">
+        <v>7484</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>8.5</v>
+        <v>0.9</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.7</v>
+        <v>0.9</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-5.1</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>쌈</t>
+        <v>-7.7</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -823,65 +878,83 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>키위(골드)</t>
+          <t>오렌지(네이블 호주)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>중품</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>10개</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n">
-        <v>14105</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>-0.4</v>
+      <c r="E10" s="3" t="n">
+        <v>12479</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>11.2</v>
+        <v>-0.2</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n"/>
-      <c r="J10" s="2" t="n"/>
+        <v>7.9</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>채소류</t>
+          <t>과일류</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>배추(여름(고랭지))</t>
+          <t>레몬(수입)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1포기</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>6111</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>-0.9</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10개</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>7820</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>3.9</v>
+        <v>-5.7</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-8.699999999999999</v>
+        <v>-12.7</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-14.7</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+        <v>-20.1</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>-22.4</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -890,118 +963,125 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>채소류</t>
+          <t>과일류</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>양배추</t>
+          <t>망고(수입)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1포기</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>3935</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>1</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>7512</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>33.2</v>
+        <v>-0.2</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>25.4</v>
+        <v>-4.2</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-4.4</v>
+        <v>9.1</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-11.1</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>쌈</t>
+        <v>37.1</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>비쌈</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>채소류</t>
+          <t>과일류</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>시금치</t>
+          <t>블루베리(수입(냉동))</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>100g</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>1174</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>-6</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1kg</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>11477</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-32.3</v>
+        <v>-0.9</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-49.6</v>
+        <v>-0.9</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-38.6</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>-30.7</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>쌈</t>
-        </is>
-      </c>
+        <v>0.3</v>
+      </c>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>채소류</t>
+          <t>과일류</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>상추(적)</t>
+          <t>아보카도(수입)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>100g</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>1096</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>-2.4</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>1906</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-35.5</v>
+        <v>0.7</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-39.7</v>
+        <v>-0.5</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-46.2</v>
+        <v>8.5</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-32.8</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+        <v>-2.7</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -1010,42 +1090,39 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>채소류</t>
+          <t>과일류</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>상추(청)</t>
+          <t>키위(골드)</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>100g</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>1058</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-2.7</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>10개</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>14105</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-39.6</v>
+        <v>-0.4</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-42.4</v>
+        <v>11.2</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-53.1</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>-40.4</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>쌈</t>
-        </is>
-      </c>
+        <v>2.1</v>
+      </c>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1055,33 +1132,38 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>얼갈이배추</t>
+          <t>배추(여름(고랭지))</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>2435</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>-2.8</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1포기</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>6111</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-21.9</v>
+        <v>-0.9</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-33.2</v>
+        <v>2.7</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-36.9</v>
+        <v>3.9</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-29.8</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>-14.7</v>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -1095,35 +1177,40 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>수박</t>
+          <t>양배추</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1개</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>23820</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>0</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1포기</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>3935</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.1</v>
+        <v>33.2</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-12.9</v>
+        <v>25.4</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>보통</t>
+        <v>-4.4</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>-11.1</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
         </is>
       </c>
     </row>
@@ -1135,33 +1222,38 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>오이(가시계통)</t>
+          <t>시금치</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10개</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>8489</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>-0.2</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>100g</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>1174</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-28.7</v>
+        <v>-6</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-24.6</v>
+        <v>-32.3</v>
       </c>
       <c r="H18" s="4" t="n">
+        <v>-49.6</v>
+      </c>
+      <c r="I18" s="4" t="n">
         <v>-38.6</v>
       </c>
-      <c r="I18" s="4" t="n">
-        <v>-36.9</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" s="4" t="n">
+        <v>-30.7</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -1175,33 +1267,38 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>오이(다다기계통)</t>
+          <t>상추(적)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10개</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>6536</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>-2</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>100g</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>1096</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-28.3</v>
+        <v>-2.4</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-40</v>
+        <v>-35.5</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-47.1</v>
+        <v>-39.7</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-45</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+        <v>-46.2</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>-32.8</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -1215,33 +1312,38 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>오이(취청)</t>
+          <t>상추(청)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>10개</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>10100</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>-1.6</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>100g</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>1058</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-30.8</v>
+        <v>-2.7</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-32.4</v>
+        <v>-39.6</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-34.2</v>
+        <v>-42.4</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-30.8</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+        <v>-53.1</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>-40.4</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -1255,33 +1357,38 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>호박(애호박)</t>
+          <t>얼갈이배추</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1개</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>1330</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>-0.7</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>1kg</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>2435</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-25.6</v>
+        <v>-2.8</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-47.8</v>
+        <v>-21.9</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-31.7</v>
+        <v>-33.2</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-23.4</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
+        <v>-36.9</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>-29.8</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -1295,35 +1402,40 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>호박(쥬키니)</t>
+          <t>수박</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>1개</t>
         </is>
       </c>
-      <c r="D22" s="3" t="n">
-        <v>1668</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>-0.4</v>
+      <c r="E22" s="3" t="n">
+        <v>23820</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-29.1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-16.4</v>
+        <v>4.3</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-21.3</v>
+        <v>-0.1</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-23.3</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>쌈</t>
+        <v>-12.9</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -1335,33 +1447,38 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>토마토</t>
+          <t>오이(가시계통)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>7889</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>-0.9</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>10개</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>8489</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.9</v>
+        <v>-0.2</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>22.8</v>
+        <v>-28.7</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.9</v>
+        <v>-24.6</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+        <v>-38.6</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>-36.9</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -1375,33 +1492,38 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>무(고랭지)</t>
+          <t>오이(다다기계통)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1개</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>2470</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>-12.1</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>10개</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>6536</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>15.2</v>
+        <v>-2</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.4</v>
+        <v>-28.3</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>18.1</v>
+        <v>-40</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-11.7</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+        <v>-47.1</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>-45</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -1415,33 +1537,38 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>당근(무세척(국산))</t>
+          <t>오이(취청)</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>4348</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>1.4</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>10개</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>10100</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>12.4</v>
+        <v>-1.6</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>12.1</v>
+        <v>-30.8</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>15.9</v>
+        <v>-32.4</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-15.9</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
+        <v>-34.2</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>-30.8</v>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -1455,33 +1582,38 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>열무</t>
+          <t>호박(애호박)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>2302</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>-4.2</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>1330</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-24.5</v>
+        <v>-0.7</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-38.5</v>
+        <v>-25.6</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-36.6</v>
+        <v>-47.8</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-31.3</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
+        <v>-31.7</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>-23.4</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -1495,35 +1627,40 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>건고추(화건)</t>
+          <t>호박(쥬키니)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>600g</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>17911</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>0</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>1668</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.3</v>
+        <v>-0.4</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.2</v>
+        <v>-29.1</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>7.7</v>
+        <v>-16.4</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>보통</t>
+        <v>-21.3</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>-23.3</v>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
         </is>
       </c>
     </row>
@@ -1535,35 +1672,40 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>풋고추(풋고추(녹광 등))</t>
+          <t>토마토</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>100g</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>1698</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>-1.4</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1kg</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>7889</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-17</v>
+        <v>-0.9</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-19.1</v>
+        <v>22.8</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>보통</t>
+        <v>-0.9</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
         </is>
       </c>
     </row>
@@ -1575,33 +1717,38 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>풋고추(꽈리고추)</t>
+          <t>무(고랭지)</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>100g</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>1594</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>-1</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>2470</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-3.9</v>
+        <v>-12.1</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-19.1</v>
+        <v>2.4</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-14.1</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
+        <v>18.1</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>-11.7</v>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -1615,35 +1762,40 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>풋고추(청양고추)</t>
+          <t>당근(무세척(국산))</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>100g</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>1406</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>0.1</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>1kg</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>4348</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>19.5</v>
+        <v>12.4</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-6.9</v>
+        <v>12.1</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>보통</t>
+        <v>15.9</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>-15.9</v>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
         </is>
       </c>
     </row>
@@ -1655,35 +1807,40 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>풋고추(오이맛고추)</t>
+          <t>열무</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>100g</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>1262</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>-0.3</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>1kg</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>2302</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-5.5</v>
+        <v>-4.2</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>15.8</v>
+        <v>-24.5</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-12.2</v>
+        <v>-38.5</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>보통</t>
+        <v>-36.6</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>-31.3</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
         </is>
       </c>
     </row>
@@ -1695,35 +1852,40 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>붉은고추</t>
+          <t>건고추(화건)</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>100g</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>2926</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>0.8</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>600g</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>17911</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>18.6</v>
+        <v>0</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>50.7</v>
+        <v>2.3</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>35.7</v>
+        <v>1.2</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>매우 비쌈</t>
+        <v>7.7</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -1735,33 +1897,38 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>양파</t>
+          <t>풋고추(풋고추(녹광 등))</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>2166</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>2</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>100g</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>1698</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>12.3</v>
+        <v>-1.4</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>16.6</v>
+        <v>-17</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>12.4</v>
+        <v>3.3</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
+        <v>-19.1</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -1775,33 +1942,38 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>파(대파)</t>
+          <t>풋고추(꽈리고추)</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>3026</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>0.9</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>100g</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>1594</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.1</v>
+        <v>-1</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>10.6</v>
+        <v>-3.9</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-3.5</v>
+        <v>15.4</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-6.7</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+        <v>-19.1</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>-14.1</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -1815,35 +1987,40 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>파(쪽파)</t>
+          <t>풋고추(청양고추)</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>7499</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>-2.6</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>100g</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>1406</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-16.5</v>
+        <v>0.1</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-24.2</v>
+        <v>0.4</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-16.5</v>
+        <v>19.5</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-19.2</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>쌈</t>
+        <v>-6.9</v>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -1855,35 +2032,40 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>생강(국산)</t>
+          <t>풋고추(오이맛고추)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>14838</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>-0.1</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>100g</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>1262</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>-0.9</v>
+        <v>-0.3</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-1.8</v>
+        <v>-5.5</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-5.2</v>
+        <v>15.8</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>비쌈</t>
+        <v>-12.2</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -1895,35 +2077,40 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>고춧가루(국산)</t>
+          <t>붉은고추</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>33884</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>-1</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>100g</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>2926</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-0.4</v>
+        <v>18.6</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.4</v>
+        <v>50.7</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>보통</t>
+        <v>35.7</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>매우 비쌈</t>
         </is>
       </c>
     </row>
@@ -1935,33 +2122,38 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>고춧가루(중국)</t>
+          <t>양파</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="D38" s="3" t="n">
-        <v>13544</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>-0.2</v>
+      <c r="E38" s="3" t="n">
+        <v>2166</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.1</v>
+        <v>12.3</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0.9</v>
+        <v>16.6</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
+        <v>12.4</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -1975,29 +2167,42 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>가지</t>
+          <t>파(대파)</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>3개</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>2407</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>-3.2</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>1kg</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>3026</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>-6.3</v>
+        <v>0.9</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="H39" s="4" t="n"/>
-      <c r="I39" s="4" t="n"/>
-      <c r="J39" s="2" t="n"/>
+        <v>5.1</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2007,35 +2212,40 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>미나리</t>
+          <t>파(쪽파)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>100g</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>1873</v>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>-1.8</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>1kg</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>7499</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>-5.5</v>
+        <v>-2.6</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>1.1</v>
+        <v>-16.5</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-1.1</v>
+        <v>-24.2</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>비쌈</t>
+        <v>-16.5</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>-19.2</v>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
         </is>
       </c>
     </row>
@@ -2047,35 +2257,40 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>깻잎</t>
+          <t>생강(국산)</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>50g</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>1537</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>-4</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>1kg</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>14838</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>-19.8</v>
+        <v>-0.1</v>
       </c>
       <c r="G41" s="4" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="I41" s="4" t="n">
         <v>-5.2</v>
       </c>
-      <c r="H41" s="4" t="n">
-        <v>-7.4</v>
-      </c>
-      <c r="I41" s="4" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>보통</t>
+      <c r="J41" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>비쌈</t>
         </is>
       </c>
     </row>
@@ -2087,29 +2302,42 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>부추</t>
+          <t>고춧가루(국산)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>100g</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>838</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>-3.8</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>1kg</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>33884</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>-1.6</v>
+        <v>-1</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H42" s="4" t="n"/>
-      <c r="I42" s="4" t="n"/>
-      <c r="J42" s="2" t="n"/>
+        <v>0.6</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2119,35 +2347,40 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>피망(청)</t>
+          <t>고춧가루(중국)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>100g</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>1950</v>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>-1.9</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>1kg</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>13544</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>-23.3</v>
+        <v>-0.2</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>28.9</v>
+        <v>-0.1</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>매우 비쌈</t>
+        <v>0.9</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -2159,37 +2392,34 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>파프리카</t>
+          <t>가지</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>1개</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>1861</v>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>-2.8</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>3개</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>2407</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>-22.8</v>
+        <v>-3.2</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>-3.3</v>
+        <v>-6.3</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>-11.9</v>
-      </c>
-      <c r="I44" s="4" t="n">
-        <v>-14.9</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>쌈</t>
-        </is>
-      </c>
+        <v>11.3</v>
+      </c>
+      <c r="I44" s="4" t="n"/>
+      <c r="J44" s="4" t="n"/>
+      <c r="K44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2199,35 +2429,40 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>멜론</t>
+          <t>미나리</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>1개</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>9538</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>0.6</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>100g</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>1873</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>5.1</v>
+        <v>-1.8</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>5.5</v>
+        <v>-5.5</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>-9</v>
+        <v>1.1</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>쌈</t>
+        <v>-1.1</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>비쌈</t>
         </is>
       </c>
     </row>
@@ -2239,35 +2474,40 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>깐마늘(국산)</t>
+          <t>깻잎</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>10133</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>-0.3</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>50g</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>1537</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>-4.4</v>
+        <v>-4</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>-7</v>
+        <v>-19.8</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>3.3</v>
+        <v>-5.2</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>-5.9</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>쌈</t>
+        <v>-7.4</v>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -2279,37 +2519,34 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>알배기배추</t>
+          <t>부추</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>1포기</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>4602</v>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>-0.2</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>100g</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>838</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.6</v>
+        <v>-3.8</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>9</v>
+        <v>-1.6</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>-10.7</v>
-      </c>
-      <c r="I47" s="4" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>쌈</t>
-        </is>
-      </c>
+        <v>1.7</v>
+      </c>
+      <c r="I47" s="4" t="n"/>
+      <c r="J47" s="4" t="n"/>
+      <c r="K47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2319,35 +2556,40 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>브로콜리(브로콜리(국산))</t>
+          <t>피망(청)</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>1개</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="n">
-        <v>3280</v>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>-3.3</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>100g</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>1950</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>-13.5</v>
+        <v>-1.9</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>-7.6</v>
+        <v>-23.3</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>-17.7</v>
+        <v>17.5</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>-18.1</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>쌈</t>
+        <v>28.9</v>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>매우 비쌈</t>
         </is>
       </c>
     </row>
@@ -2359,33 +2601,38 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>방울토마토</t>
+          <t>파프리카</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="n">
-        <v>9093</v>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>-1.3</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>1861</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>11.7</v>
+        <v>-2.8</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>22.6</v>
+        <v>-22.8</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>-20</v>
+        <v>-3.3</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>-14.8</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
+        <v>-11.9</v>
+      </c>
+      <c r="J49" s="4" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -2399,33 +2646,263 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
+          <t>멜론</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>9538</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>-9</v>
+      </c>
+      <c r="J50" s="4" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>채소류</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>깐마늘(국산)</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>1kg</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>10133</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J51" s="4" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>채소류</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>알배기배추</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>1포기</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>4602</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="J52" s="4" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>채소류</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>브로콜리(브로콜리(국산))</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>3280</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>-17.7</v>
+      </c>
+      <c r="J53" s="4" t="n">
+        <v>-18.1</v>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>채소류</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>방울토마토</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>1kg</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>9093</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>-14.8</v>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>채소류</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>방울토마토(대추방울토마토)</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E55" s="3" t="n">
         <v>10762</v>
       </c>
-      <c r="E50" s="4" t="n">
+      <c r="F55" s="4" t="n">
         <v>-3.7</v>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="G55" s="4" t="n">
         <v>10.2</v>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="H55" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="H50" s="4" t="n">
+      <c r="I55" s="4" t="n">
         <v>-1.2</v>
       </c>
-      <c r="I50" s="4" t="n">
+      <c r="J55" s="4" t="n">
         <v>-5.1</v>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -2442,19 +2919,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2470,40 +2948,45 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>등급</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>단위</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>오늘 가격(원)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>전일 대비(%)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1주 전 대비(%)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>1개월 전 대비(%)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>1년 전 대비(%)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>평년 대비(%)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>가격 수준</t>
         </is>
@@ -2522,28 +3005,33 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>10kg</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>51560</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="F2" s="4" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="G2" s="4" t="n">
         <v>-12.5</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="H2" s="4" t="n">
         <v>-24.5</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="I2" s="4" t="n">
         <v>-36.1</v>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="J2" s="4" t="n">
         <v>-1.6</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -2562,26 +3050,31 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t>15kg</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>53560</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="F3" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="G3" s="4" t="n">
         <v>-12.1</v>
       </c>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n">
         <v>-10.9</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="J3" s="4" t="n">
         <v>5.4</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>비쌈</t>
         </is>
@@ -2595,35 +3088,40 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>바나나(수입)</t>
+          <t>포도(캠벨얼리)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>13kg</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>31940</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>0</v>
+          <t>L과</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3kg</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>18400</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-2.5</v>
+        <v>-6.4</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>1.9</v>
+        <v>-8</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-3.3</v>
+        <v>-6.2</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>보통</t>
+        <v>-10.3</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
         </is>
       </c>
     </row>
@@ -2635,35 +3133,40 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>파인애플(수입)</t>
+          <t>포도(거봉)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12kg</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>39940</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>0</v>
+          <t>L과</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2kg</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>13780</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>-0.2</v>
+        <v>-3.2</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>2</v>
+        <v>-6.5</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-8.5</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>보통</t>
+        <v>-19.4</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>-18.8</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
         </is>
       </c>
     </row>
@@ -2675,33 +3178,38 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>오렌지(네이블 호주)</t>
+          <t>포도(샤인머스켓)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18kg</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>60075</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>0</v>
+          <t>L과</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2kg</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>10226</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3.7</v>
+        <v>-3.1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.7</v>
+        <v>-3.9</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-10.3</v>
+        <v>-18</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-8.699999999999999</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+        <v>-1.9</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>-19.5</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -2715,35 +3223,40 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>레몬(수입)</t>
+          <t>감귤(시설)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17kg</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>57180</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>-0.2</v>
+          <t>M과</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3kg</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>18580</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-5.4</v>
+        <v>0</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-7.8</v>
+        <v>-5.2</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>12</v>
+        <v>-2.5</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-12</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>쌈</t>
+        <v>-9.1</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -2755,35 +3268,40 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>망고(수입)</t>
+          <t>바나나(수입)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5kg</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>78025</v>
-      </c>
-      <c r="E8" s="4" t="n">
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>13kg</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>31940</v>
+      </c>
+      <c r="F8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="4" t="n">
-        <v>-4</v>
-      </c>
       <c r="G8" s="4" t="n">
-        <v>5.2</v>
+        <v>-2.5</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>10.5</v>
+        <v>1.9</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>매우 비쌈</t>
+        <v>-3.3</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -2795,65 +3313,83 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>키위(골드)</t>
+          <t>파인애플(수입)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5.7kg</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>40220</v>
-      </c>
-      <c r="E9" s="4" t="n">
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>12kg</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>39940</v>
+      </c>
+      <c r="F9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>-1</v>
-      </c>
       <c r="G9" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="2" t="n"/>
+        <v>-0.2</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>채소류</t>
+          <t>과일류</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>배추(여름(고랭지))</t>
+          <t>오렌지(네이블 호주)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>10kg(그물망 3포기)</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>17000</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>-3.7</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>18kg</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>60075</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-20.5</v>
+        <v>0</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10.1</v>
+        <v>3.7</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-26.3</v>
+        <v>-1.7</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-18.3</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+        <v>-10.3</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -2862,38 +3398,43 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>채소류</t>
+          <t>과일류</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>양배추</t>
+          <t>레몬(수입)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8kg</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>8878</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>3.1</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17kg</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>57180</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5.4</v>
+        <v>-0.2</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>48.2</v>
+        <v>-5.4</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.2</v>
+        <v>-7.8</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-17.7</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>-12</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -2902,82 +3443,84 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>채소류</t>
+          <t>과일류</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>시금치</t>
+          <t>망고(수입)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4kg</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>23260</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>-11</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5kg</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>78025</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-47.6</v>
+        <v>0</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-62.2</v>
+        <v>-4</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-49.6</v>
+        <v>5.2</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-28.4</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>쌈</t>
+        <v>10.5</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>매우 비쌈</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>채소류</t>
+          <t>과일류</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>상추(적)</t>
+          <t>키위(골드)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4kg</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>14680</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>-3.5</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5.7kg</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>40220</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-31.8</v>
+        <v>0</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-76.09999999999999</v>
+        <v>-1</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-69.90000000000001</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>-63.3</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>쌈</t>
-        </is>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2987,33 +3530,38 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>상추(청)</t>
+          <t>배추(여름(고랭지))</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4kg</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>14625</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>-3</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10kg(그물망 3포기)</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>17000</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-33.5</v>
+        <v>-3.7</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-76.59999999999999</v>
+        <v>-20.5</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-69.3</v>
+        <v>10.1</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-60.9</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+        <v>-26.3</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>-18.3</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -3027,33 +3575,38 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>얼갈이배추</t>
+          <t>양배추</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4kg</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>5664</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-9.6</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>8kg</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>8878</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-34.6</v>
+        <v>3.1</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-61.1</v>
+        <v>5.4</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-40.9</v>
+        <v>48.2</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-34.1</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+        <v>4.2</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>-17.7</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -3067,35 +3620,40 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>수박</t>
+          <t>시금치</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1개</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>17980</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>-1.4</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4kg</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>23260</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.7</v>
+        <v>-11</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-5.3</v>
+        <v>-47.6</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>6.8</v>
+        <v>-62.2</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>비쌈</t>
+        <v>-49.6</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>-28.4</v>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
         </is>
       </c>
     </row>
@@ -3107,33 +3665,38 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>오이(가시계통)</t>
+          <t>상추(적)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10kg</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>12800</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>-6.2</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4kg</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>14680</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-31.9</v>
+        <v>-3.5</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-54.1</v>
+        <v>-31.8</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-48.5</v>
+        <v>-76.09999999999999</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-53.3</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+        <v>-69.90000000000001</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>-63.3</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -3147,33 +3710,38 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>오이(다다기계통)</t>
+          <t>상추(청)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>50개</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>21400</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>1.5</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4kg</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>14625</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-23</v>
+        <v>-3</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-61.2</v>
+        <v>-33.5</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-47.6</v>
+        <v>-76.59999999999999</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-39.1</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
+        <v>-69.3</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>-60.9</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -3187,33 +3755,38 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>오이(취청)</t>
+          <t>얼갈이배추</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>50개</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>16867</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>-0.8</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4kg</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>5664</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-30</v>
+        <v>-9.6</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-67.90000000000001</v>
+        <v>-34.6</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-57.2</v>
+        <v>-61.1</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-53.2</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+        <v>-40.9</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>-34.1</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -3227,35 +3800,40 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>호박(애호박)</t>
+          <t>수박</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>20개</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>13140</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>-2.8</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>17980</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-46.5</v>
+        <v>-1.4</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-72.90000000000001</v>
+        <v>-1.7</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-58.4</v>
+        <v>-5.3</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-49.4</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>쌈</t>
+        <v>6.8</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>비쌈</t>
         </is>
       </c>
     </row>
@@ -3267,33 +3845,38 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>호박(쥬키니)</t>
+          <t>오이(가시계통)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>10kg</t>
         </is>
       </c>
-      <c r="D21" s="3" t="n">
-        <v>9924</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>-4.4</v>
+      <c r="E21" s="3" t="n">
+        <v>12800</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-35.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-68.90000000000001</v>
+        <v>-31.9</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-56.2</v>
+        <v>-54.1</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-60.9</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
+        <v>-48.5</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>-53.3</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -3307,35 +3890,40 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>토마토</t>
+          <t>오이(다다기계통)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>5kg</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>28540</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>1.7</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>50개</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>21400</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.5</v>
+        <v>1.5</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>24</v>
+        <v>-23</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>32.5</v>
+        <v>-61.2</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>비쌈</t>
+        <v>-47.6</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>-39.1</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
         </is>
       </c>
     </row>
@@ -3347,35 +3935,40 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>무(고랭지)</t>
+          <t>오이(취청)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>20kg</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>21140</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>1.6</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>50개</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>16867</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.7</v>
+        <v>-0.8</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>16.4</v>
+        <v>-30</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>50.5</v>
+        <v>-67.90000000000001</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>비쌈</t>
+        <v>-57.2</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>-53.2</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
         </is>
       </c>
     </row>
@@ -3387,33 +3980,38 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>당근(무세척(국산))</t>
+          <t>호박(애호박)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>20kg</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>45280</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>1.3</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>20개</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>13140</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.3</v>
+        <v>-2.8</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>11.3</v>
+        <v>-46.5</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>10.7</v>
+        <v>-72.90000000000001</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-24.1</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+        <v>-58.4</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>-49.4</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -3427,33 +4025,38 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>열무</t>
+          <t>호박(쥬키니)</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>4kg</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>7416</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>0</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>10kg</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>9924</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-29.5</v>
+        <v>-4.4</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-45.2</v>
+        <v>-35.4</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-24.1</v>
+        <v>-68.90000000000001</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-17.7</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
+        <v>-56.2</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>-60.9</v>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -3467,35 +4070,40 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>건고추(화건)</t>
+          <t>토마토</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>30kg</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>673200</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>0</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>5kg</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>28540</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1</v>
+        <v>1.7</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.9</v>
+        <v>-2.5</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>보통</t>
+        <v>32.5</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>비쌈</t>
         </is>
       </c>
     </row>
@@ -3507,35 +4115,40 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>풋고추(풋고추(녹광 등))</t>
+          <t>무(고랭지)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>10kg</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>62433</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>-5.3</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>20kg</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>21140</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-18.1</v>
+        <v>1.6</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-11</v>
+        <v>-1.7</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-29.6</v>
+        <v>16.4</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>쌈</t>
+        <v>50.5</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>비쌈</t>
         </is>
       </c>
     </row>
@@ -3547,33 +4160,38 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>풋고추(꽈리고추)</t>
+          <t>당근(무세척(국산))</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>4kg</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>24560</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>-8</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>20kg</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>45280</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-42.8</v>
+        <v>1.3</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-15.5</v>
+        <v>2.3</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-41.6</v>
+        <v>11.3</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-38.5</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
+        <v>10.7</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>-24.1</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -3587,33 +4205,38 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>풋고추(청양고추)</t>
+          <t>당근(세척(수입))</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>중품</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
           <t>10kg</t>
         </is>
       </c>
-      <c r="D29" s="3" t="n">
-        <v>53100</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>-6.3</v>
+      <c r="E29" s="3" t="n">
+        <v>8366</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-6.9</v>
+        <v>0</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-10.9</v>
+        <v>0.8</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-12.6</v>
+        <v>1.7</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-14.6</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
+        <v>-1.3</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>-10.3</v>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -3627,33 +4250,38 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>풋고추(오이맛고추)</t>
+          <t>열무</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>10kg</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>54560</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>-4.7</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>4kg</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>7416</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-26.9</v>
+        <v>0</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>9.5</v>
+        <v>-29.5</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-23.9</v>
+        <v>-45.2</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
+        <v>-24.1</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>-17.7</v>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -3667,35 +4295,40 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>붉은고추</t>
+          <t>건고추(화건)</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>10kg</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>134060</v>
-      </c>
-      <c r="E31" s="4" t="n">
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>30kg</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>673200</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="I31" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F31" s="4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>124.3</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>매우 비쌈</t>
+      <c r="J31" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -3707,35 +4340,40 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>피마늘(한지)</t>
+          <t>풋고추(풋고추(녹광 등))</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>10kg</t>
         </is>
       </c>
-      <c r="D32" s="3" t="n">
-        <v>115000</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>0</v>
+      <c r="E32" s="3" t="n">
+        <v>62433</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0</v>
+        <v>-5.3</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>4.5</v>
+        <v>-18.1</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>16.6</v>
+        <v>-11</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>매우 비쌈</t>
+        <v>-29.6</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
         </is>
       </c>
     </row>
@@ -3747,35 +4385,40 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>피마늘(난지(대서))</t>
+          <t>풋고추(꽈리고추)</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>10kg</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>57560</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>0</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>4kg</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>24560</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0</v>
+        <v>-42.8</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>13.4</v>
+        <v>-15.5</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>보통</t>
+        <v>-41.6</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>-38.5</v>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
         </is>
       </c>
     </row>
@@ -3787,35 +4430,40 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>양파</t>
+          <t>풋고추(청양고추)</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>15kg</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>18980</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>0</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10kg</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>53100</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.6</v>
+        <v>-6.3</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.4</v>
+        <v>-6.9</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>3.7</v>
+        <v>-10.9</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>보통</t>
+        <v>-12.6</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>-14.6</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
         </is>
       </c>
     </row>
@@ -3827,33 +4475,38 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>파(대파)</t>
+          <t>풋고추(오이맛고추)</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>0.7</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10kg</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>54560</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-6.3</v>
+        <v>-4.7</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-9.699999999999999</v>
+        <v>-26.9</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-7.1</v>
+        <v>9.5</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-14.2</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
+        <v>-23.9</v>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -3867,35 +4520,40 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>파(쪽파)</t>
+          <t>붉은고추</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>7598</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>0</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10kg</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>134060</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>-9.199999999999999</v>
+        <v>2</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-23.2</v>
+        <v>0.8</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>9.4</v>
+        <v>124.3</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>보통</t>
+        <v>44.7</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>매우 비쌈</t>
         </is>
       </c>
     </row>
@@ -3907,35 +4565,40 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>생강(국산)</t>
+          <t>피마늘(한지)</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
           <t>10kg</t>
         </is>
       </c>
-      <c r="D37" s="3" t="n">
-        <v>65700</v>
-      </c>
-      <c r="E37" s="4" t="n">
+      <c r="E37" s="3" t="n">
+        <v>115000</v>
+      </c>
+      <c r="F37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F37" s="4" t="n">
-        <v>-0.8</v>
-      </c>
       <c r="G37" s="4" t="n">
-        <v>-2.2</v>
+        <v>0</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-17.6</v>
+        <v>4.5</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>보통</t>
+        <v>16.6</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>매우 비쌈</t>
         </is>
       </c>
     </row>
@@ -3947,29 +4610,42 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>가지</t>
+          <t>피마늘(난지(대서))</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>5kg</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>9432</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>-0.6</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10kg</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>57560</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>-47.5</v>
+        <v>0</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-38.6</v>
-      </c>
-      <c r="H38" s="4" t="n"/>
-      <c r="I38" s="4" t="n"/>
-      <c r="J38" s="2" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3979,33 +4655,38 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>미나리</t>
+          <t>양파</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>8kg</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>69500</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>-0.9</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>15kg</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>18980</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>-22.7</v>
+        <v>0</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-16.5</v>
+        <v>0.6</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>-28.3</v>
+        <v>1.4</v>
       </c>
       <c r="I39" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J39" s="4" t="n">
         <v>-3.8</v>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -4019,33 +4700,38 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>깻잎</t>
+          <t>파(대파)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2kg</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>26440</v>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>-8.1</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>1kg</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>2038</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>-44.2</v>
+        <v>0.7</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>-38.9</v>
+        <v>-6.3</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-36.5</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>-25.4</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
+        <v>-7.1</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>-14.2</v>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -4059,29 +4745,42 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>부추</t>
+          <t>파(쪽파)</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>4kg</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>16652</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>0.4</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>1kg</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>7598</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>-26.1</v>
+        <v>0</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>-10.8</v>
-      </c>
-      <c r="H41" s="4" t="n"/>
-      <c r="I41" s="4" t="n"/>
-      <c r="J41" s="2" t="n"/>
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>-23.2</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -4091,35 +4790,40 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>피망(청)</t>
+          <t>생강(국산)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
           <t>10kg</t>
         </is>
       </c>
-      <c r="D42" s="3" t="n">
-        <v>44480</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>-7.4</v>
+      <c r="E42" s="3" t="n">
+        <v>65700</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>-40.7</v>
+        <v>0</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>-20.7</v>
+        <v>-0.8</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>-9.1</v>
+        <v>-2.2</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>비쌈</t>
+        <v>-17.6</v>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -4131,35 +4835,40 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>파프리카</t>
+          <t>생강(수입)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>5kg</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>30380</v>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>-2.6</v>
+          <t>중품</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10kg</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>80533</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>-24.9</v>
+        <v>0</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>-41.5</v>
+        <v>-1.6</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>-26.9</v>
+        <v>-1.9</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>-16.5</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>쌈</t>
+        <v>-7.1</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>비쌈</t>
         </is>
       </c>
     </row>
@@ -4171,37 +4880,34 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>멜론</t>
+          <t>가지</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>8kg</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>29300</v>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>0</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>5kg</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>9432</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>-0.3</v>
+        <v>-0.6</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>9.4</v>
+        <v>-47.5</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="I44" s="4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+        <v>-38.6</v>
+      </c>
+      <c r="I44" s="4" t="n"/>
+      <c r="J44" s="4" t="n"/>
+      <c r="K44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -4211,35 +4917,40 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>깐마늘(국산)(깐마늘(대서))</t>
+          <t>미나리</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>20kg</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>168200</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>0</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>8kg</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>69500</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>-0.1</v>
+        <v>-0.9</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>-0.1</v>
+        <v>-22.7</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>10</v>
+        <v>-16.5</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>비쌈</t>
+        <v>-28.3</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -4251,35 +4962,40 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>깐마늘(국산)(깐마늘(남도))</t>
+          <t>깻잎</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>20kg</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>173000</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>0</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>2kg</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>26440</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0</v>
+        <v>-8.1</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>0</v>
+        <v>-44.2</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>7.5</v>
+        <v>-38.9</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>비쌈</t>
+        <v>-36.5</v>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>-25.4</v>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
         </is>
       </c>
     </row>
@@ -4291,37 +5007,34 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>알배기배추</t>
+          <t>부추</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>8kg</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>24300</v>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>-1.6</v>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>4kg</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>16652</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>-45.2</v>
+        <v>0.4</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>-37.6</v>
+        <v>-26.1</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>-24.4</v>
-      </c>
-      <c r="I47" s="4" t="n">
-        <v>-32.2</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>쌈</t>
-        </is>
-      </c>
+        <v>-10.8</v>
+      </c>
+      <c r="I47" s="4" t="n"/>
+      <c r="J47" s="4" t="n"/>
+      <c r="K47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -4331,35 +5044,40 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>브로콜리(브로콜리(국산))</t>
+          <t>피망(청)</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>8kg</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="n">
-        <v>34460</v>
-      </c>
-      <c r="E48" s="4" t="n">
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>10kg</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>44480</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>-40.7</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>-20.7</v>
+      </c>
+      <c r="I48" s="4" t="n">
         <v>-9.1</v>
       </c>
-      <c r="F48" s="4" t="n">
-        <v>-40.6</v>
-      </c>
-      <c r="G48" s="4" t="n">
-        <v>-44</v>
-      </c>
-      <c r="H48" s="4" t="n">
-        <v>-55.1</v>
-      </c>
-      <c r="I48" s="4" t="n">
-        <v>-30.5</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>쌈</t>
+      <c r="J48" s="4" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>비쌈</t>
         </is>
       </c>
     </row>
@@ -4371,33 +5089,308 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
+          <t>파프리카</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>5kg</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>30380</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>-24.9</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>-41.5</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>-26.9</v>
+      </c>
+      <c r="J49" s="4" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>채소류</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>멜론</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>8kg</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>29300</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="J50" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>채소류</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>깐마늘(국산)(깐마늘(대서))</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>20kg</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>168200</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J51" s="4" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>비쌈</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>채소류</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>깐마늘(국산)(깐마늘(남도))</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>20kg</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>173000</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J52" s="4" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>비쌈</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>채소류</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>알배기배추</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>8kg</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>24300</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>-45.2</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>-37.6</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>-24.4</v>
+      </c>
+      <c r="J53" s="4" t="n">
+        <v>-32.2</v>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>채소류</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>브로콜리(브로콜리(국산))</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>8kg</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>34460</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>-40.6</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>-44</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>-55.1</v>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>-30.5</v>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>채소류</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>방울토마토(대추방울토마토)</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>3kg</t>
         </is>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E55" s="3" t="n">
         <v>26040</v>
       </c>
-      <c r="E49" s="4" t="n">
+      <c r="F55" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="G55" s="4" t="n">
         <v>-10.5</v>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="H55" s="4" t="n">
         <v>29.2</v>
       </c>
-      <c r="H49" s="4" t="n">
+      <c r="I55" s="4" t="n">
         <v>34.9</v>
       </c>
-      <c r="I49" s="4" t="n">
+      <c r="J55" s="4" t="n">
         <v>21.9</v>
       </c>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t>매우 비쌈</t>
         </is>
@@ -47437,4 +48430,32 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>한국농수산식품유통공사(aT) KAMIS 농산물유통정보 일별 부류별 소매·도매 가격</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>가격 수준: 평년(최근 5년 중 최대·최소 제외 평균) 대비 등락률 기준</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/fruitbasket_prices.xlsx
+++ b/docs/fruitbasket_prices.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="최신_소매" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="최신_도매" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="최근이력" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="자료출처" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신_소매" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신_도매" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최근이력" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자료출처" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/docs/fruitbasket_prices.xlsx
+++ b/docs/fruitbasket_prices.xlsx
@@ -532,22 +532,22 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>20421</v>
+        <v>20175</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>-4.6</v>
+        <v>-1.2</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-4</v>
+        <v>-5.2</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-10.2</v>
+        <v>-11.3</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-26.3</v>
+        <v>-27.2</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>-21</v>
+        <v>-21.9</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -577,9 +577,11 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>22500</v>
-      </c>
-      <c r="F3" s="4" t="n"/>
+        <v>22208</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>-1.3</v>
+      </c>
       <c r="G3" s="4" t="n"/>
       <c r="H3" s="4" t="n"/>
       <c r="I3" s="4" t="n"/>
@@ -608,22 +610,22 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>26066</v>
+        <v>26193</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-2.3</v>
+        <v>-1.8</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-8.199999999999999</v>
+        <v>-7.7</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-15.3</v>
+        <v>-14.8</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-12.9</v>
+        <v>-12.5</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -653,22 +655,22 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7538</v>
+        <v>7560</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-2.7</v>
+        <v>-2.5</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>-14.3</v>
+        <v>-14.1</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -698,22 +700,22 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>19038</v>
+        <v>19000</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.6</v>
+        <v>-0.2</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0</v>
+        <v>-0.2</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-14.8</v>
+        <v>-15</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-20.6</v>
+        <v>-20.7</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -743,22 +745,22 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>10506</v>
+        <v>10343</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-12</v>
+        <v>-1.6</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-9.199999999999999</v>
+        <v>-10.6</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-21.8</v>
+        <v>-23</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-22.5</v>
+        <v>-23.7</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-47.9</v>
+        <v>-48.7</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -788,16 +790,18 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3397</v>
-      </c>
-      <c r="F8" s="4" t="n"/>
+        <v>3579</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>5.4</v>
+      </c>
       <c r="G8" s="4" t="n"/>
       <c r="H8" s="4" t="n">
-        <v>-54.3</v>
+        <v>-51.8</v>
       </c>
       <c r="I8" s="4" t="n"/>
       <c r="J8" s="4" t="n">
-        <v>-14.4</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -827,22 +831,22 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>6220</v>
+        <v>5958</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.3</v>
+        <v>-4.2</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-3.9</v>
+        <v>-8</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-16.3</v>
+        <v>-19.8</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-22.1</v>
+        <v>-25.4</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-17.3</v>
+        <v>-20.8</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -872,20 +876,18 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7349</v>
+        <v>7261</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>-7.7</v>
-      </c>
+        <v>-1.2</v>
+      </c>
+      <c r="G10" s="4" t="n"/>
       <c r="H10" s="4" t="n"/>
       <c r="I10" s="4" t="n">
-        <v>-21.3</v>
+        <v>-22.2</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-12.1</v>
+        <v>-13.1</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -918,7 +920,7 @@
         <v>327</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>-1.5</v>
@@ -963,7 +965,7 @@
         <v>7608</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>0.4</v>
@@ -1008,7 +1010,7 @@
         <v>12755</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>-0.9</v>
@@ -1050,22 +1052,22 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>8426</v>
+        <v>8451</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.2</v>
+        <v>-0.9</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-14.2</v>
+        <v>-14</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-13.8</v>
+        <v>-13.6</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1095,22 +1097,22 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>6205</v>
+        <v>6225</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.9</v>
+        <v>0.3</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-6.5</v>
+        <v>-6.2</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-19.9</v>
+        <v>-19.6</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2</v>
+        <v>-1.7</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1143,7 +1145,7 @@
         <v>11606</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>-0.1</v>
@@ -1177,22 +1179,22 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2051</v>
+        <v>2007</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.7</v>
+        <v>-2.1</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.5</v>
+        <v>-1.6</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2</v>
+        <v>-0.2</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.2</v>
+        <v>-3.3</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
@@ -1222,16 +1224,16 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>16116</v>
+        <v>16073</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3</v>
+        <v>-0.3</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>17.3</v>
+        <v>17</v>
       </c>
       <c r="I18" s="4" t="n"/>
       <c r="J18" s="4" t="n"/>
@@ -1259,22 +1261,22 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>5598</v>
+        <v>5557</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.5</v>
+        <v>-0.7</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-4</v>
+        <v>-4.7</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-3.4</v>
+        <v>-4.1</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-9.699999999999999</v>
+        <v>-10.3</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-10.7</v>
+        <v>-11.4</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
@@ -1304,22 +1306,22 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>4570</v>
+        <v>4694</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>13.9</v>
+        <v>16.9</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>46.3</v>
+        <v>50.3</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>19</v>
+        <v>22.2</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -1349,22 +1351,22 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>934</v>
+        <v>901</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-6.8</v>
+        <v>-3.5</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-10.7</v>
+        <v>-13.9</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-54.4</v>
+        <v>-56</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-38.2</v>
+        <v>-40.4</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-29.9</v>
+        <v>-32.4</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -1394,22 +1396,22 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-3.7</v>
+        <v>-0.4</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.7</v>
+        <v>-5.1</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-48.6</v>
+        <v>-48.8</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-41.4</v>
+        <v>-41.7</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-33</v>
+        <v>-33.3</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -1439,22 +1441,22 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-4.2</v>
+        <v>-0.2</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-5.2</v>
+        <v>-5.4</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-50.5</v>
+        <v>-50.6</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-44</v>
+        <v>-44.1</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-37.8</v>
+        <v>-38</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -1484,22 +1486,22 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>2159</v>
+        <v>2141</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.4</v>
+        <v>-0.8</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.4</v>
+        <v>-1.2</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-40.2</v>
+        <v>-40.7</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-36.4</v>
+        <v>-36.9</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-30.2</v>
+        <v>-30.8</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -1529,22 +1531,22 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>24625</v>
+        <v>24675</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-5.6</v>
+        <v>-5.4</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -1574,22 +1576,22 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>8222</v>
+        <v>7900</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-3.1</v>
+        <v>-3.9</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-5.1</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-31.9</v>
+        <v>-34.6</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-37.1</v>
+        <v>-39.5</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-35.9</v>
+        <v>-38.4</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -1619,22 +1621,22 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>6582</v>
+        <v>6461</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.7</v>
+        <v>-1.8</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.3</v>
+        <v>-1.6</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-47.6</v>
+        <v>-48.5</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-41.6</v>
+        <v>-42.6</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-40.1</v>
+        <v>-41.2</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -1664,22 +1666,22 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>8347</v>
+        <v>8294</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-10.9</v>
+        <v>-0.6</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-9.4</v>
+        <v>-10</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-47.2</v>
+        <v>-47.6</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-38.8</v>
+        <v>-39.2</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-36.6</v>
+        <v>-37</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -1709,22 +1711,22 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1101</v>
+        <v>1079</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-5.4</v>
+        <v>-7.3</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-55.5</v>
+        <v>-56.4</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-38.7</v>
+        <v>-39.9</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-32.4</v>
+        <v>-33.7</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -1754,22 +1756,22 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>1508</v>
+        <v>1487</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.3</v>
+        <v>-1.4</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-2.5</v>
+        <v>-3.8</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-35.4</v>
+        <v>-36.3</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-21.3</v>
+        <v>-22.3</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-30.6</v>
+        <v>-31.5</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
@@ -1799,22 +1801,22 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>6775</v>
+        <v>6702</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-6.5</v>
+        <v>-1.1</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-8.800000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>14.1</v>
+        <v>12.8</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-3.6</v>
+        <v>-4.7</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-21</v>
+        <v>-21.9</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
@@ -1844,22 +1846,22 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>2281</v>
+        <v>2262</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1.9</v>
+        <v>-0.8</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.5</v>
+        <v>-1.3</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-6.3</v>
+        <v>-7.1</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-19.1</v>
+        <v>-19.7</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -1889,22 +1891,22 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>4395</v>
+        <v>4404</v>
       </c>
       <c r="F33" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.6</v>
+        <v>-0.4</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-10.1</v>
+        <v>-9.9</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
@@ -1934,22 +1936,22 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1981</v>
+        <v>1964</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-2.9</v>
+        <v>-0.9</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-4.8</v>
+        <v>-5.6</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-42.7</v>
+        <v>-43.2</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-41.8</v>
+        <v>-42.3</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-35.6</v>
+        <v>-36.2</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -1979,16 +1981,16 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>17542</v>
+        <v>17535</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.3</v>
+        <v>-0</v>
       </c>
       <c r="G35" s="4" t="n">
         <v>-1</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="I35" s="4" t="n">
         <v>5.1</v>
@@ -2024,22 +2026,22 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1631</v>
+        <v>1627</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>-1.3</v>
+        <v>-0.2</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-2</v>
+        <v>-2.2</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-8.9</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>-18.2</v>
+        <v>-18.4</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>-2.9</v>
+        <v>-3.2</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -2069,13 +2071,13 @@
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>-1.6</v>
+        <v>0.1</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-2.7</v>
+        <v>-2.6</v>
       </c>
       <c r="H37" s="4" t="n">
         <v>3.8</v>
@@ -2084,7 +2086,7 @@
         <v>-17.3</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>-16.2</v>
+        <v>-16.1</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
@@ -2114,22 +2116,22 @@
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>-1</v>
+        <v>-0.2</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-2.2</v>
+        <v>-2.4</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-3.8</v>
+        <v>-4.1</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-7.4</v>
+        <v>-7.6</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>-3.4</v>
+        <v>-3.6</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -2159,22 +2161,22 @@
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1049</v>
+        <v>1028</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>-2.4</v>
+        <v>-2</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-7.3</v>
+        <v>-9.1</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>-11.4</v>
+        <v>-13.2</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>-13.3</v>
+        <v>-15</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>-13.2</v>
+        <v>-15</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -2204,22 +2206,22 @@
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>2604</v>
+        <v>2595</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>-1.3</v>
+        <v>-1.7</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>22.5</v>
+        <v>22.1</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>26.2</v>
+        <v>25.8</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>22.4</v>
+        <v>21.9</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -2249,22 +2251,22 @@
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>2252</v>
+        <v>2214</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>8.6</v>
+        <v>-1.7</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>-2.3</v>
+        <v>-3.9</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>1.1</v>
+        <v>-0.6</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -2294,22 +2296,22 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>2809</v>
+        <v>2774</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>-3.8</v>
+        <v>-1.2</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>-5.6</v>
+        <v>-6.8</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>-16.4</v>
+        <v>-17.4</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>-15.9</v>
+        <v>-16.9</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -2339,22 +2341,22 @@
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>5768</v>
+        <v>5889</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>-6.3</v>
+        <v>2.1</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>-7.5</v>
+        <v>-5.5</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>-42.1</v>
+        <v>-40.9</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>-39.1</v>
+        <v>-37.8</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>-36</v>
+        <v>-34.7</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -2384,22 +2386,22 @@
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>12441</v>
+        <v>12555</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>-2.3</v>
+        <v>0.9</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>-18</v>
+        <v>-17.2</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>-17</v>
+        <v>-16.2</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>-3.6</v>
+        <v>-2.7</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -2429,13 +2431,13 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>31700</v>
+        <v>31696</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>-6.3</v>
+        <v>-0</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>-6.3</v>
+        <v>-6.4</v>
       </c>
       <c r="H45" s="4" t="n">
         <v>-6.2</v>
@@ -2519,16 +2521,16 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>2220</v>
+        <v>2233</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>-2.9</v>
+        <v>0.6</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>-3.1</v>
+        <v>-2.5</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>-9.4</v>
+        <v>-8.9</v>
       </c>
       <c r="I47" s="4" t="n"/>
       <c r="J47" s="4" t="n"/>
@@ -2556,22 +2558,22 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1879</v>
+        <v>1863</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>-1.1</v>
+        <v>-0.9</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>-0.4</v>
+        <v>-1.3</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>-3.1</v>
+        <v>-3.9</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -2601,26 +2603,26 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>1405</v>
+        <v>1367</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1.8</v>
+        <v>-2.7</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>-1.3</v>
+        <v>-4</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>-24.7</v>
+        <v>-26.7</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>-12.9</v>
+        <v>-15.3</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>-3.2</v>
+        <v>-5.9</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쌈</t>
         </is>
       </c>
     </row>
@@ -2646,16 +2648,16 @@
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>7.4</v>
+        <v>1</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>-9.5</v>
+        <v>-8.6</v>
       </c>
       <c r="I50" s="4" t="n"/>
       <c r="J50" s="4" t="n"/>
@@ -2683,22 +2685,22 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>1537</v>
+        <v>1545</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>-3.3</v>
+        <v>-2.8</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>-21</v>
+        <v>-20.6</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>21.4</v>
+        <v>22</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -2728,22 +2730,22 @@
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>1582</v>
+        <v>1565</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>-2.2</v>
+        <v>-1.1</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>-7.1</v>
+        <v>-8.1</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>-37.6</v>
+        <v>-38.2</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>-24.5</v>
+        <v>-25.3</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>-22.5</v>
+        <v>-23.4</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -2773,16 +2775,16 @@
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>9678</v>
+        <v>9674</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0.6</v>
+        <v>-0</v>
       </c>
       <c r="G53" s="4" t="n">
         <v>1.3</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="I53" s="4" t="n">
         <v>-10.2</v>
@@ -2818,22 +2820,22 @@
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>10425</v>
+        <v>10150</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>-5</v>
+        <v>-2.6</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>-2.7</v>
+        <v>-5.2</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>-2.7</v>
+        <v>-5.2</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>-8.1</v>
+        <v>-10.5</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>-7.6</v>
+        <v>-10</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -2863,22 +2865,22 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>3274</v>
+        <v>3255</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>-15.5</v>
+        <v>-0.6</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>-20.3</v>
+        <v>-20.8</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>-28.5</v>
+        <v>-28.9</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>-28.4</v>
+        <v>-28.8</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>-33</v>
+        <v>-33.4</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -2908,22 +2910,22 @@
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>2993</v>
+        <v>2983</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>6.7</v>
+        <v>-0.3</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>-0.6</v>
+        <v>-0.9</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>-21.5</v>
+        <v>-21.8</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>-16.2</v>
+        <v>-16.4</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>-22.9</v>
+        <v>-23.1</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -2956,7 +2958,7 @@
         <v>9277</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>-5.8</v>
+        <v>0</v>
       </c>
       <c r="G57" s="4" t="n">
         <v>-6.6</v>
@@ -2998,22 +3000,22 @@
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>9342</v>
+        <v>8768</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>-1.1</v>
+        <v>-6.1</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>-2.2</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>6.2</v>
+        <v>-0.3</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>-6.1</v>
+        <v>-11.9</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>-15.2</v>
+        <v>-20.4</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -3032,7 +3034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3424,7 +3426,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>바나나(수입)</t>
+          <t>단감(부유)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -3434,30 +3436,26 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13kg</t>
+          <t>10kg</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>30960</v>
+        <v>45625</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="4" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>-4.5</v>
-      </c>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n"/>
       <c r="I9" s="4" t="n">
-        <v>-5.1</v>
+        <v>8.1</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-4</v>
+        <v>13.6</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>비쌈</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3467,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>파인애플(수입)</t>
+          <t>바나나(수입)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -3479,26 +3477,26 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12kg</t>
+          <t>13kg</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>39760</v>
+        <v>30960</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.3</v>
+        <v>-0.6</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2</v>
+        <v>-4.5</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-6.7</v>
+        <v>-5.1</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.4</v>
+        <v>-4</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -3514,7 +3512,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>오렌지(네이블 호주)</t>
+          <t>파인애플(수입)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -3524,30 +3522,30 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18kg</t>
+          <t>12kg</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>58725</v>
+        <v>39760</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-2.2</v>
+        <v>-0.2</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-12.3</v>
+        <v>-6.7</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-12.6</v>
+        <v>0.4</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>쌈</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3557,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>레몬(수입)</t>
+          <t>오렌지(네이블 호주)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -3569,26 +3567,26 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17kg</t>
+          <t>18kg</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>55980</v>
+        <v>58725</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-7.1</v>
+        <v>-2.2</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>10.1</v>
+        <v>-12.3</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-21.9</v>
+        <v>-12.6</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -3604,7 +3602,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>망고(수입)</t>
+          <t>레몬(수입)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -3614,30 +3612,30 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5kg</t>
+          <t>17kg</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>68375</v>
+        <v>55980</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-5.5</v>
+        <v>0.3</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-12.6</v>
+        <v>-7.1</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.3</v>
+        <v>10.1</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>16</v>
+        <v>-21.9</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>비쌈</t>
+          <t>쌈</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3647,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>키위(골드)</t>
+          <t>망고(수입)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -3659,34 +3657,42 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5.7kg</t>
+          <t>5kg</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>41860</v>
+        <v>68375</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>4</v>
+        <v>-5.5</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
-      <c r="K14" s="2" t="n"/>
+        <v>-12.6</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>비쌈</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>채소류</t>
+          <t>과일류</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>배추(여름(고랭지))</t>
+          <t>키위(골드)</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -3696,32 +3702,24 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10kg(그물망 3포기)</t>
+          <t>5.7kg</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>14600</v>
+        <v>41860</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-5.7</v>
+        <v>4</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-21.2</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>비쌈</t>
-        </is>
-      </c>
+        <v>3.7</v>
+      </c>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3731,7 +3729,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>양배추</t>
+          <t>배추(여름(고랭지))</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -3741,30 +3739,30 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8kg</t>
+          <t>10kg(그물망 3포기)</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>13400</v>
+        <v>14600</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>35.2</v>
+        <v>-5.7</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>119.9</v>
+        <v>-21.2</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>69.7</v>
+        <v>17.2</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>22.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>매우 비쌈</t>
+          <t>비쌈</t>
         </is>
       </c>
     </row>
@@ -3776,7 +3774,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>시금치</t>
+          <t>양배추</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -3786,30 +3784,30 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4kg</t>
+          <t>8kg</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>18120</v>
+        <v>13400</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.1</v>
+        <v>35.2</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-66.7</v>
+        <v>119.9</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-41.9</v>
+        <v>69.7</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-26.7</v>
+        <v>22.2</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>쌈</t>
+          <t>매우 비쌈</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3819,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>상추(적)</t>
+          <t>시금치</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -3835,22 +3833,22 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>16260</v>
+        <v>18120</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-4.6</v>
+        <v>-2.1</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-65.90000000000001</v>
+        <v>-66.7</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-63</v>
+        <v>-41.9</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-57.4</v>
+        <v>-26.7</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -3866,7 +3864,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>상추(청)</t>
+          <t>상추(적)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -3880,19 +3878,19 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>15075</v>
+        <v>16260</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.8</v>
+        <v>-4.6</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-69.59999999999999</v>
+        <v>-65.90000000000001</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-62.4</v>
+        <v>-63</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>-57.4</v>
@@ -3911,7 +3909,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>얼갈이배추</t>
+          <t>상추(청)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -3925,22 +3923,22 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>5598</v>
+        <v>15075</v>
       </c>
       <c r="F20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.6</v>
+        <v>-3.8</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-49.6</v>
+        <v>-69.59999999999999</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-31.7</v>
+        <v>-62.4</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-28</v>
+        <v>-57.4</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -3956,7 +3954,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>수박</t>
+          <t>얼갈이배추</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -3966,30 +3964,30 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1개</t>
+          <t>4kg</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>17220</v>
+        <v>5598</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-5.3</v>
+        <v>-49.6</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-11.5</v>
+        <v>-31.7</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.1</v>
+        <v>-28</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쌈</t>
         </is>
       </c>
     </row>
@@ -4001,7 +3999,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>오이(가시계통)</t>
+          <t>수박</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -4011,30 +4009,30 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>10kg</t>
+          <t>1개</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>14300</v>
+        <v>17220</v>
       </c>
       <c r="F22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-13.3</v>
+        <v>-0.5</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-47.9</v>
+        <v>-5.3</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-44.9</v>
+        <v>-11.5</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-50.2</v>
+        <v>2.1</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>쌈</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4044,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>오이(다다기계통)</t>
+          <t>오이(가시계통)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -4056,26 +4054,26 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>50개</t>
+          <t>10kg</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>19080</v>
+        <v>14300</v>
       </c>
       <c r="F23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-29.3</v>
+        <v>-13.3</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-55.3</v>
+        <v>-47.9</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-55.2</v>
+        <v>-44.9</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-49.6</v>
+        <v>-50.2</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -4091,7 +4089,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>오이(취청)</t>
+          <t>오이(다다기계통)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -4105,22 +4103,22 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>20833</v>
+        <v>19080</v>
       </c>
       <c r="F24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.8</v>
+        <v>-29.3</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-50.4</v>
+        <v>-55.3</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-34.4</v>
+        <v>-55.2</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-40.1</v>
+        <v>-49.6</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -4136,7 +4134,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>호박(애호박)</t>
+          <t>오이(취청)</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -4146,26 +4144,26 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>20개</t>
+          <t>50개</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>13380</v>
+        <v>20833</v>
       </c>
       <c r="F25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-2.2</v>
+        <v>-0.8</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-67.5</v>
+        <v>-50.4</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-48.2</v>
+        <v>-34.4</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-49</v>
+        <v>-40.1</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -4181,7 +4179,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>호박(쥬키니)</t>
+          <t>호박(애호박)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -4191,26 +4189,26 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>10kg</t>
+          <t>20개</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>7898</v>
+        <v>13380</v>
       </c>
       <c r="F26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-19.4</v>
+        <v>-2.2</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-79.8</v>
+        <v>-67.5</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-58.7</v>
+        <v>-48.2</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-68.59999999999999</v>
+        <v>-49</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -4226,7 +4224,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>토마토</t>
+          <t>호박(쥬키니)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -4236,26 +4234,26 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5kg</t>
+          <t>10kg</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>24340</v>
+        <v>7898</v>
       </c>
       <c r="F27" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-2.2</v>
+        <v>-19.4</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.7</v>
+        <v>-79.8</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>16.8</v>
+        <v>-58.7</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-13.6</v>
+        <v>-68.59999999999999</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -4271,7 +4269,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>무(고랭지)</t>
+          <t>토마토</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -4281,30 +4279,30 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>20kg</t>
+          <t>5kg</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>19580</v>
+        <v>24340</v>
       </c>
       <c r="F28" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-6</v>
+        <v>-2.2</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>13.9</v>
+        <v>2.7</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>26.5</v>
+        <v>16.8</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6.1</v>
+        <v>-13.6</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>비쌈</t>
+          <t>쌈</t>
         </is>
       </c>
     </row>
@@ -4316,7 +4314,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>당근(무세척(국산))</t>
+          <t>무(고랭지)</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -4330,26 +4328,26 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>46500</v>
+        <v>19580</v>
       </c>
       <c r="F29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>8.1</v>
+        <v>13.9</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>31.7</v>
+        <v>26.5</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-13.6</v>
+        <v>6.1</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>쌈</t>
+          <t>비쌈</t>
         </is>
       </c>
     </row>
@@ -4361,36 +4359,36 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>당근(세척(수입))</t>
+          <t>당근(무세척(국산))</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>중품</t>
+          <t>상품</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>10kg</t>
+          <t>20kg</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>8398</v>
+        <v>46500</v>
       </c>
       <c r="F30" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.4</v>
+        <v>8.1</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.8</v>
+        <v>31.7</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-10.8</v>
+        <v>-13.6</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
@@ -4406,36 +4404,36 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>열무</t>
+          <t>당근(세척(수입))</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>상품</t>
+          <t>중품</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>4kg</t>
+          <t>10kg</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>6332</v>
+        <v>8398</v>
       </c>
       <c r="F31" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-7.3</v>
+        <v>0</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-47.4</v>
+        <v>2.4</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-32.2</v>
+        <v>-0.8</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-34.2</v>
+        <v>-10.8</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
@@ -4451,7 +4449,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>건고추(화건)</t>
+          <t>열무</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -4461,30 +4459,30 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>30kg</t>
+          <t>4kg</t>
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>675800</v>
+        <v>6332</v>
       </c>
       <c r="F32" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.5</v>
+        <v>-7.3</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.6</v>
+        <v>-47.4</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.4</v>
+        <v>-32.2</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>2.1</v>
+        <v>-34.2</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쌈</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4494,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>풋고추(풋고추(녹광 등))</t>
+          <t>건고추(화건)</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -4506,30 +4504,30 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>10kg</t>
+          <t>30kg</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>58833</v>
+        <v>675800</v>
       </c>
       <c r="F33" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-3.7</v>
+        <v>0.5</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-29.8</v>
+        <v>-0.6</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-18.8</v>
+        <v>2.4</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-12.7</v>
+        <v>2.1</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>쌈</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4539,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>풋고추(꽈리고추)</t>
+          <t>풋고추(풋고추(녹광 등))</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -4551,26 +4549,26 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>4kg</t>
+          <t>10kg</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>29040</v>
+        <v>58833</v>
       </c>
       <c r="F34" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>11.1</v>
+        <v>-3.7</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-30.1</v>
+        <v>-29.8</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-10.3</v>
+        <v>-18.8</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-11.2</v>
+        <v>-12.7</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -4586,7 +4584,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>풋고추(청양고추)</t>
+          <t>풋고추(꽈리고추)</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -4596,26 +4594,26 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>10kg</t>
+          <t>4kg</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>44800</v>
+        <v>29040</v>
       </c>
       <c r="F35" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-6.6</v>
+        <v>11.1</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-17</v>
+        <v>-30.1</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-19.1</v>
+        <v>-10.3</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-26.6</v>
+        <v>-11.2</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
@@ -4631,7 +4629,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>풋고추(오이맛고추)</t>
+          <t>풋고추(청양고추)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -4645,22 +4643,22 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>37160</v>
+        <v>44800</v>
       </c>
       <c r="F36" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-19.5</v>
+        <v>-6.6</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-49</v>
+        <v>-17</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>-31.1</v>
+        <v>-19.1</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>-39.6</v>
+        <v>-26.6</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -4676,7 +4674,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>붉은고추</t>
+          <t>풋고추(오이맛고추)</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -4690,26 +4688,26 @@
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>93440</v>
+        <v>37160</v>
       </c>
       <c r="F37" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>4.5</v>
+        <v>-19.5</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-2.6</v>
+        <v>-49</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>26.1</v>
+        <v>-31.1</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>-1.4</v>
+        <v>-39.6</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쌈</t>
         </is>
       </c>
     </row>
@@ -4721,7 +4719,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>피마늘(한지)</t>
+          <t>붉은고추</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -4735,26 +4733,26 @@
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>116000</v>
+        <v>93440</v>
       </c>
       <c r="F38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>2.7</v>
+        <v>-2.6</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>16.6</v>
+        <v>26.1</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>35.5</v>
+        <v>-1.4</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>매우 비쌈</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4764,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>피마늘(난지(대서))</t>
+          <t>피마늘(한지)</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -4780,26 +4778,26 @@
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>57560</v>
+        <v>116000</v>
       </c>
       <c r="F39" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>13.4</v>
+        <v>16.6</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>4.3</v>
+        <v>35.5</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 비쌈</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4809,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>양파</t>
+          <t>피마늘(난지(대서))</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -4821,26 +4819,26 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>15kg</t>
+          <t>10kg</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>18700</v>
+        <v>57560</v>
       </c>
       <c r="F40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>1</v>
+        <v>13.4</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>-4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -4856,7 +4854,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>파(대파)</t>
+          <t>양파</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -4866,30 +4864,30 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>15kg</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1864</v>
+        <v>18700</v>
       </c>
       <c r="F41" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>-7.4</v>
+        <v>-0.1</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>-11.8</v>
+        <v>-0.3</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>-29.1</v>
+        <v>1</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>-22.7</v>
+        <v>-4.2</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>쌈</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4899,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>파(쪽파)</t>
+          <t>파(대파)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -4915,22 +4913,22 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>6396</v>
+        <v>1864</v>
       </c>
       <c r="F42" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>-13.2</v>
+        <v>-7.4</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>-30.8</v>
+        <v>-11.8</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>-6.7</v>
+        <v>-29.1</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>-14.5</v>
+        <v>-22.7</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -4946,7 +4944,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>생강(국산)</t>
+          <t>파(쪽파)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -4956,26 +4954,26 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>10kg</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>55640</v>
+        <v>6396</v>
       </c>
       <c r="F43" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>-3.7</v>
+        <v>-13.2</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>-17.1</v>
+        <v>-30.8</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>-25.9</v>
+        <v>-6.7</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>-16.2</v>
+        <v>-14.5</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -4991,12 +4989,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>생강(수입)</t>
+          <t>생강(국산)</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>중품</t>
+          <t>상품</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5005,26 +5003,26 @@
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>79533</v>
+        <v>55640</v>
       </c>
       <c r="F44" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>-0.4</v>
+        <v>-3.7</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>-3</v>
+        <v>-17.1</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>-6</v>
+        <v>-25.9</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>10.6</v>
+        <v>-16.2</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>비쌈</t>
+          <t>쌈</t>
         </is>
       </c>
     </row>
@@ -5036,34 +5034,42 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>가지</t>
+          <t>생강(수입)</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>상품</t>
+          <t>중품</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>5kg</t>
+          <t>10kg</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>12420</v>
+        <v>79533</v>
       </c>
       <c r="F45" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>-6.5</v>
+        <v>-0.4</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>-40.8</v>
-      </c>
-      <c r="I45" s="4" t="n"/>
-      <c r="J45" s="4" t="n"/>
-      <c r="K45" s="2" t="n"/>
+        <v>-3</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>비쌈</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -5073,7 +5079,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>미나리</t>
+          <t>가지</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -5083,32 +5089,24 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>8kg</t>
+          <t>5kg</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>58520</v>
+        <v>12420</v>
       </c>
       <c r="F46" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>-16.7</v>
+        <v>-6.5</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>-34.4</v>
-      </c>
-      <c r="I46" s="4" t="n">
-        <v>-27.5</v>
-      </c>
-      <c r="J46" s="4" t="n">
-        <v>-13.1</v>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>쌈</t>
-        </is>
-      </c>
+        <v>-40.8</v>
+      </c>
+      <c r="I46" s="4" t="n"/>
+      <c r="J46" s="4" t="n"/>
+      <c r="K46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -5118,7 +5116,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>깻잎</t>
+          <t>미나리</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -5128,26 +5126,26 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>2kg</t>
+          <t>8kg</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>26860</v>
+        <v>58520</v>
       </c>
       <c r="F47" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>4</v>
+        <v>-16.7</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>-50.5</v>
+        <v>-34.4</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>-24.5</v>
+        <v>-27.5</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>-16.5</v>
+        <v>-13.1</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
@@ -5163,7 +5161,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>부추</t>
+          <t>깻잎</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -5173,24 +5171,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>4kg</t>
+          <t>2kg</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>13652</v>
+        <v>26860</v>
       </c>
       <c r="F48" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>-2.7</v>
+        <v>4</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>-39.9</v>
-      </c>
-      <c r="I48" s="4" t="n"/>
-      <c r="J48" s="4" t="n"/>
-      <c r="K48" s="2" t="n"/>
+        <v>-50.5</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>-24.5</v>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -5200,7 +5206,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>피망(청)</t>
+          <t>부추</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -5210,32 +5216,24 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>10kg</t>
+          <t>4kg</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>40700</v>
+        <v>13652</v>
       </c>
       <c r="F49" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>10.8</v>
+        <v>-2.7</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>-54</v>
-      </c>
-      <c r="I49" s="4" t="n">
-        <v>-17.6</v>
-      </c>
-      <c r="J49" s="4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+        <v>-39.9</v>
+      </c>
+      <c r="I49" s="4" t="n"/>
+      <c r="J49" s="4" t="n"/>
+      <c r="K49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -5245,7 +5243,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>파프리카</t>
+          <t>피망(청)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -5255,30 +5253,30 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>5kg</t>
+          <t>10kg</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>24560</v>
+        <v>40700</v>
       </c>
       <c r="F50" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>8.6</v>
+        <v>10.8</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>-57</v>
+        <v>-54</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>-35.8</v>
+        <v>-17.6</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>-29.5</v>
+        <v>2.9</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>쌈</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5288,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>멜론</t>
+          <t>파프리카</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -5300,26 +5298,26 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>8kg</t>
+          <t>5kg</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>26680</v>
+        <v>24560</v>
       </c>
       <c r="F51" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>-3.6</v>
+        <v>8.6</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>-1.9</v>
+        <v>-57</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>-16.7</v>
+        <v>-35.8</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>-6.9</v>
+        <v>-29.5</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -5335,7 +5333,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>깐마늘(국산)(깐마늘(대서))</t>
+          <t>멜론</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -5345,30 +5343,30 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>20kg</t>
+          <t>8kg</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>170600</v>
+        <v>26680</v>
       </c>
       <c r="F52" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>1.4</v>
+        <v>-3.6</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>1.3</v>
+        <v>-1.9</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>11.3</v>
+        <v>-16.7</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>13.7</v>
+        <v>-6.9</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>비쌈</t>
+          <t>쌈</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5378,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>깐마늘(국산)(깐마늘(남도))</t>
+          <t>깐마늘(국산)(깐마늘(대서))</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -5394,22 +5392,22 @@
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>173000</v>
+        <v>170600</v>
       </c>
       <c r="F53" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>7.5</v>
+        <v>11.3</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>10.7</v>
+        <v>13.7</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -5425,7 +5423,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>알배기배추</t>
+          <t>깐마늘(국산)(깐마늘(남도))</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -5435,30 +5433,30 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>8kg</t>
+          <t>20kg</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>19700</v>
+        <v>173000</v>
       </c>
       <c r="F54" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>-4.8</v>
+        <v>0</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>-50.4</v>
+        <v>0</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>-23</v>
+        <v>7.5</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>-38.2</v>
+        <v>10.7</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>쌈</t>
+          <t>비쌈</t>
         </is>
       </c>
     </row>
@@ -5470,7 +5468,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>브로콜리(브로콜리(국산))</t>
+          <t>알배기배추</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -5484,22 +5482,22 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>33500</v>
+        <v>19700</v>
       </c>
       <c r="F55" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>-8.5</v>
+        <v>-4.8</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>-53.7</v>
+        <v>-50.4</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>-46.1</v>
+        <v>-23</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>-33.2</v>
+        <v>-38.2</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -5515,7 +5513,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>방울토마토(대추방울토마토)</t>
+          <t>브로콜리(브로콜리(국산))</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -5525,28 +5523,73 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>3kg</t>
+          <t>8kg</t>
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>21260</v>
+        <v>33500</v>
       </c>
       <c r="F56" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G56" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>-53.7</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>-46.1</v>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>-33.2</v>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>쌈</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>채소류</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>방울토마토(대추방울토마토)</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>3kg</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>21260</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="4" t="n">
         <v>-7.9</v>
       </c>
-      <c r="H56" s="4" t="n">
+      <c r="H57" s="4" t="n">
         <v>-12.7</v>
       </c>
-      <c r="I56" s="4" t="n">
+      <c r="I57" s="4" t="n">
         <v>14.6</v>
       </c>
-      <c r="J56" s="4" t="n">
+      <c r="J57" s="4" t="n">
         <v>-12.1</v>
       </c>
-      <c r="K56" s="2" t="inlineStr">
+      <c r="K57" s="2" t="inlineStr">
         <is>
           <t>쌈</t>
         </is>
@@ -5563,7 +5606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL226"/>
+  <dimension ref="A1:BM228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5885,6 +5928,11 @@
       <c r="BL1" s="5" t="inlineStr">
         <is>
           <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="BM1" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -5985,6 +6033,7 @@
       <c r="BJ2" s="6" t="n"/>
       <c r="BK2" s="6" t="n"/>
       <c r="BL2" s="6" t="n"/>
+      <c r="BM2" s="6" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6191,6 +6240,9 @@
       <c r="BL3" s="6" t="n">
         <v>5598</v>
       </c>
+      <c r="BM3" s="6" t="n">
+        <v>5557</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6397,6 +6449,9 @@
       <c r="BL4" s="6" t="n">
         <v>4570</v>
       </c>
+      <c r="BM4" s="6" t="n">
+        <v>4694</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6603,6 +6658,9 @@
       <c r="BL5" s="6" t="n">
         <v>3273</v>
       </c>
+      <c r="BM5" s="6" t="n">
+        <v>3262</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6809,6 +6867,9 @@
       <c r="BL6" s="6" t="n">
         <v>934</v>
       </c>
+      <c r="BM6" s="6" t="n">
+        <v>901</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7015,6 +7076,9 @@
       <c r="BL7" s="6" t="n">
         <v>987</v>
       </c>
+      <c r="BM7" s="6" t="n">
+        <v>983</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7221,6 +7285,9 @@
       <c r="BL8" s="6" t="n">
         <v>981</v>
       </c>
+      <c r="BM8" s="6" t="n">
+        <v>979</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7427,6 +7494,9 @@
       <c r="BL9" s="6" t="n">
         <v>2159</v>
       </c>
+      <c r="BM9" s="6" t="n">
+        <v>2141</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7633,6 +7703,9 @@
       <c r="BL10" s="6" t="n">
         <v>24625</v>
       </c>
+      <c r="BM10" s="6" t="n">
+        <v>24675</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7838,6 +7911,9 @@
       </c>
       <c r="BL11" s="6" t="n">
         <v>19432</v>
+      </c>
+      <c r="BM11" s="6" t="n">
+        <v>19545</v>
       </c>
     </row>
     <row r="12">
@@ -8023,6 +8099,7 @@
       <c r="BJ12" s="6" t="n"/>
       <c r="BK12" s="6" t="n"/>
       <c r="BL12" s="6" t="n"/>
+      <c r="BM12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8207,6 +8284,7 @@
       <c r="BJ13" s="6" t="n"/>
       <c r="BK13" s="6" t="n"/>
       <c r="BL13" s="6" t="n"/>
+      <c r="BM13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8413,6 +8491,9 @@
       <c r="BL14" s="6" t="n">
         <v>8222</v>
       </c>
+      <c r="BM14" s="6" t="n">
+        <v>7900</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8618,6 +8699,9 @@
       </c>
       <c r="BL15" s="6" t="n">
         <v>6582</v>
+      </c>
+      <c r="BM15" s="6" t="n">
+        <v>6461</v>
       </c>
     </row>
     <row r="16">
@@ -8817,6 +8901,9 @@
       <c r="BL16" s="6" t="n">
         <v>5300</v>
       </c>
+      <c r="BM16" s="6" t="n">
+        <v>5095</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9023,6 +9110,9 @@
       <c r="BL17" s="6" t="n">
         <v>8347</v>
       </c>
+      <c r="BM17" s="6" t="n">
+        <v>8294</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9229,6 +9319,9 @@
       <c r="BL18" s="6" t="n">
         <v>1101</v>
       </c>
+      <c r="BM18" s="6" t="n">
+        <v>1079</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9434,6 +9527,9 @@
       </c>
       <c r="BL19" s="6" t="n">
         <v>1508</v>
+      </c>
+      <c r="BM19" s="6" t="n">
+        <v>1487</v>
       </c>
     </row>
     <row r="20">
@@ -9529,6 +9625,7 @@
       <c r="BJ20" s="6" t="n"/>
       <c r="BK20" s="6" t="n"/>
       <c r="BL20" s="6" t="n"/>
+      <c r="BM20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9734,6 +9831,9 @@
       </c>
       <c r="BL21" s="6" t="n">
         <v>6775</v>
+      </c>
+      <c r="BM21" s="6" t="n">
+        <v>6702</v>
       </c>
     </row>
     <row r="22">
@@ -9849,6 +9949,7 @@
       <c r="BJ22" s="6" t="n"/>
       <c r="BK22" s="6" t="n"/>
       <c r="BL22" s="6" t="n"/>
+      <c r="BM22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9963,6 +10064,7 @@
       <c r="BJ23" s="6" t="n"/>
       <c r="BK23" s="6" t="n"/>
       <c r="BL23" s="6" t="n"/>
+      <c r="BM23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -10150,6 +10252,9 @@
       </c>
       <c r="BL24" s="6" t="n">
         <v>2281</v>
+      </c>
+      <c r="BM24" s="6" t="n">
+        <v>2262</v>
       </c>
     </row>
     <row r="25">
@@ -10333,6 +10438,9 @@
       <c r="BL25" s="6" t="n">
         <v>2032</v>
       </c>
+      <c r="BM25" s="6" t="n">
+        <v>2146</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -10538,6 +10646,9 @@
       </c>
       <c r="BL26" s="6" t="n">
         <v>4395</v>
+      </c>
+      <c r="BM26" s="6" t="n">
+        <v>4404</v>
       </c>
     </row>
     <row r="27">
@@ -10667,6 +10778,9 @@
       <c r="BL27" s="6" t="n">
         <v>3796</v>
       </c>
+      <c r="BM27" s="6" t="n">
+        <v>3796</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -10872,6 +10986,9 @@
       </c>
       <c r="BL28" s="6" t="n">
         <v>1981</v>
+      </c>
+      <c r="BM28" s="6" t="n">
+        <v>1964</v>
       </c>
     </row>
     <row r="29">
@@ -11068,6 +11185,9 @@
       </c>
       <c r="BL29" s="6" t="n">
         <v>17542</v>
+      </c>
+      <c r="BM29" s="6" t="n">
+        <v>17535</v>
       </c>
     </row>
     <row r="30">
@@ -11181,6 +11301,7 @@
       <c r="BJ30" s="6" t="n"/>
       <c r="BK30" s="6" t="n"/>
       <c r="BL30" s="6" t="n"/>
+      <c r="BM30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -11387,6 +11508,9 @@
       <c r="BL31" s="6" t="n">
         <v>1631</v>
       </c>
+      <c r="BM31" s="6" t="n">
+        <v>1627</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -11593,6 +11717,9 @@
       <c r="BL32" s="6" t="n">
         <v>1435</v>
       </c>
+      <c r="BM32" s="6" t="n">
+        <v>1436</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -11798,6 +11925,9 @@
       </c>
       <c r="BL33" s="6" t="n">
         <v>1257</v>
+      </c>
+      <c r="BM33" s="6" t="n">
+        <v>1254</v>
       </c>
     </row>
     <row r="34">
@@ -11919,6 +12049,9 @@
       <c r="BL34" s="6" t="n">
         <v>755</v>
       </c>
+      <c r="BM34" s="6" t="n">
+        <v>755</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -12125,6 +12258,9 @@
       <c r="BL35" s="6" t="n">
         <v>1049</v>
       </c>
+      <c r="BM35" s="6" t="n">
+        <v>1028</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -12331,6 +12467,9 @@
       <c r="BL36" s="6" t="n">
         <v>2604</v>
       </c>
+      <c r="BM36" s="6" t="n">
+        <v>2595</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -12537,6 +12676,9 @@
       <c r="BL37" s="6" t="n">
         <v>2252</v>
       </c>
+      <c r="BM37" s="6" t="n">
+        <v>2214</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -12743,6 +12885,9 @@
       <c r="BL38" s="6" t="n">
         <v>2809</v>
       </c>
+      <c r="BM38" s="6" t="n">
+        <v>2774</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -12949,6 +13094,9 @@
       <c r="BL39" s="6" t="n">
         <v>5768</v>
       </c>
+      <c r="BM39" s="6" t="n">
+        <v>5889</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -13155,6 +13303,9 @@
       <c r="BL40" s="6" t="n">
         <v>12441</v>
       </c>
+      <c r="BM40" s="6" t="n">
+        <v>12555</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -13361,6 +13512,9 @@
       <c r="BL41" s="6" t="n">
         <v>31700</v>
       </c>
+      <c r="BM41" s="6" t="n">
+        <v>31696</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -13565,6 +13719,9 @@
         <v>13544</v>
       </c>
       <c r="BL42" s="6" t="n">
+        <v>13544</v>
+      </c>
+      <c r="BM42" s="6" t="n">
         <v>13544</v>
       </c>
     </row>
@@ -13713,6 +13870,9 @@
       <c r="BL43" s="6" t="n">
         <v>2220</v>
       </c>
+      <c r="BM43" s="6" t="n">
+        <v>2233</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -13809,6 +13969,7 @@
       <c r="BJ44" s="6" t="n"/>
       <c r="BK44" s="6" t="n"/>
       <c r="BL44" s="6" t="n"/>
+      <c r="BM44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -14015,6 +14176,9 @@
       <c r="BL45" s="6" t="n">
         <v>1879</v>
       </c>
+      <c r="BM45" s="6" t="n">
+        <v>1863</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -14220,6 +14384,9 @@
       </c>
       <c r="BL46" s="6" t="n">
         <v>1405</v>
+      </c>
+      <c r="BM46" s="6" t="n">
+        <v>1367</v>
       </c>
     </row>
     <row r="47">
@@ -14367,6 +14534,9 @@
       <c r="BL47" s="6" t="n">
         <v>714</v>
       </c>
+      <c r="BM47" s="6" t="n">
+        <v>721</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -14573,6 +14743,9 @@
       <c r="BL48" s="6" t="n">
         <v>1537</v>
       </c>
+      <c r="BM48" s="6" t="n">
+        <v>1545</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -14778,6 +14951,9 @@
       </c>
       <c r="BL49" s="6" t="n">
         <v>1582</v>
+      </c>
+      <c r="BM49" s="6" t="n">
+        <v>1565</v>
       </c>
     </row>
     <row r="50">
@@ -14963,6 +15139,9 @@
       <c r="BL50" s="6" t="n">
         <v>1385</v>
       </c>
+      <c r="BM50" s="6" t="n">
+        <v>1347</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -15168,6 +15347,9 @@
       </c>
       <c r="BL51" s="6" t="n">
         <v>9678</v>
+      </c>
+      <c r="BM51" s="6" t="n">
+        <v>9674</v>
       </c>
     </row>
     <row r="52">
@@ -15345,6 +15527,7 @@
       <c r="BJ52" s="6" t="n"/>
       <c r="BK52" s="6" t="n"/>
       <c r="BL52" s="6" t="n"/>
+      <c r="BM52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -15551,6 +15734,9 @@
       <c r="BL53" s="6" t="n">
         <v>10425</v>
       </c>
+      <c r="BM53" s="6" t="n">
+        <v>10150</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -15757,6 +15943,9 @@
       <c r="BL54" s="6" t="n">
         <v>8670</v>
       </c>
+      <c r="BM54" s="6" t="n">
+        <v>8670</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -15962,6 +16151,9 @@
       </c>
       <c r="BL55" s="6" t="n">
         <v>3274</v>
+      </c>
+      <c r="BM55" s="6" t="n">
+        <v>3255</v>
       </c>
     </row>
     <row r="56">
@@ -16121,6 +16313,9 @@
       <c r="BL56" s="6" t="n">
         <v>2153</v>
       </c>
+      <c r="BM56" s="6" t="n">
+        <v>2090</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -16327,6 +16522,9 @@
       <c r="BL57" s="6" t="n">
         <v>2993</v>
       </c>
+      <c r="BM57" s="6" t="n">
+        <v>2983</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -16533,6 +16731,9 @@
       <c r="BL58" s="6" t="n">
         <v>9277</v>
       </c>
+      <c r="BM58" s="6" t="n">
+        <v>9277</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -16738,6 +16939,9 @@
       </c>
       <c r="BL59" s="6" t="n">
         <v>9342</v>
+      </c>
+      <c r="BM59" s="6" t="n">
+        <v>8768</v>
       </c>
     </row>
     <row r="60">
@@ -16887,6 +17091,7 @@
       <c r="BJ60" s="6" t="n"/>
       <c r="BK60" s="6" t="n"/>
       <c r="BL60" s="6" t="n"/>
+      <c r="BM60" s="6" t="n"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -17035,6 +17240,7 @@
       <c r="BJ61" s="6" t="n"/>
       <c r="BK61" s="6" t="n"/>
       <c r="BL61" s="6" t="n"/>
+      <c r="BM61" s="6" t="n"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -17195,6 +17401,7 @@
       <c r="BJ62" s="6" t="n"/>
       <c r="BK62" s="6" t="n"/>
       <c r="BL62" s="6" t="n"/>
+      <c r="BM62" s="6" t="n"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -17355,6 +17562,7 @@
       <c r="BJ63" s="6" t="n"/>
       <c r="BK63" s="6" t="n"/>
       <c r="BL63" s="6" t="n"/>
+      <c r="BM63" s="6" t="n"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -17519,6 +17727,9 @@
       <c r="BL64" s="6" t="n">
         <v>20421</v>
       </c>
+      <c r="BM64" s="6" t="n">
+        <v>20175</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -17682,6 +17893,9 @@
       </c>
       <c r="BL65" s="6" t="n">
         <v>14985</v>
+      </c>
+      <c r="BM65" s="6" t="n">
+        <v>14439</v>
       </c>
     </row>
     <row r="66">
@@ -17776,6 +17990,9 @@
       </c>
       <c r="BL66" s="6" t="n">
         <v>18829</v>
+      </c>
+      <c r="BM66" s="6" t="n">
+        <v>18717</v>
       </c>
     </row>
     <row r="67">
@@ -17869,6 +18086,9 @@
       <c r="BL67" s="6" t="n">
         <v>22500</v>
       </c>
+      <c r="BM67" s="6" t="n">
+        <v>22208</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -18056,6 +18276,9 @@
       </c>
       <c r="BL68" s="6" t="n">
         <v>26066</v>
+      </c>
+      <c r="BM68" s="6" t="n">
+        <v>26193</v>
       </c>
     </row>
     <row r="69">
@@ -18242,6 +18465,9 @@
       </c>
       <c r="BL69" s="6" t="n">
         <v>19484</v>
+      </c>
+      <c r="BM69" s="6" t="n">
+        <v>19329</v>
       </c>
     </row>
     <row r="70">
@@ -18399,6 +18625,7 @@
       <c r="BJ70" s="6" t="n"/>
       <c r="BK70" s="6" t="n"/>
       <c r="BL70" s="6" t="n"/>
+      <c r="BM70" s="6" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -18525,6 +18752,7 @@
       <c r="BJ71" s="6" t="n"/>
       <c r="BK71" s="6" t="n"/>
       <c r="BL71" s="6" t="n"/>
+      <c r="BM71" s="6" t="n"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -18709,6 +18937,7 @@
       <c r="BJ72" s="6" t="n"/>
       <c r="BK72" s="6" t="n"/>
       <c r="BL72" s="6" t="n"/>
+      <c r="BM72" s="6" t="n"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -18885,6 +19114,7 @@
       <c r="BJ73" s="6" t="n"/>
       <c r="BK73" s="6" t="n"/>
       <c r="BL73" s="6" t="n"/>
+      <c r="BM73" s="6" t="n"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -19090,6 +19320,9 @@
       </c>
       <c r="BL74" s="6" t="n">
         <v>7538</v>
+      </c>
+      <c r="BM74" s="6" t="n">
+        <v>7560</v>
       </c>
     </row>
     <row r="75">
@@ -19275,6 +19508,7 @@
       <c r="BJ75" s="6" t="n"/>
       <c r="BK75" s="6" t="n"/>
       <c r="BL75" s="6" t="n"/>
+      <c r="BM75" s="6" t="n"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -19481,6 +19715,9 @@
       <c r="BL76" s="6" t="n">
         <v>19038</v>
       </c>
+      <c r="BM76" s="6" t="n">
+        <v>19000</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -19686,6 +19923,9 @@
       </c>
       <c r="BL77" s="6" t="n">
         <v>10506</v>
+      </c>
+      <c r="BM77" s="6" t="n">
+        <v>10343</v>
       </c>
     </row>
     <row r="78">
@@ -19889,6 +20129,9 @@
       <c r="BL78" s="6" t="n">
         <v>6220</v>
       </c>
+      <c r="BM78" s="6" t="n">
+        <v>5958</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -20090,6 +20333,9 @@
       </c>
       <c r="BL79" s="6" t="n">
         <v>4644</v>
+      </c>
+      <c r="BM79" s="6" t="n">
+        <v>4448</v>
       </c>
     </row>
     <row r="80">
@@ -20183,6 +20429,9 @@
       <c r="BL80" s="6" t="n">
         <v>3397</v>
       </c>
+      <c r="BM80" s="6" t="n">
+        <v>3579</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -20275,6 +20524,9 @@
       <c r="BL81" s="6" t="n">
         <v>2693</v>
       </c>
+      <c r="BM81" s="6" t="n">
+        <v>2771</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -20371,6 +20623,9 @@
       <c r="BL82" s="6" t="n">
         <v>7349</v>
       </c>
+      <c r="BM82" s="6" t="n">
+        <v>7261</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -20467,6 +20722,9 @@
       <c r="BL83" s="6" t="n">
         <v>6071</v>
       </c>
+      <c r="BM83" s="6" t="n">
+        <v>5798</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -20673,6 +20931,9 @@
       <c r="BL84" s="6" t="n">
         <v>327</v>
       </c>
+      <c r="BM84" s="6" t="n">
+        <v>327</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -20877,6 +21138,9 @@
         <v>292</v>
       </c>
       <c r="BL85" s="6" t="n">
+        <v>291</v>
+      </c>
+      <c r="BM85" s="6" t="n">
         <v>291</v>
       </c>
     </row>
@@ -21029,6 +21293,7 @@
       <c r="BJ86" s="6" t="n"/>
       <c r="BK86" s="6" t="n"/>
       <c r="BL86" s="6" t="n"/>
+      <c r="BM86" s="6" t="n"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -21139,6 +21404,7 @@
       <c r="BJ87" s="6" t="n"/>
       <c r="BK87" s="6" t="n"/>
       <c r="BL87" s="6" t="n"/>
+      <c r="BM87" s="6" t="n"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -21345,6 +21611,9 @@
       <c r="BL88" s="6" t="n">
         <v>7608</v>
       </c>
+      <c r="BM88" s="6" t="n">
+        <v>7608</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -21551,6 +21820,9 @@
       <c r="BL89" s="6" t="n">
         <v>6181</v>
       </c>
+      <c r="BM89" s="6" t="n">
+        <v>6133</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -21755,6 +22027,9 @@
         <v>12952</v>
       </c>
       <c r="BL90" s="6" t="n">
+        <v>12755</v>
+      </c>
+      <c r="BM90" s="6" t="n">
         <v>12755</v>
       </c>
     </row>
@@ -21863,6 +22138,7 @@
         <v>17000</v>
       </c>
       <c r="BL91" s="6" t="n"/>
+      <c r="BM91" s="6" t="n"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -22069,6 +22345,9 @@
       <c r="BL92" s="6" t="n">
         <v>8426</v>
       </c>
+      <c r="BM92" s="6" t="n">
+        <v>8451</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -22273,6 +22552,9 @@
         <v>7060</v>
       </c>
       <c r="BL93" s="6" t="n">
+        <v>7521</v>
+      </c>
+      <c r="BM93" s="6" t="n">
         <v>7521</v>
       </c>
     </row>
@@ -22459,6 +22741,7 @@
       <c r="BJ94" s="6" t="n"/>
       <c r="BK94" s="6" t="n"/>
       <c r="BL94" s="6" t="n"/>
+      <c r="BM94" s="6" t="n"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -22662,6 +22945,9 @@
       </c>
       <c r="BL95" s="6" t="n">
         <v>6205</v>
+      </c>
+      <c r="BM95" s="6" t="n">
+        <v>6225</v>
       </c>
     </row>
     <row r="96">
@@ -22809,6 +23095,9 @@
       <c r="BL96" s="6" t="n">
         <v>11606</v>
       </c>
+      <c r="BM96" s="6" t="n">
+        <v>11606</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -23014,6 +23303,9 @@
       </c>
       <c r="BL97" s="6" t="n">
         <v>2051</v>
+      </c>
+      <c r="BM97" s="6" t="n">
+        <v>2007</v>
       </c>
     </row>
     <row r="98">
@@ -23161,6 +23453,9 @@
       <c r="BL98" s="6" t="n">
         <v>16116</v>
       </c>
+      <c r="BM98" s="6" t="n">
+        <v>16073</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -23307,6 +23602,9 @@
       <c r="BL99" s="6" t="n">
         <v>12421</v>
       </c>
+      <c r="BM99" s="6" t="n">
+        <v>12421</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -23513,6 +23811,9 @@
       <c r="BL100" s="6" t="n">
         <v>14600</v>
       </c>
+      <c r="BM100" s="6" t="n">
+        <v>14600</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -23719,6 +24020,9 @@
       <c r="BL101" s="6" t="n">
         <v>11240</v>
       </c>
+      <c r="BM101" s="6" t="n">
+        <v>11240</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -23925,6 +24229,9 @@
       <c r="BL102" s="6" t="n">
         <v>13400</v>
       </c>
+      <c r="BM102" s="6" t="n">
+        <v>13400</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -24131,6 +24438,9 @@
       <c r="BL103" s="6" t="n">
         <v>8726</v>
       </c>
+      <c r="BM103" s="6" t="n">
+        <v>8726</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -24337,6 +24647,9 @@
       <c r="BL104" s="6" t="n">
         <v>18120</v>
       </c>
+      <c r="BM104" s="6" t="n">
+        <v>18120</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -24543,6 +24856,9 @@
       <c r="BL105" s="6" t="n">
         <v>13150</v>
       </c>
+      <c r="BM105" s="6" t="n">
+        <v>13150</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -24749,6 +25065,9 @@
       <c r="BL106" s="6" t="n">
         <v>16260</v>
       </c>
+      <c r="BM106" s="6" t="n">
+        <v>16260</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -24955,6 +25274,9 @@
       <c r="BL107" s="6" t="n">
         <v>11300</v>
       </c>
+      <c r="BM107" s="6" t="n">
+        <v>11300</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -25161,6 +25483,9 @@
       <c r="BL108" s="6" t="n">
         <v>15075</v>
       </c>
+      <c r="BM108" s="6" t="n">
+        <v>15075</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -25367,6 +25692,9 @@
       <c r="BL109" s="6" t="n">
         <v>11200</v>
       </c>
+      <c r="BM109" s="6" t="n">
+        <v>11200</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -25573,6 +25901,9 @@
       <c r="BL110" s="6" t="n">
         <v>5598</v>
       </c>
+      <c r="BM110" s="6" t="n">
+        <v>5598</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -25779,6 +26110,9 @@
       <c r="BL111" s="6" t="n">
         <v>3998</v>
       </c>
+      <c r="BM111" s="6" t="n">
+        <v>3998</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -25985,6 +26319,9 @@
       <c r="BL112" s="6" t="n">
         <v>17220</v>
       </c>
+      <c r="BM112" s="6" t="n">
+        <v>17220</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -26189,6 +26526,9 @@
         <v>13380</v>
       </c>
       <c r="BL113" s="6" t="n">
+        <v>12940</v>
+      </c>
+      <c r="BM113" s="6" t="n">
         <v>12940</v>
       </c>
     </row>
@@ -26331,6 +26671,7 @@
       <c r="BJ114" s="6" t="n"/>
       <c r="BK114" s="6" t="n"/>
       <c r="BL114" s="6" t="n"/>
+      <c r="BM114" s="6" t="n"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -26471,6 +26812,7 @@
       <c r="BJ115" s="6" t="n"/>
       <c r="BK115" s="6" t="n"/>
       <c r="BL115" s="6" t="n"/>
+      <c r="BM115" s="6" t="n"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -26677,6 +27019,9 @@
       <c r="BL116" s="6" t="n">
         <v>14300</v>
       </c>
+      <c r="BM116" s="6" t="n">
+        <v>14300</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -26883,6 +27228,9 @@
       <c r="BL117" s="6" t="n">
         <v>10150</v>
       </c>
+      <c r="BM117" s="6" t="n">
+        <v>10150</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -27089,6 +27437,9 @@
       <c r="BL118" s="6" t="n">
         <v>19080</v>
       </c>
+      <c r="BM118" s="6" t="n">
+        <v>19080</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -27295,6 +27646,9 @@
       <c r="BL119" s="6" t="n">
         <v>12292</v>
       </c>
+      <c r="BM119" s="6" t="n">
+        <v>12292</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -27501,6 +27855,9 @@
       <c r="BL120" s="6" t="n">
         <v>20833</v>
       </c>
+      <c r="BM120" s="6" t="n">
+        <v>20833</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -27707,6 +28064,9 @@
       <c r="BL121" s="6" t="n">
         <v>12000</v>
       </c>
+      <c r="BM121" s="6" t="n">
+        <v>12000</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -27913,6 +28273,9 @@
       <c r="BL122" s="6" t="n">
         <v>13380</v>
       </c>
+      <c r="BM122" s="6" t="n">
+        <v>13380</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -28119,6 +28482,9 @@
       <c r="BL123" s="6" t="n">
         <v>9102</v>
       </c>
+      <c r="BM123" s="6" t="n">
+        <v>9102</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -28325,6 +28691,9 @@
       <c r="BL124" s="6" t="n">
         <v>7898</v>
       </c>
+      <c r="BM124" s="6" t="n">
+        <v>7898</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -28531,6 +28900,9 @@
       <c r="BL125" s="6" t="n">
         <v>5096</v>
       </c>
+      <c r="BM125" s="6" t="n">
+        <v>5096</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -28737,6 +29109,9 @@
       <c r="BL126" s="6" t="n">
         <v>24340</v>
       </c>
+      <c r="BM126" s="6" t="n">
+        <v>24340</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -28941,6 +29316,9 @@
         <v>19420</v>
       </c>
       <c r="BL127" s="6" t="n">
+        <v>19380</v>
+      </c>
+      <c r="BM127" s="6" t="n">
         <v>19380</v>
       </c>
     </row>
@@ -29045,6 +29423,7 @@
       <c r="BJ128" s="6" t="n"/>
       <c r="BK128" s="6" t="n"/>
       <c r="BL128" s="6" t="n"/>
+      <c r="BM128" s="6" t="n"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -29147,6 +29526,7 @@
       <c r="BJ129" s="6" t="n"/>
       <c r="BK129" s="6" t="n"/>
       <c r="BL129" s="6" t="n"/>
+      <c r="BM129" s="6" t="n"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -29347,6 +29727,9 @@
       <c r="BL130" s="6" t="n">
         <v>19580</v>
       </c>
+      <c r="BM130" s="6" t="n">
+        <v>19580</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -29547,6 +29930,9 @@
       <c r="BL131" s="6" t="n">
         <v>15040</v>
       </c>
+      <c r="BM131" s="6" t="n">
+        <v>15040</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -29753,6 +30139,9 @@
       <c r="BL132" s="6" t="n">
         <v>46500</v>
       </c>
+      <c r="BM132" s="6" t="n">
+        <v>46500</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -29959,6 +30348,9 @@
       <c r="BL133" s="6" t="n">
         <v>33380</v>
       </c>
+      <c r="BM133" s="6" t="n">
+        <v>33380</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -30165,6 +30557,9 @@
       <c r="BL134" s="6" t="n">
         <v>8398</v>
       </c>
+      <c r="BM134" s="6" t="n">
+        <v>8398</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -30371,6 +30766,9 @@
       <c r="BL135" s="6" t="n">
         <v>6332</v>
       </c>
+      <c r="BM135" s="6" t="n">
+        <v>6332</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -30575,6 +30973,9 @@
         <v>4866</v>
       </c>
       <c r="BL136" s="6" t="n">
+        <v>4600</v>
+      </c>
+      <c r="BM136" s="6" t="n">
         <v>4600</v>
       </c>
     </row>
@@ -30765,6 +31166,9 @@
       <c r="BL137" s="6" t="n">
         <v>675800</v>
       </c>
+      <c r="BM137" s="6" t="n">
+        <v>675800</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -30951,6 +31355,9 @@
         <v>633000</v>
       </c>
       <c r="BL138" s="6" t="n">
+        <v>633000</v>
+      </c>
+      <c r="BM138" s="6" t="n">
         <v>633000</v>
       </c>
     </row>
@@ -31065,6 +31472,7 @@
       <c r="BJ139" s="6" t="n"/>
       <c r="BK139" s="6" t="n"/>
       <c r="BL139" s="6" t="n"/>
+      <c r="BM139" s="6" t="n"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -31177,6 +31585,7 @@
       <c r="BJ140" s="6" t="n"/>
       <c r="BK140" s="6" t="n"/>
       <c r="BL140" s="6" t="n"/>
+      <c r="BM140" s="6" t="n"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -31383,6 +31792,9 @@
       <c r="BL141" s="6" t="n">
         <v>58833</v>
       </c>
+      <c r="BM141" s="6" t="n">
+        <v>58833</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -31589,6 +32001,9 @@
       <c r="BL142" s="6" t="n">
         <v>26667</v>
       </c>
+      <c r="BM142" s="6" t="n">
+        <v>26667</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -31795,6 +32210,9 @@
       <c r="BL143" s="6" t="n">
         <v>29040</v>
       </c>
+      <c r="BM143" s="6" t="n">
+        <v>29040</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -32001,6 +32419,9 @@
       <c r="BL144" s="6" t="n">
         <v>19220</v>
       </c>
+      <c r="BM144" s="6" t="n">
+        <v>19220</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -32207,6 +32628,9 @@
       <c r="BL145" s="6" t="n">
         <v>44800</v>
       </c>
+      <c r="BM145" s="6" t="n">
+        <v>44800</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -32413,6 +32837,9 @@
       <c r="BL146" s="6" t="n">
         <v>29220</v>
       </c>
+      <c r="BM146" s="6" t="n">
+        <v>29220</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -32619,6 +33046,9 @@
       <c r="BL147" s="6" t="n">
         <v>37160</v>
       </c>
+      <c r="BM147" s="6" t="n">
+        <v>37160</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -32825,6 +33255,9 @@
       <c r="BL148" s="6" t="n">
         <v>23520</v>
       </c>
+      <c r="BM148" s="6" t="n">
+        <v>23520</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -33031,6 +33464,9 @@
       <c r="BL149" s="6" t="n">
         <v>93440</v>
       </c>
+      <c r="BM149" s="6" t="n">
+        <v>93440</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -33237,6 +33673,9 @@
       <c r="BL150" s="6" t="n">
         <v>51380</v>
       </c>
+      <c r="BM150" s="6" t="n">
+        <v>51380</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -33443,6 +33882,9 @@
       <c r="BL151" s="6" t="n">
         <v>116000</v>
       </c>
+      <c r="BM151" s="6" t="n">
+        <v>116000</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -33649,6 +34091,9 @@
       <c r="BL152" s="6" t="n">
         <v>80000</v>
       </c>
+      <c r="BM152" s="6" t="n">
+        <v>80000</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -33855,6 +34300,9 @@
       <c r="BL153" s="6" t="n">
         <v>57560</v>
       </c>
+      <c r="BM153" s="6" t="n">
+        <v>57560</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -34061,6 +34509,9 @@
       <c r="BL154" s="6" t="n">
         <v>44000</v>
       </c>
+      <c r="BM154" s="6" t="n">
+        <v>44000</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -34267,6 +34718,9 @@
       <c r="BL155" s="6" t="n">
         <v>18700</v>
       </c>
+      <c r="BM155" s="6" t="n">
+        <v>18700</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -34473,6 +34927,9 @@
       <c r="BL156" s="6" t="n">
         <v>14560</v>
       </c>
+      <c r="BM156" s="6" t="n">
+        <v>14560</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -34679,6 +35136,9 @@
       <c r="BL157" s="6" t="n">
         <v>1864</v>
       </c>
+      <c r="BM157" s="6" t="n">
+        <v>1864</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -34885,6 +35345,9 @@
       <c r="BL158" s="6" t="n">
         <v>1564</v>
       </c>
+      <c r="BM158" s="6" t="n">
+        <v>1564</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -35091,6 +35554,9 @@
       <c r="BL159" s="6" t="n">
         <v>6396</v>
       </c>
+      <c r="BM159" s="6" t="n">
+        <v>6396</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -35297,6 +35763,9 @@
       <c r="BL160" s="6" t="n">
         <v>4768</v>
       </c>
+      <c r="BM160" s="6" t="n">
+        <v>4768</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -35503,6 +35972,9 @@
       <c r="BL161" s="6" t="n">
         <v>55640</v>
       </c>
+      <c r="BM161" s="6" t="n">
+        <v>55640</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -35709,6 +36181,9 @@
       <c r="BL162" s="6" t="n">
         <v>47475</v>
       </c>
+      <c r="BM162" s="6" t="n">
+        <v>47475</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -35913,6 +36388,9 @@
         <v>79867</v>
       </c>
       <c r="BL163" s="6" t="n">
+        <v>79533</v>
+      </c>
+      <c r="BM163" s="6" t="n">
         <v>79533</v>
       </c>
     </row>
@@ -36061,6 +36539,9 @@
       <c r="BL164" s="6" t="n">
         <v>12420</v>
       </c>
+      <c r="BM164" s="6" t="n">
+        <v>12420</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -36207,6 +36688,9 @@
       <c r="BL165" s="6" t="n">
         <v>7450</v>
       </c>
+      <c r="BM165" s="6" t="n">
+        <v>7450</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -36413,6 +36897,9 @@
       <c r="BL166" s="6" t="n">
         <v>58520</v>
       </c>
+      <c r="BM166" s="6" t="n">
+        <v>58520</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -36619,6 +37106,9 @@
       <c r="BL167" s="6" t="n">
         <v>43500</v>
       </c>
+      <c r="BM167" s="6" t="n">
+        <v>43500</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -36825,6 +37315,9 @@
       <c r="BL168" s="6" t="n">
         <v>26860</v>
       </c>
+      <c r="BM168" s="6" t="n">
+        <v>26860</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -37029,6 +37522,9 @@
         <v>19150</v>
       </c>
       <c r="BL169" s="6" t="n">
+        <v>19625</v>
+      </c>
+      <c r="BM169" s="6" t="n">
         <v>19625</v>
       </c>
     </row>
@@ -37177,6 +37673,9 @@
       <c r="BL170" s="6" t="n">
         <v>13652</v>
       </c>
+      <c r="BM170" s="6" t="n">
+        <v>13652</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -37383,6 +37882,9 @@
       <c r="BL171" s="6" t="n">
         <v>40700</v>
       </c>
+      <c r="BM171" s="6" t="n">
+        <v>40700</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -37589,6 +38091,9 @@
       <c r="BL172" s="6" t="n">
         <v>24120</v>
       </c>
+      <c r="BM172" s="6" t="n">
+        <v>24120</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -37795,6 +38300,9 @@
       <c r="BL173" s="6" t="n">
         <v>24560</v>
       </c>
+      <c r="BM173" s="6" t="n">
+        <v>24560</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -38001,6 +38509,9 @@
       <c r="BL174" s="6" t="n">
         <v>17960</v>
       </c>
+      <c r="BM174" s="6" t="n">
+        <v>17960</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -38207,6 +38718,9 @@
       <c r="BL175" s="6" t="n">
         <v>26680</v>
       </c>
+      <c r="BM175" s="6" t="n">
+        <v>26680</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -38413,6 +38927,9 @@
       <c r="BL176" s="6" t="n">
         <v>21980</v>
       </c>
+      <c r="BM176" s="6" t="n">
+        <v>21980</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -38619,6 +39136,9 @@
       <c r="BL177" s="6" t="n">
         <v>170600</v>
       </c>
+      <c r="BM177" s="6" t="n">
+        <v>170600</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -38825,6 +39345,9 @@
       <c r="BL178" s="6" t="n">
         <v>144400</v>
       </c>
+      <c r="BM178" s="6" t="n">
+        <v>144400</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -39031,6 +39554,9 @@
       <c r="BL179" s="6" t="n">
         <v>173000</v>
       </c>
+      <c r="BM179" s="6" t="n">
+        <v>173000</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -39237,6 +39763,9 @@
       <c r="BL180" s="6" t="n">
         <v>155000</v>
       </c>
+      <c r="BM180" s="6" t="n">
+        <v>155000</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -39443,6 +39972,9 @@
       <c r="BL181" s="6" t="n">
         <v>19700</v>
       </c>
+      <c r="BM181" s="6" t="n">
+        <v>19700</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -39649,6 +40181,9 @@
       <c r="BL182" s="6" t="n">
         <v>14040</v>
       </c>
+      <c r="BM182" s="6" t="n">
+        <v>14040</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -39855,6 +40390,9 @@
       <c r="BL183" s="6" t="n">
         <v>33500</v>
       </c>
+      <c r="BM183" s="6" t="n">
+        <v>33500</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -40061,6 +40599,9 @@
       <c r="BL184" s="6" t="n">
         <v>24040</v>
       </c>
+      <c r="BM184" s="6" t="n">
+        <v>24040</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -40267,6 +40808,9 @@
       <c r="BL185" s="6" t="n">
         <v>21260</v>
       </c>
+      <c r="BM185" s="6" t="n">
+        <v>21260</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -40471,6 +41015,9 @@
         <v>17300</v>
       </c>
       <c r="BL186" s="6" t="n">
+        <v>17140</v>
+      </c>
+      <c r="BM186" s="6" t="n">
         <v>17140</v>
       </c>
     </row>
@@ -40605,6 +41152,7 @@
       <c r="BJ187" s="6" t="n"/>
       <c r="BK187" s="6" t="n"/>
       <c r="BL187" s="6" t="n"/>
+      <c r="BM187" s="6" t="n"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -40737,6 +41285,7 @@
       <c r="BJ188" s="6" t="n"/>
       <c r="BK188" s="6" t="n"/>
       <c r="BL188" s="6" t="n"/>
+      <c r="BM188" s="6" t="n"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -40889,6 +41438,7 @@
       <c r="BJ189" s="6" t="n"/>
       <c r="BK189" s="6" t="n"/>
       <c r="BL189" s="6" t="n"/>
+      <c r="BM189" s="6" t="n"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -41041,6 +41591,7 @@
       <c r="BJ190" s="6" t="n"/>
       <c r="BK190" s="6" t="n"/>
       <c r="BL190" s="6" t="n"/>
+      <c r="BM190" s="6" t="n"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -41215,6 +41766,9 @@
         <v>43525</v>
       </c>
       <c r="BL191" s="6" t="n">
+        <v>43167</v>
+      </c>
+      <c r="BM191" s="6" t="n">
         <v>43167</v>
       </c>
     </row>
@@ -41385,6 +41939,9 @@
         <v>37250</v>
       </c>
       <c r="BL192" s="6" t="n">
+        <v>38833</v>
+      </c>
+      <c r="BM192" s="6" t="n">
         <v>38833</v>
       </c>
     </row>
@@ -41479,6 +42036,7 @@
       <c r="BJ193" s="6" t="n"/>
       <c r="BK193" s="6" t="n"/>
       <c r="BL193" s="6" t="n"/>
+      <c r="BM193" s="6" t="n"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -41571,6 +42129,7 @@
       <c r="BJ194" s="6" t="n"/>
       <c r="BK194" s="6" t="n"/>
       <c r="BL194" s="6" t="n"/>
+      <c r="BM194" s="6" t="n"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -41737,6 +42296,9 @@
       <c r="BL195" s="6" t="n">
         <v>50860</v>
       </c>
+      <c r="BM195" s="6" t="n">
+        <v>50860</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -41903,6 +42465,9 @@
       <c r="BL196" s="6" t="n">
         <v>42960</v>
       </c>
+      <c r="BM196" s="6" t="n">
+        <v>42960</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -42057,6 +42622,7 @@
       <c r="BJ197" s="6" t="n"/>
       <c r="BK197" s="6" t="n"/>
       <c r="BL197" s="6" t="n"/>
+      <c r="BM197" s="6" t="n"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -42211,6 +42777,7 @@
       <c r="BJ198" s="6" t="n"/>
       <c r="BK198" s="6" t="n"/>
       <c r="BL198" s="6" t="n"/>
+      <c r="BM198" s="6" t="n"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -42367,6 +42934,7 @@
       <c r="BJ199" s="6" t="n"/>
       <c r="BK199" s="6" t="n"/>
       <c r="BL199" s="6" t="n"/>
+      <c r="BM199" s="6" t="n"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -42523,6 +43091,7 @@
       <c r="BJ200" s="6" t="n"/>
       <c r="BK200" s="6" t="n"/>
       <c r="BL200" s="6" t="n"/>
+      <c r="BM200" s="6" t="n"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -42729,6 +43298,9 @@
       <c r="BL201" s="6" t="n">
         <v>18225</v>
       </c>
+      <c r="BM201" s="6" t="n">
+        <v>18225</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -42935,6 +43507,9 @@
       <c r="BL202" s="6" t="n">
         <v>14500</v>
       </c>
+      <c r="BM202" s="6" t="n">
+        <v>14500</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -43141,6 +43716,9 @@
       <c r="BL203" s="6" t="n">
         <v>13475</v>
       </c>
+      <c r="BM203" s="6" t="n">
+        <v>13475</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -43347,6 +43925,9 @@
       <c r="BL204" s="6" t="n">
         <v>11125</v>
       </c>
+      <c r="BM204" s="6" t="n">
+        <v>11125</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -43553,6 +44134,9 @@
       <c r="BL205" s="6" t="n">
         <v>9492</v>
       </c>
+      <c r="BM205" s="6" t="n">
+        <v>9492</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -43757,6 +44341,9 @@
         <v>7632</v>
       </c>
       <c r="BL206" s="6" t="n">
+        <v>7364</v>
+      </c>
+      <c r="BM206" s="6" t="n">
         <v>7364</v>
       </c>
     </row>
@@ -43961,6 +44548,9 @@
       <c r="BL207" s="6" t="n">
         <v>18975</v>
       </c>
+      <c r="BM207" s="6" t="n">
+        <v>18975</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -44161,6 +44751,9 @@
         <v>16112</v>
       </c>
       <c r="BL208" s="6" t="n">
+        <v>15725</v>
+      </c>
+      <c r="BM208" s="6" t="n">
         <v>15725</v>
       </c>
     </row>
@@ -44257,6 +44850,9 @@
       <c r="BL209" s="6" t="n">
         <v>16880</v>
       </c>
+      <c r="BM209" s="6" t="n">
+        <v>16880</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -44351,6 +44947,9 @@
       <c r="BL210" s="6" t="n">
         <v>13800</v>
       </c>
+      <c r="BM210" s="6" t="n">
+        <v>13800</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -44365,12 +44964,12 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>바나나</t>
+          <t>단감</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>수입(13kg)</t>
+          <t>부유(10kg)</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -44380,182 +44979,69 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>13kg</t>
-        </is>
-      </c>
-      <c r="G211" s="6" t="n">
-        <v>28920</v>
-      </c>
-      <c r="H211" s="6" t="n">
-        <v>28020</v>
-      </c>
-      <c r="I211" s="6" t="n">
-        <v>27900</v>
-      </c>
-      <c r="J211" s="6" t="n">
-        <v>27900</v>
-      </c>
-      <c r="K211" s="6" t="n">
-        <v>27900</v>
-      </c>
-      <c r="L211" s="6" t="n">
-        <v>27900</v>
-      </c>
-      <c r="M211" s="6" t="n">
-        <v>27760</v>
-      </c>
-      <c r="N211" s="6" t="n">
-        <v>27760</v>
-      </c>
-      <c r="O211" s="6" t="n">
-        <v>27620</v>
-      </c>
-      <c r="P211" s="6" t="n">
-        <v>27620</v>
-      </c>
-      <c r="Q211" s="6" t="n">
-        <v>27620</v>
-      </c>
-      <c r="R211" s="6" t="n">
-        <v>27620</v>
-      </c>
-      <c r="S211" s="6" t="n">
-        <v>28020</v>
-      </c>
-      <c r="T211" s="6" t="n">
-        <v>27820</v>
-      </c>
-      <c r="U211" s="6" t="n">
-        <v>27820</v>
-      </c>
-      <c r="V211" s="6" t="n">
-        <v>27940</v>
-      </c>
-      <c r="W211" s="6" t="n">
-        <v>28140</v>
-      </c>
-      <c r="X211" s="6" t="n">
-        <v>28140</v>
-      </c>
-      <c r="Y211" s="6" t="n">
-        <v>28140</v>
-      </c>
-      <c r="Z211" s="6" t="n">
-        <v>28480</v>
-      </c>
-      <c r="AA211" s="6" t="n">
-        <v>28660</v>
-      </c>
-      <c r="AB211" s="6" t="n">
-        <v>29140</v>
-      </c>
-      <c r="AC211" s="6" t="n">
-        <v>29540</v>
-      </c>
-      <c r="AD211" s="6" t="n">
-        <v>29540</v>
-      </c>
-      <c r="AE211" s="6" t="n">
-        <v>29860</v>
-      </c>
-      <c r="AF211" s="6" t="n">
-        <v>30120</v>
-      </c>
-      <c r="AG211" s="6" t="n">
-        <v>30320</v>
-      </c>
-      <c r="AH211" s="6" t="n">
-        <v>30240</v>
-      </c>
-      <c r="AI211" s="6" t="n">
-        <v>30080</v>
-      </c>
-      <c r="AJ211" s="6" t="n">
-        <v>30280</v>
-      </c>
-      <c r="AK211" s="6" t="n">
-        <v>30620</v>
-      </c>
-      <c r="AL211" s="6" t="n">
-        <v>30620</v>
-      </c>
-      <c r="AM211" s="6" t="n">
-        <v>30820</v>
-      </c>
-      <c r="AN211" s="6" t="n">
-        <v>30820</v>
-      </c>
-      <c r="AO211" s="6" t="n">
-        <v>31560</v>
-      </c>
-      <c r="AP211" s="6" t="n">
-        <v>31960</v>
-      </c>
-      <c r="AQ211" s="6" t="n">
-        <v>32160</v>
-      </c>
-      <c r="AR211" s="6" t="n">
-        <v>32160</v>
-      </c>
-      <c r="AS211" s="6" t="n">
-        <v>32100</v>
-      </c>
-      <c r="AT211" s="6" t="n">
-        <v>32300</v>
-      </c>
-      <c r="AU211" s="6" t="n">
-        <v>32300</v>
-      </c>
-      <c r="AV211" s="6" t="n">
-        <v>32300</v>
-      </c>
-      <c r="AW211" s="6" t="n">
-        <v>32760</v>
-      </c>
-      <c r="AX211" s="6" t="n">
-        <v>32760</v>
-      </c>
-      <c r="AY211" s="6" t="n">
-        <v>32760</v>
-      </c>
-      <c r="AZ211" s="6" t="n">
-        <v>32760</v>
-      </c>
-      <c r="BA211" s="6" t="n">
-        <v>32760</v>
-      </c>
-      <c r="BB211" s="6" t="n">
-        <v>32760</v>
-      </c>
-      <c r="BC211" s="6" t="n">
-        <v>32140</v>
-      </c>
-      <c r="BD211" s="6" t="n">
-        <v>32140</v>
-      </c>
-      <c r="BE211" s="6" t="n">
-        <v>31940</v>
-      </c>
-      <c r="BF211" s="6" t="n">
-        <v>31940</v>
-      </c>
-      <c r="BG211" s="6" t="n">
-        <v>31360</v>
-      </c>
-      <c r="BH211" s="6" t="n">
-        <v>31140</v>
-      </c>
-      <c r="BI211" s="6" t="n">
-        <v>31140</v>
-      </c>
-      <c r="BJ211" s="6" t="n">
-        <v>31060</v>
-      </c>
-      <c r="BK211" s="6" t="n">
-        <v>30960</v>
-      </c>
-      <c r="BL211" s="6" t="n">
-        <v>30960</v>
+          <t>10kg</t>
+        </is>
+      </c>
+      <c r="G211" s="6" t="n"/>
+      <c r="H211" s="6" t="n"/>
+      <c r="I211" s="6" t="n"/>
+      <c r="J211" s="6" t="n"/>
+      <c r="K211" s="6" t="n"/>
+      <c r="L211" s="6" t="n"/>
+      <c r="M211" s="6" t="n"/>
+      <c r="N211" s="6" t="n"/>
+      <c r="O211" s="6" t="n"/>
+      <c r="P211" s="6" t="n"/>
+      <c r="Q211" s="6" t="n"/>
+      <c r="R211" s="6" t="n"/>
+      <c r="S211" s="6" t="n"/>
+      <c r="T211" s="6" t="n"/>
+      <c r="U211" s="6" t="n"/>
+      <c r="V211" s="6" t="n"/>
+      <c r="W211" s="6" t="n"/>
+      <c r="X211" s="6" t="n"/>
+      <c r="Y211" s="6" t="n"/>
+      <c r="Z211" s="6" t="n"/>
+      <c r="AA211" s="6" t="n"/>
+      <c r="AB211" s="6" t="n"/>
+      <c r="AC211" s="6" t="n"/>
+      <c r="AD211" s="6" t="n"/>
+      <c r="AE211" s="6" t="n"/>
+      <c r="AF211" s="6" t="n"/>
+      <c r="AG211" s="6" t="n"/>
+      <c r="AH211" s="6" t="n"/>
+      <c r="AI211" s="6" t="n"/>
+      <c r="AJ211" s="6" t="n"/>
+      <c r="AK211" s="6" t="n"/>
+      <c r="AL211" s="6" t="n"/>
+      <c r="AM211" s="6" t="n"/>
+      <c r="AN211" s="6" t="n"/>
+      <c r="AO211" s="6" t="n"/>
+      <c r="AP211" s="6" t="n"/>
+      <c r="AQ211" s="6" t="n"/>
+      <c r="AR211" s="6" t="n"/>
+      <c r="AS211" s="6" t="n"/>
+      <c r="AT211" s="6" t="n"/>
+      <c r="AU211" s="6" t="n"/>
+      <c r="AV211" s="6" t="n"/>
+      <c r="AW211" s="6" t="n"/>
+      <c r="AX211" s="6" t="n"/>
+      <c r="AY211" s="6" t="n"/>
+      <c r="AZ211" s="6" t="n"/>
+      <c r="BA211" s="6" t="n"/>
+      <c r="BB211" s="6" t="n"/>
+      <c r="BC211" s="6" t="n"/>
+      <c r="BD211" s="6" t="n"/>
+      <c r="BE211" s="6" t="n"/>
+      <c r="BF211" s="6" t="n"/>
+      <c r="BG211" s="6" t="n"/>
+      <c r="BH211" s="6" t="n"/>
+      <c r="BI211" s="6" t="n"/>
+      <c r="BJ211" s="6" t="n"/>
+      <c r="BK211" s="6" t="n"/>
+      <c r="BL211" s="6" t="n"/>
+      <c r="BM211" s="6" t="n">
+        <v>45625</v>
       </c>
     </row>
     <row r="212">
@@ -44571,12 +45057,12 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>바나나</t>
+          <t>단감</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>수입(13kg)</t>
+          <t>부유(10kg)</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -44586,182 +45072,69 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>13kg</t>
-        </is>
-      </c>
-      <c r="G212" s="6" t="n">
-        <v>25660</v>
-      </c>
-      <c r="H212" s="6" t="n">
-        <v>25040</v>
-      </c>
-      <c r="I212" s="6" t="n">
-        <v>24840</v>
-      </c>
-      <c r="J212" s="6" t="n">
-        <v>24840</v>
-      </c>
-      <c r="K212" s="6" t="n">
-        <v>24840</v>
-      </c>
-      <c r="L212" s="6" t="n">
-        <v>24840</v>
-      </c>
-      <c r="M212" s="6" t="n">
-        <v>24560</v>
-      </c>
-      <c r="N212" s="6" t="n">
-        <v>24560</v>
-      </c>
-      <c r="O212" s="6" t="n">
-        <v>24520</v>
-      </c>
-      <c r="P212" s="6" t="n">
-        <v>24520</v>
-      </c>
-      <c r="Q212" s="6" t="n">
-        <v>24520</v>
-      </c>
-      <c r="R212" s="6" t="n">
-        <v>24520</v>
-      </c>
-      <c r="S212" s="6" t="n">
-        <v>24520</v>
-      </c>
-      <c r="T212" s="6" t="n">
-        <v>24100</v>
-      </c>
-      <c r="U212" s="6" t="n">
-        <v>24240</v>
-      </c>
-      <c r="V212" s="6" t="n">
-        <v>24240</v>
-      </c>
-      <c r="W212" s="6" t="n">
-        <v>24440</v>
-      </c>
-      <c r="X212" s="6" t="n">
-        <v>24440</v>
-      </c>
-      <c r="Y212" s="6" t="n">
-        <v>24440</v>
-      </c>
-      <c r="Z212" s="6" t="n">
-        <v>24500</v>
-      </c>
-      <c r="AA212" s="6" t="n">
-        <v>24640</v>
-      </c>
-      <c r="AB212" s="6" t="n">
-        <v>25080</v>
-      </c>
-      <c r="AC212" s="6" t="n">
-        <v>25280</v>
-      </c>
-      <c r="AD212" s="6" t="n">
-        <v>25480</v>
-      </c>
-      <c r="AE212" s="6" t="n">
-        <v>25560</v>
-      </c>
-      <c r="AF212" s="6" t="n">
-        <v>25560</v>
-      </c>
-      <c r="AG212" s="6" t="n">
-        <v>25660</v>
-      </c>
-      <c r="AH212" s="6" t="n">
-        <v>25600</v>
-      </c>
-      <c r="AI212" s="6" t="n">
-        <v>25600</v>
-      </c>
-      <c r="AJ212" s="6" t="n">
-        <v>26220</v>
-      </c>
-      <c r="AK212" s="6" t="n">
-        <v>26220</v>
-      </c>
-      <c r="AL212" s="6" t="n">
-        <v>26220</v>
-      </c>
-      <c r="AM212" s="6" t="n">
-        <v>26420</v>
-      </c>
-      <c r="AN212" s="6" t="n">
-        <v>26420</v>
-      </c>
-      <c r="AO212" s="6" t="n">
-        <v>27300</v>
-      </c>
-      <c r="AP212" s="6" t="n">
-        <v>27700</v>
-      </c>
-      <c r="AQ212" s="6" t="n">
-        <v>27700</v>
-      </c>
-      <c r="AR212" s="6" t="n">
-        <v>27900</v>
-      </c>
-      <c r="AS212" s="6" t="n">
-        <v>27760</v>
-      </c>
-      <c r="AT212" s="6" t="n">
-        <v>27800</v>
-      </c>
-      <c r="AU212" s="6" t="n">
-        <v>27800</v>
-      </c>
-      <c r="AV212" s="6" t="n">
-        <v>27800</v>
-      </c>
-      <c r="AW212" s="6" t="n">
-        <v>27660</v>
-      </c>
-      <c r="AX212" s="6" t="n">
-        <v>27660</v>
-      </c>
-      <c r="AY212" s="6" t="n">
-        <v>27660</v>
-      </c>
-      <c r="AZ212" s="6" t="n">
-        <v>27660</v>
-      </c>
-      <c r="BA212" s="6" t="n">
-        <v>27660</v>
-      </c>
-      <c r="BB212" s="6" t="n">
-        <v>27660</v>
-      </c>
-      <c r="BC212" s="6" t="n">
-        <v>27580</v>
-      </c>
-      <c r="BD212" s="6" t="n">
-        <v>27580</v>
-      </c>
-      <c r="BE212" s="6" t="n">
-        <v>27380</v>
-      </c>
-      <c r="BF212" s="6" t="n">
-        <v>27380</v>
-      </c>
-      <c r="BG212" s="6" t="n">
-        <v>26860</v>
-      </c>
-      <c r="BH212" s="6" t="n">
-        <v>26860</v>
-      </c>
-      <c r="BI212" s="6" t="n">
-        <v>26860</v>
-      </c>
-      <c r="BJ212" s="6" t="n">
-        <v>26860</v>
-      </c>
-      <c r="BK212" s="6" t="n">
-        <v>26860</v>
-      </c>
-      <c r="BL212" s="6" t="n">
-        <v>26860</v>
+          <t>10kg</t>
+        </is>
+      </c>
+      <c r="G212" s="6" t="n"/>
+      <c r="H212" s="6" t="n"/>
+      <c r="I212" s="6" t="n"/>
+      <c r="J212" s="6" t="n"/>
+      <c r="K212" s="6" t="n"/>
+      <c r="L212" s="6" t="n"/>
+      <c r="M212" s="6" t="n"/>
+      <c r="N212" s="6" t="n"/>
+      <c r="O212" s="6" t="n"/>
+      <c r="P212" s="6" t="n"/>
+      <c r="Q212" s="6" t="n"/>
+      <c r="R212" s="6" t="n"/>
+      <c r="S212" s="6" t="n"/>
+      <c r="T212" s="6" t="n"/>
+      <c r="U212" s="6" t="n"/>
+      <c r="V212" s="6" t="n"/>
+      <c r="W212" s="6" t="n"/>
+      <c r="X212" s="6" t="n"/>
+      <c r="Y212" s="6" t="n"/>
+      <c r="Z212" s="6" t="n"/>
+      <c r="AA212" s="6" t="n"/>
+      <c r="AB212" s="6" t="n"/>
+      <c r="AC212" s="6" t="n"/>
+      <c r="AD212" s="6" t="n"/>
+      <c r="AE212" s="6" t="n"/>
+      <c r="AF212" s="6" t="n"/>
+      <c r="AG212" s="6" t="n"/>
+      <c r="AH212" s="6" t="n"/>
+      <c r="AI212" s="6" t="n"/>
+      <c r="AJ212" s="6" t="n"/>
+      <c r="AK212" s="6" t="n"/>
+      <c r="AL212" s="6" t="n"/>
+      <c r="AM212" s="6" t="n"/>
+      <c r="AN212" s="6" t="n"/>
+      <c r="AO212" s="6" t="n"/>
+      <c r="AP212" s="6" t="n"/>
+      <c r="AQ212" s="6" t="n"/>
+      <c r="AR212" s="6" t="n"/>
+      <c r="AS212" s="6" t="n"/>
+      <c r="AT212" s="6" t="n"/>
+      <c r="AU212" s="6" t="n"/>
+      <c r="AV212" s="6" t="n"/>
+      <c r="AW212" s="6" t="n"/>
+      <c r="AX212" s="6" t="n"/>
+      <c r="AY212" s="6" t="n"/>
+      <c r="AZ212" s="6" t="n"/>
+      <c r="BA212" s="6" t="n"/>
+      <c r="BB212" s="6" t="n"/>
+      <c r="BC212" s="6" t="n"/>
+      <c r="BD212" s="6" t="n"/>
+      <c r="BE212" s="6" t="n"/>
+      <c r="BF212" s="6" t="n"/>
+      <c r="BG212" s="6" t="n"/>
+      <c r="BH212" s="6" t="n"/>
+      <c r="BI212" s="6" t="n"/>
+      <c r="BJ212" s="6" t="n"/>
+      <c r="BK212" s="6" t="n"/>
+      <c r="BL212" s="6" t="n"/>
+      <c r="BM212" s="6" t="n">
+        <v>38275</v>
       </c>
     </row>
     <row r="213">
@@ -44777,12 +45150,12 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>참다래</t>
+          <t>바나나</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>그린 뉴질랜드(10kg)</t>
+          <t>수입(13kg)</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -44792,87 +45165,186 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>10kg</t>
+          <t>13kg</t>
         </is>
       </c>
       <c r="G213" s="6" t="n">
-        <v>57140</v>
+        <v>28920</v>
       </c>
       <c r="H213" s="6" t="n">
-        <v>57140</v>
+        <v>28020</v>
       </c>
       <c r="I213" s="6" t="n">
-        <v>57140</v>
+        <v>27900</v>
       </c>
       <c r="J213" s="6" t="n">
-        <v>57140</v>
+        <v>27900</v>
       </c>
       <c r="K213" s="6" t="n">
-        <v>57140</v>
+        <v>27900</v>
       </c>
       <c r="L213" s="6" t="n">
-        <v>57140</v>
+        <v>27900</v>
       </c>
       <c r="M213" s="6" t="n">
-        <v>56980</v>
+        <v>27760</v>
       </c>
       <c r="N213" s="6" t="n">
-        <v>56980</v>
+        <v>27760</v>
       </c>
       <c r="O213" s="6" t="n">
-        <v>56840</v>
+        <v>27620</v>
       </c>
       <c r="P213" s="6" t="n">
-        <v>56840</v>
-      </c>
-      <c r="Q213" s="6" t="n"/>
-      <c r="R213" s="6" t="n"/>
-      <c r="S213" s="6" t="n"/>
-      <c r="T213" s="6" t="n"/>
-      <c r="U213" s="6" t="n"/>
-      <c r="V213" s="6" t="n"/>
-      <c r="W213" s="6" t="n"/>
-      <c r="X213" s="6" t="n"/>
-      <c r="Y213" s="6" t="n"/>
-      <c r="Z213" s="6" t="n"/>
-      <c r="AA213" s="6" t="n"/>
-      <c r="AB213" s="6" t="n"/>
-      <c r="AC213" s="6" t="n"/>
-      <c r="AD213" s="6" t="n"/>
-      <c r="AE213" s="6" t="n"/>
-      <c r="AF213" s="6" t="n"/>
-      <c r="AG213" s="6" t="n"/>
-      <c r="AH213" s="6" t="n"/>
-      <c r="AI213" s="6" t="n"/>
-      <c r="AJ213" s="6" t="n"/>
-      <c r="AK213" s="6" t="n"/>
-      <c r="AL213" s="6" t="n"/>
-      <c r="AM213" s="6" t="n"/>
-      <c r="AN213" s="6" t="n"/>
-      <c r="AO213" s="6" t="n"/>
-      <c r="AP213" s="6" t="n"/>
-      <c r="AQ213" s="6" t="n"/>
-      <c r="AR213" s="6" t="n"/>
-      <c r="AS213" s="6" t="n"/>
-      <c r="AT213" s="6" t="n"/>
-      <c r="AU213" s="6" t="n"/>
-      <c r="AV213" s="6" t="n"/>
-      <c r="AW213" s="6" t="n"/>
-      <c r="AX213" s="6" t="n"/>
-      <c r="AY213" s="6" t="n"/>
-      <c r="AZ213" s="6" t="n"/>
-      <c r="BA213" s="6" t="n"/>
-      <c r="BB213" s="6" t="n"/>
-      <c r="BC213" s="6" t="n"/>
-      <c r="BD213" s="6" t="n"/>
-      <c r="BE213" s="6" t="n"/>
-      <c r="BF213" s="6" t="n"/>
-      <c r="BG213" s="6" t="n"/>
-      <c r="BH213" s="6" t="n"/>
-      <c r="BI213" s="6" t="n"/>
-      <c r="BJ213" s="6" t="n"/>
-      <c r="BK213" s="6" t="n"/>
-      <c r="BL213" s="6" t="n"/>
+        <v>27620</v>
+      </c>
+      <c r="Q213" s="6" t="n">
+        <v>27620</v>
+      </c>
+      <c r="R213" s="6" t="n">
+        <v>27620</v>
+      </c>
+      <c r="S213" s="6" t="n">
+        <v>28020</v>
+      </c>
+      <c r="T213" s="6" t="n">
+        <v>27820</v>
+      </c>
+      <c r="U213" s="6" t="n">
+        <v>27820</v>
+      </c>
+      <c r="V213" s="6" t="n">
+        <v>27940</v>
+      </c>
+      <c r="W213" s="6" t="n">
+        <v>28140</v>
+      </c>
+      <c r="X213" s="6" t="n">
+        <v>28140</v>
+      </c>
+      <c r="Y213" s="6" t="n">
+        <v>28140</v>
+      </c>
+      <c r="Z213" s="6" t="n">
+        <v>28480</v>
+      </c>
+      <c r="AA213" s="6" t="n">
+        <v>28660</v>
+      </c>
+      <c r="AB213" s="6" t="n">
+        <v>29140</v>
+      </c>
+      <c r="AC213" s="6" t="n">
+        <v>29540</v>
+      </c>
+      <c r="AD213" s="6" t="n">
+        <v>29540</v>
+      </c>
+      <c r="AE213" s="6" t="n">
+        <v>29860</v>
+      </c>
+      <c r="AF213" s="6" t="n">
+        <v>30120</v>
+      </c>
+      <c r="AG213" s="6" t="n">
+        <v>30320</v>
+      </c>
+      <c r="AH213" s="6" t="n">
+        <v>30240</v>
+      </c>
+      <c r="AI213" s="6" t="n">
+        <v>30080</v>
+      </c>
+      <c r="AJ213" s="6" t="n">
+        <v>30280</v>
+      </c>
+      <c r="AK213" s="6" t="n">
+        <v>30620</v>
+      </c>
+      <c r="AL213" s="6" t="n">
+        <v>30620</v>
+      </c>
+      <c r="AM213" s="6" t="n">
+        <v>30820</v>
+      </c>
+      <c r="AN213" s="6" t="n">
+        <v>30820</v>
+      </c>
+      <c r="AO213" s="6" t="n">
+        <v>31560</v>
+      </c>
+      <c r="AP213" s="6" t="n">
+        <v>31960</v>
+      </c>
+      <c r="AQ213" s="6" t="n">
+        <v>32160</v>
+      </c>
+      <c r="AR213" s="6" t="n">
+        <v>32160</v>
+      </c>
+      <c r="AS213" s="6" t="n">
+        <v>32100</v>
+      </c>
+      <c r="AT213" s="6" t="n">
+        <v>32300</v>
+      </c>
+      <c r="AU213" s="6" t="n">
+        <v>32300</v>
+      </c>
+      <c r="AV213" s="6" t="n">
+        <v>32300</v>
+      </c>
+      <c r="AW213" s="6" t="n">
+        <v>32760</v>
+      </c>
+      <c r="AX213" s="6" t="n">
+        <v>32760</v>
+      </c>
+      <c r="AY213" s="6" t="n">
+        <v>32760</v>
+      </c>
+      <c r="AZ213" s="6" t="n">
+        <v>32760</v>
+      </c>
+      <c r="BA213" s="6" t="n">
+        <v>32760</v>
+      </c>
+      <c r="BB213" s="6" t="n">
+        <v>32760</v>
+      </c>
+      <c r="BC213" s="6" t="n">
+        <v>32140</v>
+      </c>
+      <c r="BD213" s="6" t="n">
+        <v>32140</v>
+      </c>
+      <c r="BE213" s="6" t="n">
+        <v>31940</v>
+      </c>
+      <c r="BF213" s="6" t="n">
+        <v>31940</v>
+      </c>
+      <c r="BG213" s="6" t="n">
+        <v>31360</v>
+      </c>
+      <c r="BH213" s="6" t="n">
+        <v>31140</v>
+      </c>
+      <c r="BI213" s="6" t="n">
+        <v>31140</v>
+      </c>
+      <c r="BJ213" s="6" t="n">
+        <v>31060</v>
+      </c>
+      <c r="BK213" s="6" t="n">
+        <v>30960</v>
+      </c>
+      <c r="BL213" s="6" t="n">
+        <v>30960</v>
+      </c>
+      <c r="BM213" s="6" t="n">
+        <v>30960</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -44887,12 +45359,12 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>참다래</t>
+          <t>바나나</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>그린 뉴질랜드(10kg)</t>
+          <t>수입(13kg)</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -44902,83 +45374,186 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>10kg</t>
+          <t>13kg</t>
         </is>
       </c>
       <c r="G214" s="6" t="n">
-        <v>53300</v>
+        <v>25660</v>
       </c>
       <c r="H214" s="6" t="n">
-        <v>56000</v>
+        <v>25040</v>
       </c>
       <c r="I214" s="6" t="n">
-        <v>56000</v>
+        <v>24840</v>
       </c>
       <c r="J214" s="6" t="n">
-        <v>56000</v>
+        <v>24840</v>
       </c>
       <c r="K214" s="6" t="n">
-        <v>56000</v>
+        <v>24840</v>
       </c>
       <c r="L214" s="6" t="n">
-        <v>56000</v>
-      </c>
-      <c r="M214" s="6" t="n"/>
-      <c r="N214" s="6" t="n"/>
+        <v>24840</v>
+      </c>
+      <c r="M214" s="6" t="n">
+        <v>24560</v>
+      </c>
+      <c r="N214" s="6" t="n">
+        <v>24560</v>
+      </c>
       <c r="O214" s="6" t="n">
-        <v>54000</v>
+        <v>24520</v>
       </c>
       <c r="P214" s="6" t="n">
-        <v>54000</v>
-      </c>
-      <c r="Q214" s="6" t="n"/>
-      <c r="R214" s="6" t="n"/>
-      <c r="S214" s="6" t="n"/>
-      <c r="T214" s="6" t="n"/>
-      <c r="U214" s="6" t="n"/>
-      <c r="V214" s="6" t="n"/>
-      <c r="W214" s="6" t="n"/>
-      <c r="X214" s="6" t="n"/>
-      <c r="Y214" s="6" t="n"/>
-      <c r="Z214" s="6" t="n"/>
-      <c r="AA214" s="6" t="n"/>
-      <c r="AB214" s="6" t="n"/>
-      <c r="AC214" s="6" t="n"/>
-      <c r="AD214" s="6" t="n"/>
-      <c r="AE214" s="6" t="n"/>
-      <c r="AF214" s="6" t="n"/>
-      <c r="AG214" s="6" t="n"/>
-      <c r="AH214" s="6" t="n"/>
-      <c r="AI214" s="6" t="n"/>
-      <c r="AJ214" s="6" t="n"/>
-      <c r="AK214" s="6" t="n"/>
-      <c r="AL214" s="6" t="n"/>
-      <c r="AM214" s="6" t="n"/>
-      <c r="AN214" s="6" t="n"/>
-      <c r="AO214" s="6" t="n"/>
-      <c r="AP214" s="6" t="n"/>
-      <c r="AQ214" s="6" t="n"/>
-      <c r="AR214" s="6" t="n"/>
-      <c r="AS214" s="6" t="n"/>
-      <c r="AT214" s="6" t="n"/>
-      <c r="AU214" s="6" t="n"/>
-      <c r="AV214" s="6" t="n"/>
-      <c r="AW214" s="6" t="n"/>
-      <c r="AX214" s="6" t="n"/>
-      <c r="AY214" s="6" t="n"/>
-      <c r="AZ214" s="6" t="n"/>
-      <c r="BA214" s="6" t="n"/>
-      <c r="BB214" s="6" t="n"/>
-      <c r="BC214" s="6" t="n"/>
-      <c r="BD214" s="6" t="n"/>
-      <c r="BE214" s="6" t="n"/>
-      <c r="BF214" s="6" t="n"/>
-      <c r="BG214" s="6" t="n"/>
-      <c r="BH214" s="6" t="n"/>
-      <c r="BI214" s="6" t="n"/>
-      <c r="BJ214" s="6" t="n"/>
-      <c r="BK214" s="6" t="n"/>
-      <c r="BL214" s="6" t="n"/>
+        <v>24520</v>
+      </c>
+      <c r="Q214" s="6" t="n">
+        <v>24520</v>
+      </c>
+      <c r="R214" s="6" t="n">
+        <v>24520</v>
+      </c>
+      <c r="S214" s="6" t="n">
+        <v>24520</v>
+      </c>
+      <c r="T214" s="6" t="n">
+        <v>24100</v>
+      </c>
+      <c r="U214" s="6" t="n">
+        <v>24240</v>
+      </c>
+      <c r="V214" s="6" t="n">
+        <v>24240</v>
+      </c>
+      <c r="W214" s="6" t="n">
+        <v>24440</v>
+      </c>
+      <c r="X214" s="6" t="n">
+        <v>24440</v>
+      </c>
+      <c r="Y214" s="6" t="n">
+        <v>24440</v>
+      </c>
+      <c r="Z214" s="6" t="n">
+        <v>24500</v>
+      </c>
+      <c r="AA214" s="6" t="n">
+        <v>24640</v>
+      </c>
+      <c r="AB214" s="6" t="n">
+        <v>25080</v>
+      </c>
+      <c r="AC214" s="6" t="n">
+        <v>25280</v>
+      </c>
+      <c r="AD214" s="6" t="n">
+        <v>25480</v>
+      </c>
+      <c r="AE214" s="6" t="n">
+        <v>25560</v>
+      </c>
+      <c r="AF214" s="6" t="n">
+        <v>25560</v>
+      </c>
+      <c r="AG214" s="6" t="n">
+        <v>25660</v>
+      </c>
+      <c r="AH214" s="6" t="n">
+        <v>25600</v>
+      </c>
+      <c r="AI214" s="6" t="n">
+        <v>25600</v>
+      </c>
+      <c r="AJ214" s="6" t="n">
+        <v>26220</v>
+      </c>
+      <c r="AK214" s="6" t="n">
+        <v>26220</v>
+      </c>
+      <c r="AL214" s="6" t="n">
+        <v>26220</v>
+      </c>
+      <c r="AM214" s="6" t="n">
+        <v>26420</v>
+      </c>
+      <c r="AN214" s="6" t="n">
+        <v>26420</v>
+      </c>
+      <c r="AO214" s="6" t="n">
+        <v>27300</v>
+      </c>
+      <c r="AP214" s="6" t="n">
+        <v>27700</v>
+      </c>
+      <c r="AQ214" s="6" t="n">
+        <v>27700</v>
+      </c>
+      <c r="AR214" s="6" t="n">
+        <v>27900</v>
+      </c>
+      <c r="AS214" s="6" t="n">
+        <v>27760</v>
+      </c>
+      <c r="AT214" s="6" t="n">
+        <v>27800</v>
+      </c>
+      <c r="AU214" s="6" t="n">
+        <v>27800</v>
+      </c>
+      <c r="AV214" s="6" t="n">
+        <v>27800</v>
+      </c>
+      <c r="AW214" s="6" t="n">
+        <v>27660</v>
+      </c>
+      <c r="AX214" s="6" t="n">
+        <v>27660</v>
+      </c>
+      <c r="AY214" s="6" t="n">
+        <v>27660</v>
+      </c>
+      <c r="AZ214" s="6" t="n">
+        <v>27660</v>
+      </c>
+      <c r="BA214" s="6" t="n">
+        <v>27660</v>
+      </c>
+      <c r="BB214" s="6" t="n">
+        <v>27660</v>
+      </c>
+      <c r="BC214" s="6" t="n">
+        <v>27580</v>
+      </c>
+      <c r="BD214" s="6" t="n">
+        <v>27580</v>
+      </c>
+      <c r="BE214" s="6" t="n">
+        <v>27380</v>
+      </c>
+      <c r="BF214" s="6" t="n">
+        <v>27380</v>
+      </c>
+      <c r="BG214" s="6" t="n">
+        <v>26860</v>
+      </c>
+      <c r="BH214" s="6" t="n">
+        <v>26860</v>
+      </c>
+      <c r="BI214" s="6" t="n">
+        <v>26860</v>
+      </c>
+      <c r="BJ214" s="6" t="n">
+        <v>26860</v>
+      </c>
+      <c r="BK214" s="6" t="n">
+        <v>26860</v>
+      </c>
+      <c r="BL214" s="6" t="n">
+        <v>26860</v>
+      </c>
+      <c r="BM214" s="6" t="n">
+        <v>26860</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -44993,12 +45568,12 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>파인애플</t>
+          <t>참다래</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>수입(12kg)</t>
+          <t>그린 뉴질랜드(10kg)</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -45008,183 +45583,88 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>12kg</t>
+          <t>10kg</t>
         </is>
       </c>
       <c r="G215" s="6" t="n">
-        <v>33760</v>
+        <v>57140</v>
       </c>
       <c r="H215" s="6" t="n">
-        <v>33960</v>
+        <v>57140</v>
       </c>
       <c r="I215" s="6" t="n">
-        <v>33960</v>
+        <v>57140</v>
       </c>
       <c r="J215" s="6" t="n">
-        <v>33960</v>
+        <v>57140</v>
       </c>
       <c r="K215" s="6" t="n">
-        <v>34080</v>
+        <v>57140</v>
       </c>
       <c r="L215" s="6" t="n">
-        <v>34080</v>
+        <v>57140</v>
       </c>
       <c r="M215" s="6" t="n">
-        <v>34220</v>
+        <v>56980</v>
       </c>
       <c r="N215" s="6" t="n">
-        <v>34220</v>
+        <v>56980</v>
       </c>
       <c r="O215" s="6" t="n">
-        <v>34420</v>
+        <v>56840</v>
       </c>
       <c r="P215" s="6" t="n">
-        <v>34420</v>
-      </c>
-      <c r="Q215" s="6" t="n">
-        <v>34420</v>
-      </c>
-      <c r="R215" s="6" t="n">
-        <v>34220</v>
-      </c>
-      <c r="S215" s="6" t="n">
-        <v>34220</v>
-      </c>
-      <c r="T215" s="6" t="n">
-        <v>34280</v>
-      </c>
-      <c r="U215" s="6" t="n">
-        <v>34580</v>
-      </c>
-      <c r="V215" s="6" t="n">
-        <v>34640</v>
-      </c>
-      <c r="W215" s="6" t="n">
-        <v>35240</v>
-      </c>
-      <c r="X215" s="6" t="n">
-        <v>35240</v>
-      </c>
-      <c r="Y215" s="6" t="n">
-        <v>35240</v>
-      </c>
-      <c r="Z215" s="6" t="n">
-        <v>35440</v>
-      </c>
-      <c r="AA215" s="6" t="n">
-        <v>35780</v>
-      </c>
-      <c r="AB215" s="6" t="n">
-        <v>35920</v>
-      </c>
-      <c r="AC215" s="6" t="n">
-        <v>36720</v>
-      </c>
-      <c r="AD215" s="6" t="n">
-        <v>37120</v>
-      </c>
-      <c r="AE215" s="6" t="n">
-        <v>37720</v>
-      </c>
-      <c r="AF215" s="6" t="n">
-        <v>38320</v>
-      </c>
-      <c r="AG215" s="6" t="n">
-        <v>38320</v>
-      </c>
-      <c r="AH215" s="6" t="n">
-        <v>38460</v>
-      </c>
-      <c r="AI215" s="6" t="n">
-        <v>38460</v>
-      </c>
-      <c r="AJ215" s="6" t="n">
-        <v>38460</v>
-      </c>
-      <c r="AK215" s="6" t="n">
-        <v>38600</v>
-      </c>
-      <c r="AL215" s="6" t="n">
-        <v>38600</v>
-      </c>
-      <c r="AM215" s="6" t="n">
-        <v>38800</v>
-      </c>
-      <c r="AN215" s="6" t="n">
-        <v>38800</v>
-      </c>
-      <c r="AO215" s="6" t="n">
-        <v>39260</v>
-      </c>
-      <c r="AP215" s="6" t="n">
-        <v>39660</v>
-      </c>
-      <c r="AQ215" s="6" t="n">
-        <v>39740</v>
-      </c>
-      <c r="AR215" s="6" t="n">
-        <v>39740</v>
-      </c>
-      <c r="AS215" s="6" t="n">
-        <v>39740</v>
-      </c>
-      <c r="AT215" s="6" t="n">
-        <v>39800</v>
-      </c>
-      <c r="AU215" s="6" t="n">
-        <v>39800</v>
-      </c>
-      <c r="AV215" s="6" t="n">
-        <v>39800</v>
-      </c>
-      <c r="AW215" s="6" t="n">
-        <v>40000</v>
-      </c>
-      <c r="AX215" s="6" t="n">
-        <v>40000</v>
-      </c>
-      <c r="AY215" s="6" t="n">
-        <v>40000</v>
-      </c>
-      <c r="AZ215" s="6" t="n">
-        <v>40000</v>
-      </c>
-      <c r="BA215" s="6" t="n">
-        <v>40000</v>
-      </c>
-      <c r="BB215" s="6" t="n">
-        <v>40000</v>
-      </c>
-      <c r="BC215" s="6" t="n">
-        <v>39940</v>
-      </c>
-      <c r="BD215" s="6" t="n">
-        <v>39940</v>
-      </c>
-      <c r="BE215" s="6" t="n">
-        <v>39940</v>
-      </c>
-      <c r="BF215" s="6" t="n">
-        <v>39940</v>
-      </c>
-      <c r="BG215" s="6" t="n">
-        <v>39540</v>
-      </c>
-      <c r="BH215" s="6" t="n">
-        <v>39640</v>
-      </c>
-      <c r="BI215" s="6" t="n">
-        <v>39640</v>
-      </c>
-      <c r="BJ215" s="6" t="n">
-        <v>39760</v>
-      </c>
-      <c r="BK215" s="6" t="n">
-        <v>39760</v>
-      </c>
-      <c r="BL215" s="6" t="n">
-        <v>39760</v>
-      </c>
+        <v>56840</v>
+      </c>
+      <c r="Q215" s="6" t="n"/>
+      <c r="R215" s="6" t="n"/>
+      <c r="S215" s="6" t="n"/>
+      <c r="T215" s="6" t="n"/>
+      <c r="U215" s="6" t="n"/>
+      <c r="V215" s="6" t="n"/>
+      <c r="W215" s="6" t="n"/>
+      <c r="X215" s="6" t="n"/>
+      <c r="Y215" s="6" t="n"/>
+      <c r="Z215" s="6" t="n"/>
+      <c r="AA215" s="6" t="n"/>
+      <c r="AB215" s="6" t="n"/>
+      <c r="AC215" s="6" t="n"/>
+      <c r="AD215" s="6" t="n"/>
+      <c r="AE215" s="6" t="n"/>
+      <c r="AF215" s="6" t="n"/>
+      <c r="AG215" s="6" t="n"/>
+      <c r="AH215" s="6" t="n"/>
+      <c r="AI215" s="6" t="n"/>
+      <c r="AJ215" s="6" t="n"/>
+      <c r="AK215" s="6" t="n"/>
+      <c r="AL215" s="6" t="n"/>
+      <c r="AM215" s="6" t="n"/>
+      <c r="AN215" s="6" t="n"/>
+      <c r="AO215" s="6" t="n"/>
+      <c r="AP215" s="6" t="n"/>
+      <c r="AQ215" s="6" t="n"/>
+      <c r="AR215" s="6" t="n"/>
+      <c r="AS215" s="6" t="n"/>
+      <c r="AT215" s="6" t="n"/>
+      <c r="AU215" s="6" t="n"/>
+      <c r="AV215" s="6" t="n"/>
+      <c r="AW215" s="6" t="n"/>
+      <c r="AX215" s="6" t="n"/>
+      <c r="AY215" s="6" t="n"/>
+      <c r="AZ215" s="6" t="n"/>
+      <c r="BA215" s="6" t="n"/>
+      <c r="BB215" s="6" t="n"/>
+      <c r="BC215" s="6" t="n"/>
+      <c r="BD215" s="6" t="n"/>
+      <c r="BE215" s="6" t="n"/>
+      <c r="BF215" s="6" t="n"/>
+      <c r="BG215" s="6" t="n"/>
+      <c r="BH215" s="6" t="n"/>
+      <c r="BI215" s="6" t="n"/>
+      <c r="BJ215" s="6" t="n"/>
+      <c r="BK215" s="6" t="n"/>
+      <c r="BL215" s="6" t="n"/>
+      <c r="BM215" s="6" t="n"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -45199,12 +45679,12 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>파인애플</t>
+          <t>참다래</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>수입(12kg)</t>
+          <t>그린 뉴질랜드(10kg)</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -45214,183 +45694,84 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>12kg</t>
+          <t>10kg</t>
         </is>
       </c>
       <c r="G216" s="6" t="n">
-        <v>29500</v>
+        <v>53300</v>
       </c>
       <c r="H216" s="6" t="n">
-        <v>30067</v>
+        <v>56000</v>
       </c>
       <c r="I216" s="6" t="n">
-        <v>29833</v>
+        <v>56000</v>
       </c>
       <c r="J216" s="6" t="n">
-        <v>29833</v>
+        <v>56000</v>
       </c>
       <c r="K216" s="6" t="n">
-        <v>30067</v>
+        <v>56000</v>
       </c>
       <c r="L216" s="6" t="n">
-        <v>30067</v>
-      </c>
-      <c r="M216" s="6" t="n">
-        <v>30267</v>
-      </c>
-      <c r="N216" s="6" t="n">
-        <v>30167</v>
-      </c>
+        <v>56000</v>
+      </c>
+      <c r="M216" s="6" t="n"/>
+      <c r="N216" s="6" t="n"/>
       <c r="O216" s="6" t="n">
-        <v>30167</v>
+        <v>54000</v>
       </c>
       <c r="P216" s="6" t="n">
-        <v>30167</v>
-      </c>
-      <c r="Q216" s="6" t="n">
-        <v>30167</v>
-      </c>
-      <c r="R216" s="6" t="n">
-        <v>29500</v>
-      </c>
-      <c r="S216" s="6" t="n">
-        <v>29500</v>
-      </c>
-      <c r="T216" s="6" t="n">
-        <v>29500</v>
-      </c>
-      <c r="U216" s="6" t="n">
-        <v>28933</v>
-      </c>
-      <c r="V216" s="6" t="n">
-        <v>29167</v>
-      </c>
-      <c r="W216" s="6" t="n">
-        <v>28750</v>
-      </c>
-      <c r="X216" s="6" t="n">
-        <v>28750</v>
-      </c>
-      <c r="Y216" s="6" t="n">
-        <v>28750</v>
-      </c>
-      <c r="Z216" s="6" t="n">
-        <v>28750</v>
-      </c>
-      <c r="AA216" s="6" t="n">
-        <v>30000</v>
-      </c>
-      <c r="AB216" s="6" t="n">
-        <v>30100</v>
-      </c>
-      <c r="AC216" s="6" t="n">
-        <v>30100</v>
-      </c>
-      <c r="AD216" s="6" t="n">
-        <v>30100</v>
-      </c>
-      <c r="AE216" s="6" t="n">
-        <v>31267</v>
-      </c>
-      <c r="AF216" s="6" t="n">
-        <v>31267</v>
-      </c>
-      <c r="AG216" s="6" t="n">
-        <v>31267</v>
-      </c>
-      <c r="AH216" s="6" t="n">
-        <v>30933</v>
-      </c>
-      <c r="AI216" s="6" t="n">
-        <v>30933</v>
-      </c>
-      <c r="AJ216" s="6" t="n">
-        <v>31833</v>
-      </c>
-      <c r="AK216" s="6" t="n">
-        <v>32033</v>
-      </c>
-      <c r="AL216" s="6" t="n">
-        <v>31500</v>
-      </c>
-      <c r="AM216" s="6" t="n">
-        <v>31500</v>
-      </c>
-      <c r="AN216" s="6" t="n">
-        <v>31500</v>
-      </c>
-      <c r="AO216" s="6" t="n">
-        <v>31500</v>
-      </c>
-      <c r="AP216" s="6" t="n">
-        <v>33167</v>
-      </c>
-      <c r="AQ216" s="6" t="n">
-        <v>33167</v>
-      </c>
-      <c r="AR216" s="6" t="n">
-        <v>33167</v>
-      </c>
-      <c r="AS216" s="6" t="n">
-        <v>33700</v>
-      </c>
-      <c r="AT216" s="6" t="n">
-        <v>33700</v>
-      </c>
-      <c r="AU216" s="6" t="n">
-        <v>33700</v>
-      </c>
-      <c r="AV216" s="6" t="n">
-        <v>33700</v>
-      </c>
-      <c r="AW216" s="6" t="n">
-        <v>34033</v>
-      </c>
-      <c r="AX216" s="6" t="n">
-        <v>34033</v>
-      </c>
-      <c r="AY216" s="6" t="n">
-        <v>34033</v>
-      </c>
-      <c r="AZ216" s="6" t="n">
-        <v>34033</v>
-      </c>
-      <c r="BA216" s="6" t="n">
-        <v>34033</v>
-      </c>
-      <c r="BB216" s="6" t="n">
-        <v>34033</v>
-      </c>
-      <c r="BC216" s="6" t="n">
-        <v>33700</v>
-      </c>
-      <c r="BD216" s="6" t="n">
-        <v>33700</v>
-      </c>
-      <c r="BE216" s="6" t="n">
-        <v>33700</v>
-      </c>
-      <c r="BF216" s="6" t="n">
-        <v>33700</v>
-      </c>
-      <c r="BG216" s="6" t="n">
-        <v>34200</v>
-      </c>
-      <c r="BH216" s="6" t="n">
-        <v>34200</v>
-      </c>
-      <c r="BI216" s="6" t="n">
-        <v>34200</v>
-      </c>
-      <c r="BJ216" s="6" t="n">
-        <v>34200</v>
-      </c>
-      <c r="BK216" s="6" t="n">
-        <v>34200</v>
-      </c>
-      <c r="BL216" s="6" t="n">
-        <v>34200</v>
-      </c>
+        <v>54000</v>
+      </c>
+      <c r="Q216" s="6" t="n"/>
+      <c r="R216" s="6" t="n"/>
+      <c r="S216" s="6" t="n"/>
+      <c r="T216" s="6" t="n"/>
+      <c r="U216" s="6" t="n"/>
+      <c r="V216" s="6" t="n"/>
+      <c r="W216" s="6" t="n"/>
+      <c r="X216" s="6" t="n"/>
+      <c r="Y216" s="6" t="n"/>
+      <c r="Z216" s="6" t="n"/>
+      <c r="AA216" s="6" t="n"/>
+      <c r="AB216" s="6" t="n"/>
+      <c r="AC216" s="6" t="n"/>
+      <c r="AD216" s="6" t="n"/>
+      <c r="AE216" s="6" t="n"/>
+      <c r="AF216" s="6" t="n"/>
+      <c r="AG216" s="6" t="n"/>
+      <c r="AH216" s="6" t="n"/>
+      <c r="AI216" s="6" t="n"/>
+      <c r="AJ216" s="6" t="n"/>
+      <c r="AK216" s="6" t="n"/>
+      <c r="AL216" s="6" t="n"/>
+      <c r="AM216" s="6" t="n"/>
+      <c r="AN216" s="6" t="n"/>
+      <c r="AO216" s="6" t="n"/>
+      <c r="AP216" s="6" t="n"/>
+      <c r="AQ216" s="6" t="n"/>
+      <c r="AR216" s="6" t="n"/>
+      <c r="AS216" s="6" t="n"/>
+      <c r="AT216" s="6" t="n"/>
+      <c r="AU216" s="6" t="n"/>
+      <c r="AV216" s="6" t="n"/>
+      <c r="AW216" s="6" t="n"/>
+      <c r="AX216" s="6" t="n"/>
+      <c r="AY216" s="6" t="n"/>
+      <c r="AZ216" s="6" t="n"/>
+      <c r="BA216" s="6" t="n"/>
+      <c r="BB216" s="6" t="n"/>
+      <c r="BC216" s="6" t="n"/>
+      <c r="BD216" s="6" t="n"/>
+      <c r="BE216" s="6" t="n"/>
+      <c r="BF216" s="6" t="n"/>
+      <c r="BG216" s="6" t="n"/>
+      <c r="BH216" s="6" t="n"/>
+      <c r="BI216" s="6" t="n"/>
+      <c r="BJ216" s="6" t="n"/>
+      <c r="BK216" s="6" t="n"/>
+      <c r="BL216" s="6" t="n"/>
+      <c r="BM216" s="6" t="n"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -45405,12 +45786,12 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>오렌지</t>
+          <t>파인애플</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>네이블 호주(18kg)</t>
+          <t>수입(12kg)</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -45420,182 +45801,185 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>18kg</t>
+          <t>12kg</t>
         </is>
       </c>
       <c r="G217" s="6" t="n">
-        <v>84575</v>
+        <v>33760</v>
       </c>
       <c r="H217" s="6" t="n">
-        <v>81950</v>
+        <v>33960</v>
       </c>
       <c r="I217" s="6" t="n">
-        <v>81100</v>
+        <v>33960</v>
       </c>
       <c r="J217" s="6" t="n">
-        <v>81100</v>
+        <v>33960</v>
       </c>
       <c r="K217" s="6" t="n">
-        <v>80980</v>
+        <v>34080</v>
       </c>
       <c r="L217" s="6" t="n">
-        <v>80980</v>
+        <v>34080</v>
       </c>
       <c r="M217" s="6" t="n">
-        <v>76860</v>
+        <v>34220</v>
       </c>
       <c r="N217" s="6" t="n">
-        <v>76860</v>
+        <v>34220</v>
       </c>
       <c r="O217" s="6" t="n">
-        <v>76860</v>
+        <v>34420</v>
       </c>
       <c r="P217" s="6" t="n">
-        <v>76860</v>
+        <v>34420</v>
       </c>
       <c r="Q217" s="6" t="n">
-        <v>76860</v>
+        <v>34420</v>
       </c>
       <c r="R217" s="6" t="n">
-        <v>74260</v>
+        <v>34220</v>
       </c>
       <c r="S217" s="6" t="n">
-        <v>72660</v>
+        <v>34220</v>
       </c>
       <c r="T217" s="6" t="n">
-        <v>70650</v>
+        <v>34280</v>
       </c>
       <c r="U217" s="6" t="n">
-        <v>68100</v>
+        <v>34580</v>
       </c>
       <c r="V217" s="6" t="n">
-        <v>66325</v>
+        <v>34640</v>
       </c>
       <c r="W217" s="6" t="n">
-        <v>66325</v>
+        <v>35240</v>
       </c>
       <c r="X217" s="6" t="n">
-        <v>66325</v>
+        <v>35240</v>
       </c>
       <c r="Y217" s="6" t="n">
-        <v>62825</v>
+        <v>35240</v>
       </c>
       <c r="Z217" s="6" t="n">
-        <v>62825</v>
+        <v>35440</v>
       </c>
       <c r="AA217" s="6" t="n">
-        <v>62825</v>
+        <v>35780</v>
       </c>
       <c r="AB217" s="6" t="n">
-        <v>62825</v>
+        <v>35920</v>
       </c>
       <c r="AC217" s="6" t="n">
-        <v>62825</v>
+        <v>36720</v>
       </c>
       <c r="AD217" s="6" t="n">
-        <v>61950</v>
+        <v>37120</v>
       </c>
       <c r="AE217" s="6" t="n">
-        <v>64125</v>
+        <v>37720</v>
       </c>
       <c r="AF217" s="6" t="n">
-        <v>62750</v>
+        <v>38320</v>
       </c>
       <c r="AG217" s="6" t="n">
-        <v>62075</v>
+        <v>38320</v>
       </c>
       <c r="AH217" s="6" t="n">
-        <v>62075</v>
+        <v>38460</v>
       </c>
       <c r="AI217" s="6" t="n">
-        <v>62200</v>
+        <v>38460</v>
       </c>
       <c r="AJ217" s="6" t="n">
-        <v>61350</v>
+        <v>38460</v>
       </c>
       <c r="AK217" s="6" t="n">
-        <v>61350</v>
+        <v>38600</v>
       </c>
       <c r="AL217" s="6" t="n">
-        <v>60375</v>
+        <v>38600</v>
       </c>
       <c r="AM217" s="6" t="n">
-        <v>60375</v>
+        <v>38800</v>
       </c>
       <c r="AN217" s="6" t="n">
-        <v>60375</v>
+        <v>38800</v>
       </c>
       <c r="AO217" s="6" t="n">
-        <v>61625</v>
+        <v>39260</v>
       </c>
       <c r="AP217" s="6" t="n">
-        <v>61625</v>
+        <v>39660</v>
       </c>
       <c r="AQ217" s="6" t="n">
-        <v>61625</v>
+        <v>39740</v>
       </c>
       <c r="AR217" s="6" t="n">
-        <v>61625</v>
+        <v>39740</v>
       </c>
       <c r="AS217" s="6" t="n">
-        <v>60800</v>
+        <v>39740</v>
       </c>
       <c r="AT217" s="6" t="n">
-        <v>60800</v>
+        <v>39800</v>
       </c>
       <c r="AU217" s="6" t="n">
-        <v>60800</v>
+        <v>39800</v>
       </c>
       <c r="AV217" s="6" t="n">
-        <v>60125</v>
+        <v>39800</v>
       </c>
       <c r="AW217" s="6" t="n">
-        <v>58875</v>
+        <v>40000</v>
       </c>
       <c r="AX217" s="6" t="n">
-        <v>58875</v>
+        <v>40000</v>
       </c>
       <c r="AY217" s="6" t="n">
-        <v>58875</v>
+        <v>40000</v>
       </c>
       <c r="AZ217" s="6" t="n">
-        <v>57950</v>
+        <v>40000</v>
       </c>
       <c r="BA217" s="6" t="n">
-        <v>57950</v>
+        <v>40000</v>
       </c>
       <c r="BB217" s="6" t="n">
-        <v>57775</v>
+        <v>40000</v>
       </c>
       <c r="BC217" s="6" t="n">
-        <v>60075</v>
+        <v>39940</v>
       </c>
       <c r="BD217" s="6" t="n">
-        <v>60075</v>
+        <v>39940</v>
       </c>
       <c r="BE217" s="6" t="n">
-        <v>60075</v>
+        <v>39940</v>
       </c>
       <c r="BF217" s="6" t="n">
-        <v>60075</v>
+        <v>39940</v>
       </c>
       <c r="BG217" s="6" t="n">
-        <v>58900</v>
+        <v>39540</v>
       </c>
       <c r="BH217" s="6" t="n">
-        <v>58900</v>
+        <v>39640</v>
       </c>
       <c r="BI217" s="6" t="n">
-        <v>58900</v>
+        <v>39640</v>
       </c>
       <c r="BJ217" s="6" t="n">
-        <v>58900</v>
+        <v>39760</v>
       </c>
       <c r="BK217" s="6" t="n">
-        <v>58900</v>
+        <v>39760</v>
       </c>
       <c r="BL217" s="6" t="n">
-        <v>58725</v>
+        <v>39760</v>
+      </c>
+      <c r="BM217" s="6" t="n">
+        <v>39760</v>
       </c>
     </row>
     <row r="218">
@@ -45611,12 +45995,12 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>오렌지</t>
+          <t>파인애플</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>네이블 호주(18kg)</t>
+          <t>수입(12kg)</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -45626,182 +46010,185 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>18kg</t>
+          <t>12kg</t>
         </is>
       </c>
       <c r="G218" s="6" t="n">
-        <v>76650</v>
+        <v>29500</v>
       </c>
       <c r="H218" s="6" t="n">
-        <v>74150</v>
+        <v>30067</v>
       </c>
       <c r="I218" s="6" t="n">
-        <v>73300</v>
+        <v>29833</v>
       </c>
       <c r="J218" s="6" t="n">
-        <v>73300</v>
+        <v>29833</v>
       </c>
       <c r="K218" s="6" t="n">
-        <v>73200</v>
+        <v>30067</v>
       </c>
       <c r="L218" s="6" t="n">
-        <v>73200</v>
+        <v>30067</v>
       </c>
       <c r="M218" s="6" t="n">
-        <v>69175</v>
+        <v>30267</v>
       </c>
       <c r="N218" s="6" t="n">
-        <v>69175</v>
+        <v>30167</v>
       </c>
       <c r="O218" s="6" t="n">
-        <v>67925</v>
+        <v>30167</v>
       </c>
       <c r="P218" s="6" t="n">
-        <v>67925</v>
+        <v>30167</v>
       </c>
       <c r="Q218" s="6" t="n">
-        <v>67675</v>
+        <v>30167</v>
       </c>
       <c r="R218" s="6" t="n">
-        <v>64875</v>
+        <v>29500</v>
       </c>
       <c r="S218" s="6" t="n">
-        <v>64875</v>
+        <v>29500</v>
       </c>
       <c r="T218" s="6" t="n">
-        <v>64760</v>
+        <v>29500</v>
       </c>
       <c r="U218" s="6" t="n">
-        <v>62260</v>
+        <v>28933</v>
       </c>
       <c r="V218" s="6" t="n">
-        <v>60760</v>
+        <v>29167</v>
       </c>
       <c r="W218" s="6" t="n">
-        <v>60560</v>
+        <v>28750</v>
       </c>
       <c r="X218" s="6" t="n">
-        <v>60560</v>
+        <v>28750</v>
       </c>
       <c r="Y218" s="6" t="n">
-        <v>59500</v>
+        <v>28750</v>
       </c>
       <c r="Z218" s="6" t="n">
-        <v>58300</v>
+        <v>28750</v>
       </c>
       <c r="AA218" s="6" t="n">
-        <v>59020</v>
+        <v>30000</v>
       </c>
       <c r="AB218" s="6" t="n">
-        <v>58360</v>
+        <v>30100</v>
       </c>
       <c r="AC218" s="6" t="n">
-        <v>58360</v>
+        <v>30100</v>
       </c>
       <c r="AD218" s="6" t="n">
-        <v>56560</v>
+        <v>30100</v>
       </c>
       <c r="AE218" s="6" t="n">
-        <v>56600</v>
+        <v>31267</v>
       </c>
       <c r="AF218" s="6" t="n">
-        <v>55360</v>
+        <v>31267</v>
       </c>
       <c r="AG218" s="6" t="n">
-        <v>54860</v>
+        <v>31267</v>
       </c>
       <c r="AH218" s="6" t="n">
-        <v>54860</v>
+        <v>30933</v>
       </c>
       <c r="AI218" s="6" t="n">
-        <v>54920</v>
+        <v>30933</v>
       </c>
       <c r="AJ218" s="6" t="n">
-        <v>55920</v>
+        <v>31833</v>
       </c>
       <c r="AK218" s="6" t="n">
-        <v>55920</v>
+        <v>32033</v>
       </c>
       <c r="AL218" s="6" t="n">
-        <v>55260</v>
+        <v>31500</v>
       </c>
       <c r="AM218" s="6" t="n">
-        <v>55260</v>
+        <v>31500</v>
       </c>
       <c r="AN218" s="6" t="n">
-        <v>55260</v>
+        <v>31500</v>
       </c>
       <c r="AO218" s="6" t="n">
-        <v>55620</v>
+        <v>31500</v>
       </c>
       <c r="AP218" s="6" t="n">
-        <v>55620</v>
+        <v>33167</v>
       </c>
       <c r="AQ218" s="6" t="n">
-        <v>55420</v>
+        <v>33167</v>
       </c>
       <c r="AR218" s="6" t="n">
-        <v>55420</v>
+        <v>33167</v>
       </c>
       <c r="AS218" s="6" t="n">
-        <v>55100</v>
+        <v>33700</v>
       </c>
       <c r="AT218" s="6" t="n">
-        <v>55100</v>
+        <v>33700</v>
       </c>
       <c r="AU218" s="6" t="n">
-        <v>55100</v>
+        <v>33700</v>
       </c>
       <c r="AV218" s="6" t="n">
-        <v>55020</v>
+        <v>33700</v>
       </c>
       <c r="AW218" s="6" t="n">
-        <v>54020</v>
+        <v>34033</v>
       </c>
       <c r="AX218" s="6" t="n">
-        <v>54020</v>
+        <v>34033</v>
       </c>
       <c r="AY218" s="6" t="n">
-        <v>54820</v>
+        <v>34033</v>
       </c>
       <c r="AZ218" s="6" t="n">
-        <v>54760</v>
+        <v>34033</v>
       </c>
       <c r="BA218" s="6" t="n">
-        <v>54760</v>
+        <v>34033</v>
       </c>
       <c r="BB218" s="6" t="n">
-        <v>54760</v>
+        <v>34033</v>
       </c>
       <c r="BC218" s="6" t="n">
-        <v>55000</v>
+        <v>33700</v>
       </c>
       <c r="BD218" s="6" t="n">
-        <v>55000</v>
+        <v>33700</v>
       </c>
       <c r="BE218" s="6" t="n">
-        <v>55000</v>
+        <v>33700</v>
       </c>
       <c r="BF218" s="6" t="n">
-        <v>55000</v>
+        <v>33700</v>
       </c>
       <c r="BG218" s="6" t="n">
-        <v>53660</v>
+        <v>34200</v>
       </c>
       <c r="BH218" s="6" t="n">
-        <v>52980</v>
+        <v>34200</v>
       </c>
       <c r="BI218" s="6" t="n">
-        <v>52980</v>
+        <v>34200</v>
       </c>
       <c r="BJ218" s="6" t="n">
-        <v>52580</v>
+        <v>34200</v>
       </c>
       <c r="BK218" s="6" t="n">
-        <v>52580</v>
+        <v>34200</v>
       </c>
       <c r="BL218" s="6" t="n">
-        <v>52380</v>
+        <v>34200</v>
+      </c>
+      <c r="BM218" s="6" t="n">
+        <v>34200</v>
       </c>
     </row>
     <row r="219">
@@ -45817,12 +46204,12 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>레몬</t>
+          <t>오렌지</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>수입(17kg)</t>
+          <t>네이블 호주(18kg)</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -45832,182 +46219,185 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>17kg</t>
+          <t>18kg</t>
         </is>
       </c>
       <c r="G219" s="6" t="n">
-        <v>81520</v>
+        <v>84575</v>
       </c>
       <c r="H219" s="6" t="n">
-        <v>78980</v>
+        <v>81950</v>
       </c>
       <c r="I219" s="6" t="n">
-        <v>78320</v>
+        <v>81100</v>
       </c>
       <c r="J219" s="6" t="n">
-        <v>78320</v>
+        <v>81100</v>
       </c>
       <c r="K219" s="6" t="n">
-        <v>77640</v>
+        <v>80980</v>
       </c>
       <c r="L219" s="6" t="n">
-        <v>77640</v>
+        <v>80980</v>
       </c>
       <c r="M219" s="6" t="n">
-        <v>76160</v>
+        <v>76860</v>
       </c>
       <c r="N219" s="6" t="n">
-        <v>76160</v>
+        <v>76860</v>
       </c>
       <c r="O219" s="6" t="n">
-        <v>75840</v>
+        <v>76860</v>
       </c>
       <c r="P219" s="6" t="n">
-        <v>75840</v>
+        <v>76860</v>
       </c>
       <c r="Q219" s="6" t="n">
-        <v>75720</v>
+        <v>76860</v>
       </c>
       <c r="R219" s="6" t="n">
-        <v>74700</v>
+        <v>74260</v>
       </c>
       <c r="S219" s="6" t="n">
-        <v>74700</v>
+        <v>72660</v>
       </c>
       <c r="T219" s="6" t="n">
-        <v>74360</v>
+        <v>70650</v>
       </c>
       <c r="U219" s="6" t="n">
-        <v>73680</v>
+        <v>68100</v>
       </c>
       <c r="V219" s="6" t="n">
-        <v>73160</v>
+        <v>66325</v>
       </c>
       <c r="W219" s="6" t="n">
-        <v>71760</v>
+        <v>66325</v>
       </c>
       <c r="X219" s="6" t="n">
-        <v>71760</v>
+        <v>66325</v>
       </c>
       <c r="Y219" s="6" t="n">
-        <v>71760</v>
+        <v>62825</v>
       </c>
       <c r="Z219" s="6" t="n">
-        <v>70560</v>
+        <v>62825</v>
       </c>
       <c r="AA219" s="6" t="n">
-        <v>68960</v>
+        <v>62825</v>
       </c>
       <c r="AB219" s="6" t="n">
-        <v>68960</v>
+        <v>62825</v>
       </c>
       <c r="AC219" s="6" t="n">
-        <v>68160</v>
+        <v>62825</v>
       </c>
       <c r="AD219" s="6" t="n">
-        <v>67820</v>
+        <v>61950</v>
       </c>
       <c r="AE219" s="6" t="n">
-        <v>67500</v>
+        <v>64125</v>
       </c>
       <c r="AF219" s="6" t="n">
-        <v>64940</v>
+        <v>62750</v>
       </c>
       <c r="AG219" s="6" t="n">
-        <v>64080</v>
+        <v>62075</v>
       </c>
       <c r="AH219" s="6" t="n">
-        <v>62880</v>
+        <v>62075</v>
       </c>
       <c r="AI219" s="6" t="n">
-        <v>62880</v>
+        <v>62200</v>
       </c>
       <c r="AJ219" s="6" t="n">
-        <v>62080</v>
+        <v>61350</v>
       </c>
       <c r="AK219" s="6" t="n">
-        <v>62080</v>
+        <v>61350</v>
       </c>
       <c r="AL219" s="6" t="n">
-        <v>62080</v>
+        <v>60375</v>
       </c>
       <c r="AM219" s="6" t="n">
-        <v>62080</v>
+        <v>60375</v>
       </c>
       <c r="AN219" s="6" t="n">
-        <v>62080</v>
+        <v>60375</v>
       </c>
       <c r="AO219" s="6" t="n">
-        <v>62420</v>
+        <v>61625</v>
       </c>
       <c r="AP219" s="6" t="n">
-        <v>62420</v>
+        <v>61625</v>
       </c>
       <c r="AQ219" s="6" t="n">
-        <v>62080</v>
+        <v>61625</v>
       </c>
       <c r="AR219" s="6" t="n">
-        <v>60880</v>
+        <v>61625</v>
       </c>
       <c r="AS219" s="6" t="n">
-        <v>60880</v>
+        <v>60800</v>
       </c>
       <c r="AT219" s="6" t="n">
-        <v>59960</v>
+        <v>60800</v>
       </c>
       <c r="AU219" s="6" t="n">
-        <v>59960</v>
+        <v>60800</v>
       </c>
       <c r="AV219" s="6" t="n">
-        <v>59960</v>
+        <v>60125</v>
       </c>
       <c r="AW219" s="6" t="n">
-        <v>60300</v>
+        <v>58875</v>
       </c>
       <c r="AX219" s="6" t="n">
-        <v>60300</v>
+        <v>58875</v>
       </c>
       <c r="AY219" s="6" t="n">
-        <v>60300</v>
+        <v>58875</v>
       </c>
       <c r="AZ219" s="6" t="n">
-        <v>60420</v>
+        <v>57950</v>
       </c>
       <c r="BA219" s="6" t="n">
-        <v>60420</v>
+        <v>57950</v>
       </c>
       <c r="BB219" s="6" t="n">
-        <v>58940</v>
+        <v>57775</v>
       </c>
       <c r="BC219" s="6" t="n">
-        <v>58340</v>
+        <v>60075</v>
       </c>
       <c r="BD219" s="6" t="n">
-        <v>58340</v>
+        <v>60075</v>
       </c>
       <c r="BE219" s="6" t="n">
-        <v>57280</v>
+        <v>60075</v>
       </c>
       <c r="BF219" s="6" t="n">
-        <v>57180</v>
+        <v>60075</v>
       </c>
       <c r="BG219" s="6" t="n">
-        <v>55520</v>
+        <v>58900</v>
       </c>
       <c r="BH219" s="6" t="n">
-        <v>55840</v>
+        <v>58900</v>
       </c>
       <c r="BI219" s="6" t="n">
-        <v>55840</v>
+        <v>58900</v>
       </c>
       <c r="BJ219" s="6" t="n">
-        <v>56180</v>
+        <v>58900</v>
       </c>
       <c r="BK219" s="6" t="n">
-        <v>56120</v>
+        <v>58900</v>
       </c>
       <c r="BL219" s="6" t="n">
-        <v>55980</v>
+        <v>58725</v>
+      </c>
+      <c r="BM219" s="6" t="n">
+        <v>58725</v>
       </c>
     </row>
     <row r="220">
@@ -46023,12 +46413,12 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>레몬</t>
+          <t>오렌지</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>수입(17kg)</t>
+          <t>네이블 호주(18kg)</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -46038,182 +46428,185 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>17kg</t>
+          <t>18kg</t>
         </is>
       </c>
       <c r="G220" s="6" t="n">
-        <v>71500</v>
+        <v>76650</v>
       </c>
       <c r="H220" s="6" t="n">
-        <v>68167</v>
+        <v>74150</v>
       </c>
       <c r="I220" s="6" t="n">
-        <v>68167</v>
+        <v>73300</v>
       </c>
       <c r="J220" s="6" t="n">
-        <v>68167</v>
+        <v>73300</v>
       </c>
       <c r="K220" s="6" t="n">
-        <v>68167</v>
+        <v>73200</v>
       </c>
       <c r="L220" s="6" t="n">
-        <v>68167</v>
+        <v>73200</v>
       </c>
       <c r="M220" s="6" t="n">
-        <v>68033</v>
+        <v>69175</v>
       </c>
       <c r="N220" s="6" t="n">
-        <v>68033</v>
+        <v>69175</v>
       </c>
       <c r="O220" s="6" t="n">
-        <v>66367</v>
+        <v>67925</v>
       </c>
       <c r="P220" s="6" t="n">
-        <v>66367</v>
+        <v>67925</v>
       </c>
       <c r="Q220" s="6" t="n">
-        <v>66367</v>
+        <v>67675</v>
       </c>
       <c r="R220" s="6" t="n">
-        <v>66033</v>
+        <v>64875</v>
       </c>
       <c r="S220" s="6" t="n">
-        <v>66033</v>
+        <v>64875</v>
       </c>
       <c r="T220" s="6" t="n">
-        <v>66033</v>
+        <v>64760</v>
       </c>
       <c r="U220" s="6" t="n">
-        <v>65533</v>
+        <v>62260</v>
       </c>
       <c r="V220" s="6" t="n">
-        <v>65500</v>
+        <v>60760</v>
       </c>
       <c r="W220" s="6" t="n">
-        <v>65500</v>
+        <v>60560</v>
       </c>
       <c r="X220" s="6" t="n">
-        <v>65500</v>
+        <v>60560</v>
       </c>
       <c r="Y220" s="6" t="n">
-        <v>65500</v>
+        <v>59500</v>
       </c>
       <c r="Z220" s="6" t="n">
-        <v>63500</v>
+        <v>58300</v>
       </c>
       <c r="AA220" s="6" t="n">
-        <v>63500</v>
+        <v>59020</v>
       </c>
       <c r="AB220" s="6" t="n">
-        <v>63500</v>
+        <v>58360</v>
       </c>
       <c r="AC220" s="6" t="n">
-        <v>62167</v>
+        <v>58360</v>
       </c>
       <c r="AD220" s="6" t="n">
-        <v>62167</v>
+        <v>56560</v>
       </c>
       <c r="AE220" s="6" t="n">
-        <v>61333</v>
+        <v>56600</v>
       </c>
       <c r="AF220" s="6" t="n">
-        <v>61333</v>
+        <v>55360</v>
       </c>
       <c r="AG220" s="6" t="n">
-        <v>61333</v>
+        <v>54860</v>
       </c>
       <c r="AH220" s="6" t="n">
-        <v>59333</v>
+        <v>54860</v>
       </c>
       <c r="AI220" s="6" t="n">
-        <v>59333</v>
+        <v>54920</v>
       </c>
       <c r="AJ220" s="6" t="n">
-        <v>57667</v>
+        <v>55920</v>
       </c>
       <c r="AK220" s="6" t="n">
-        <v>57667</v>
+        <v>55920</v>
       </c>
       <c r="AL220" s="6" t="n">
-        <v>56000</v>
+        <v>55260</v>
       </c>
       <c r="AM220" s="6" t="n">
-        <v>56000</v>
+        <v>55260</v>
       </c>
       <c r="AN220" s="6" t="n">
-        <v>56000</v>
+        <v>55260</v>
       </c>
       <c r="AO220" s="6" t="n">
-        <v>57167</v>
+        <v>55620</v>
       </c>
       <c r="AP220" s="6" t="n">
-        <v>57167</v>
+        <v>55620</v>
       </c>
       <c r="AQ220" s="6" t="n">
-        <v>57167</v>
+        <v>55420</v>
       </c>
       <c r="AR220" s="6" t="n">
-        <v>57167</v>
+        <v>55420</v>
       </c>
       <c r="AS220" s="6" t="n">
-        <v>56333</v>
+        <v>55100</v>
       </c>
       <c r="AT220" s="6" t="n">
-        <v>55500</v>
+        <v>55100</v>
       </c>
       <c r="AU220" s="6" t="n">
-        <v>55500</v>
+        <v>55100</v>
       </c>
       <c r="AV220" s="6" t="n">
-        <v>55500</v>
+        <v>55020</v>
       </c>
       <c r="AW220" s="6" t="n">
-        <v>55500</v>
+        <v>54020</v>
       </c>
       <c r="AX220" s="6" t="n">
-        <v>55500</v>
+        <v>54020</v>
       </c>
       <c r="AY220" s="6" t="n">
-        <v>55500</v>
+        <v>54820</v>
       </c>
       <c r="AZ220" s="6" t="n">
-        <v>54125</v>
+        <v>54760</v>
       </c>
       <c r="BA220" s="6" t="n">
-        <v>54125</v>
+        <v>54760</v>
       </c>
       <c r="BB220" s="6" t="n">
-        <v>52750</v>
+        <v>54760</v>
       </c>
       <c r="BC220" s="6" t="n">
-        <v>53375</v>
+        <v>55000</v>
       </c>
       <c r="BD220" s="6" t="n">
-        <v>53375</v>
+        <v>55000</v>
       </c>
       <c r="BE220" s="6" t="n">
-        <v>53250</v>
+        <v>55000</v>
       </c>
       <c r="BF220" s="6" t="n">
-        <v>53125</v>
+        <v>55000</v>
       </c>
       <c r="BG220" s="6" t="n">
-        <v>50625</v>
+        <v>53660</v>
       </c>
       <c r="BH220" s="6" t="n">
-        <v>50000</v>
+        <v>52980</v>
       </c>
       <c r="BI220" s="6" t="n">
-        <v>50000</v>
+        <v>52980</v>
       </c>
       <c r="BJ220" s="6" t="n">
-        <v>50000</v>
+        <v>52580</v>
       </c>
       <c r="BK220" s="6" t="n">
-        <v>50000</v>
+        <v>52580</v>
       </c>
       <c r="BL220" s="6" t="n">
-        <v>50700</v>
+        <v>52380</v>
+      </c>
+      <c r="BM220" s="6" t="n">
+        <v>52380</v>
       </c>
     </row>
     <row r="221">
@@ -46229,12 +46622,12 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>체리</t>
+          <t>레몬</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>수입(5kg)</t>
+          <t>수입(17kg)</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -46244,113 +46637,186 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>5kg</t>
+          <t>17kg</t>
         </is>
       </c>
       <c r="G221" s="6" t="n">
-        <v>75080</v>
+        <v>81520</v>
       </c>
       <c r="H221" s="6" t="n">
-        <v>76760</v>
+        <v>78980</v>
       </c>
       <c r="I221" s="6" t="n">
-        <v>78100</v>
+        <v>78320</v>
       </c>
       <c r="J221" s="6" t="n">
-        <v>78100</v>
+        <v>78320</v>
       </c>
       <c r="K221" s="6" t="n">
-        <v>79360</v>
+        <v>77640</v>
       </c>
       <c r="L221" s="6" t="n">
-        <v>79360</v>
+        <v>77640</v>
       </c>
       <c r="M221" s="6" t="n">
-        <v>82680</v>
+        <v>76160</v>
       </c>
       <c r="N221" s="6" t="n">
-        <v>82680</v>
+        <v>76160</v>
       </c>
       <c r="O221" s="6" t="n">
-        <v>82020</v>
+        <v>75840</v>
       </c>
       <c r="P221" s="6" t="n">
-        <v>82020</v>
+        <v>75840</v>
       </c>
       <c r="Q221" s="6" t="n">
-        <v>84360</v>
+        <v>75720</v>
       </c>
       <c r="R221" s="6" t="n">
-        <v>86080</v>
+        <v>74700</v>
       </c>
       <c r="S221" s="6" t="n">
-        <v>87620</v>
+        <v>74700</v>
       </c>
       <c r="T221" s="6" t="n">
-        <v>88080</v>
+        <v>74360</v>
       </c>
       <c r="U221" s="6" t="n">
-        <v>86480</v>
+        <v>73680</v>
       </c>
       <c r="V221" s="6" t="n">
-        <v>84020</v>
+        <v>73160</v>
       </c>
       <c r="W221" s="6" t="n">
-        <v>87020</v>
+        <v>71760</v>
       </c>
       <c r="X221" s="6" t="n">
-        <v>87020</v>
+        <v>71760</v>
       </c>
       <c r="Y221" s="6" t="n">
-        <v>86680</v>
+        <v>71760</v>
       </c>
       <c r="Z221" s="6" t="n">
-        <v>88020</v>
+        <v>70560</v>
       </c>
       <c r="AA221" s="6" t="n">
-        <v>85025</v>
+        <v>68960</v>
       </c>
       <c r="AB221" s="6" t="n">
-        <v>85450</v>
+        <v>68960</v>
       </c>
       <c r="AC221" s="6" t="n">
-        <v>95000</v>
-      </c>
-      <c r="AD221" s="6" t="n"/>
-      <c r="AE221" s="6" t="n"/>
-      <c r="AF221" s="6" t="n"/>
-      <c r="AG221" s="6" t="n"/>
-      <c r="AH221" s="6" t="n"/>
-      <c r="AI221" s="6" t="n"/>
-      <c r="AJ221" s="6" t="n"/>
-      <c r="AK221" s="6" t="n"/>
-      <c r="AL221" s="6" t="n"/>
-      <c r="AM221" s="6" t="n"/>
-      <c r="AN221" s="6" t="n"/>
-      <c r="AO221" s="6" t="n"/>
-      <c r="AP221" s="6" t="n"/>
-      <c r="AQ221" s="6" t="n"/>
-      <c r="AR221" s="6" t="n"/>
-      <c r="AS221" s="6" t="n"/>
-      <c r="AT221" s="6" t="n"/>
-      <c r="AU221" s="6" t="n"/>
-      <c r="AV221" s="6" t="n"/>
-      <c r="AW221" s="6" t="n"/>
-      <c r="AX221" s="6" t="n"/>
-      <c r="AY221" s="6" t="n"/>
-      <c r="AZ221" s="6" t="n"/>
-      <c r="BA221" s="6" t="n"/>
-      <c r="BB221" s="6" t="n"/>
-      <c r="BC221" s="6" t="n"/>
-      <c r="BD221" s="6" t="n"/>
-      <c r="BE221" s="6" t="n"/>
-      <c r="BF221" s="6" t="n"/>
-      <c r="BG221" s="6" t="n"/>
-      <c r="BH221" s="6" t="n"/>
-      <c r="BI221" s="6" t="n"/>
-      <c r="BJ221" s="6" t="n"/>
-      <c r="BK221" s="6" t="n"/>
-      <c r="BL221" s="6" t="n"/>
+        <v>68160</v>
+      </c>
+      <c r="AD221" s="6" t="n">
+        <v>67820</v>
+      </c>
+      <c r="AE221" s="6" t="n">
+        <v>67500</v>
+      </c>
+      <c r="AF221" s="6" t="n">
+        <v>64940</v>
+      </c>
+      <c r="AG221" s="6" t="n">
+        <v>64080</v>
+      </c>
+      <c r="AH221" s="6" t="n">
+        <v>62880</v>
+      </c>
+      <c r="AI221" s="6" t="n">
+        <v>62880</v>
+      </c>
+      <c r="AJ221" s="6" t="n">
+        <v>62080</v>
+      </c>
+      <c r="AK221" s="6" t="n">
+        <v>62080</v>
+      </c>
+      <c r="AL221" s="6" t="n">
+        <v>62080</v>
+      </c>
+      <c r="AM221" s="6" t="n">
+        <v>62080</v>
+      </c>
+      <c r="AN221" s="6" t="n">
+        <v>62080</v>
+      </c>
+      <c r="AO221" s="6" t="n">
+        <v>62420</v>
+      </c>
+      <c r="AP221" s="6" t="n">
+        <v>62420</v>
+      </c>
+      <c r="AQ221" s="6" t="n">
+        <v>62080</v>
+      </c>
+      <c r="AR221" s="6" t="n">
+        <v>60880</v>
+      </c>
+      <c r="AS221" s="6" t="n">
+        <v>60880</v>
+      </c>
+      <c r="AT221" s="6" t="n">
+        <v>59960</v>
+      </c>
+      <c r="AU221" s="6" t="n">
+        <v>59960</v>
+      </c>
+      <c r="AV221" s="6" t="n">
+        <v>59960</v>
+      </c>
+      <c r="AW221" s="6" t="n">
+        <v>60300</v>
+      </c>
+      <c r="AX221" s="6" t="n">
+        <v>60300</v>
+      </c>
+      <c r="AY221" s="6" t="n">
+        <v>60300</v>
+      </c>
+      <c r="AZ221" s="6" t="n">
+        <v>60420</v>
+      </c>
+      <c r="BA221" s="6" t="n">
+        <v>60420</v>
+      </c>
+      <c r="BB221" s="6" t="n">
+        <v>58940</v>
+      </c>
+      <c r="BC221" s="6" t="n">
+        <v>58340</v>
+      </c>
+      <c r="BD221" s="6" t="n">
+        <v>58340</v>
+      </c>
+      <c r="BE221" s="6" t="n">
+        <v>57280</v>
+      </c>
+      <c r="BF221" s="6" t="n">
+        <v>57180</v>
+      </c>
+      <c r="BG221" s="6" t="n">
+        <v>55520</v>
+      </c>
+      <c r="BH221" s="6" t="n">
+        <v>55840</v>
+      </c>
+      <c r="BI221" s="6" t="n">
+        <v>55840</v>
+      </c>
+      <c r="BJ221" s="6" t="n">
+        <v>56180</v>
+      </c>
+      <c r="BK221" s="6" t="n">
+        <v>56120</v>
+      </c>
+      <c r="BL221" s="6" t="n">
+        <v>55980</v>
+      </c>
+      <c r="BM221" s="6" t="n">
+        <v>55980</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -46365,12 +46831,12 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>체리</t>
+          <t>레몬</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>수입(5kg)</t>
+          <t>수입(17kg)</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -46380,113 +46846,186 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>5kg</t>
+          <t>17kg</t>
         </is>
       </c>
       <c r="G222" s="6" t="n">
-        <v>64350</v>
+        <v>71500</v>
       </c>
       <c r="H222" s="6" t="n">
-        <v>65900</v>
+        <v>68167</v>
       </c>
       <c r="I222" s="6" t="n">
-        <v>67100</v>
+        <v>68167</v>
       </c>
       <c r="J222" s="6" t="n">
-        <v>67100</v>
+        <v>68167</v>
       </c>
       <c r="K222" s="6" t="n">
-        <v>70850</v>
+        <v>68167</v>
       </c>
       <c r="L222" s="6" t="n">
-        <v>70850</v>
+        <v>68167</v>
       </c>
       <c r="M222" s="6" t="n">
-        <v>74000</v>
+        <v>68033</v>
       </c>
       <c r="N222" s="6" t="n">
-        <v>74500</v>
+        <v>68033</v>
       </c>
       <c r="O222" s="6" t="n">
-        <v>72000</v>
+        <v>66367</v>
       </c>
       <c r="P222" s="6" t="n">
-        <v>72000</v>
+        <v>66367</v>
       </c>
       <c r="Q222" s="6" t="n">
-        <v>75000</v>
+        <v>66367</v>
       </c>
       <c r="R222" s="6" t="n">
-        <v>75000</v>
+        <v>66033</v>
       </c>
       <c r="S222" s="6" t="n">
-        <v>75000</v>
+        <v>66033</v>
       </c>
       <c r="T222" s="6" t="n">
-        <v>75000</v>
+        <v>66033</v>
       </c>
       <c r="U222" s="6" t="n">
-        <v>71100</v>
+        <v>65533</v>
       </c>
       <c r="V222" s="6" t="n">
-        <v>71100</v>
+        <v>65500</v>
       </c>
       <c r="W222" s="6" t="n">
-        <v>71100</v>
+        <v>65500</v>
       </c>
       <c r="X222" s="6" t="n">
-        <v>71100</v>
+        <v>65500</v>
       </c>
       <c r="Y222" s="6" t="n">
-        <v>69850</v>
+        <v>65500</v>
       </c>
       <c r="Z222" s="6" t="n">
-        <v>77350</v>
+        <v>63500</v>
       </c>
       <c r="AA222" s="6" t="n">
-        <v>76100</v>
+        <v>63500</v>
       </c>
       <c r="AB222" s="6" t="n">
-        <v>76100</v>
+        <v>63500</v>
       </c>
       <c r="AC222" s="6" t="n">
-        <v>90000</v>
-      </c>
-      <c r="AD222" s="6" t="n"/>
-      <c r="AE222" s="6" t="n"/>
-      <c r="AF222" s="6" t="n"/>
-      <c r="AG222" s="6" t="n"/>
-      <c r="AH222" s="6" t="n"/>
-      <c r="AI222" s="6" t="n"/>
-      <c r="AJ222" s="6" t="n"/>
-      <c r="AK222" s="6" t="n"/>
-      <c r="AL222" s="6" t="n"/>
-      <c r="AM222" s="6" t="n"/>
-      <c r="AN222" s="6" t="n"/>
-      <c r="AO222" s="6" t="n"/>
-      <c r="AP222" s="6" t="n"/>
-      <c r="AQ222" s="6" t="n"/>
-      <c r="AR222" s="6" t="n"/>
-      <c r="AS222" s="6" t="n"/>
-      <c r="AT222" s="6" t="n"/>
-      <c r="AU222" s="6" t="n"/>
-      <c r="AV222" s="6" t="n"/>
-      <c r="AW222" s="6" t="n"/>
-      <c r="AX222" s="6" t="n"/>
-      <c r="AY222" s="6" t="n"/>
-      <c r="AZ222" s="6" t="n"/>
-      <c r="BA222" s="6" t="n"/>
-      <c r="BB222" s="6" t="n"/>
-      <c r="BC222" s="6" t="n"/>
-      <c r="BD222" s="6" t="n"/>
-      <c r="BE222" s="6" t="n"/>
-      <c r="BF222" s="6" t="n"/>
-      <c r="BG222" s="6" t="n"/>
-      <c r="BH222" s="6" t="n"/>
-      <c r="BI222" s="6" t="n"/>
-      <c r="BJ222" s="6" t="n"/>
-      <c r="BK222" s="6" t="n"/>
-      <c r="BL222" s="6" t="n"/>
+        <v>62167</v>
+      </c>
+      <c r="AD222" s="6" t="n">
+        <v>62167</v>
+      </c>
+      <c r="AE222" s="6" t="n">
+        <v>61333</v>
+      </c>
+      <c r="AF222" s="6" t="n">
+        <v>61333</v>
+      </c>
+      <c r="AG222" s="6" t="n">
+        <v>61333</v>
+      </c>
+      <c r="AH222" s="6" t="n">
+        <v>59333</v>
+      </c>
+      <c r="AI222" s="6" t="n">
+        <v>59333</v>
+      </c>
+      <c r="AJ222" s="6" t="n">
+        <v>57667</v>
+      </c>
+      <c r="AK222" s="6" t="n">
+        <v>57667</v>
+      </c>
+      <c r="AL222" s="6" t="n">
+        <v>56000</v>
+      </c>
+      <c r="AM222" s="6" t="n">
+        <v>56000</v>
+      </c>
+      <c r="AN222" s="6" t="n">
+        <v>56000</v>
+      </c>
+      <c r="AO222" s="6" t="n">
+        <v>57167</v>
+      </c>
+      <c r="AP222" s="6" t="n">
+        <v>57167</v>
+      </c>
+      <c r="AQ222" s="6" t="n">
+        <v>57167</v>
+      </c>
+      <c r="AR222" s="6" t="n">
+        <v>57167</v>
+      </c>
+      <c r="AS222" s="6" t="n">
+        <v>56333</v>
+      </c>
+      <c r="AT222" s="6" t="n">
+        <v>55500</v>
+      </c>
+      <c r="AU222" s="6" t="n">
+        <v>55500</v>
+      </c>
+      <c r="AV222" s="6" t="n">
+        <v>55500</v>
+      </c>
+      <c r="AW222" s="6" t="n">
+        <v>55500</v>
+      </c>
+      <c r="AX222" s="6" t="n">
+        <v>55500</v>
+      </c>
+      <c r="AY222" s="6" t="n">
+        <v>55500</v>
+      </c>
+      <c r="AZ222" s="6" t="n">
+        <v>54125</v>
+      </c>
+      <c r="BA222" s="6" t="n">
+        <v>54125</v>
+      </c>
+      <c r="BB222" s="6" t="n">
+        <v>52750</v>
+      </c>
+      <c r="BC222" s="6" t="n">
+        <v>53375</v>
+      </c>
+      <c r="BD222" s="6" t="n">
+        <v>53375</v>
+      </c>
+      <c r="BE222" s="6" t="n">
+        <v>53250</v>
+      </c>
+      <c r="BF222" s="6" t="n">
+        <v>53125</v>
+      </c>
+      <c r="BG222" s="6" t="n">
+        <v>50625</v>
+      </c>
+      <c r="BH222" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="BI222" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="BJ222" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="BK222" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="BL222" s="6" t="n">
+        <v>50700</v>
+      </c>
+      <c r="BM222" s="6" t="n">
+        <v>50700</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -46501,7 +47040,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>망고</t>
+          <t>체리</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -46520,179 +47059,110 @@
         </is>
       </c>
       <c r="G223" s="6" t="n">
-        <v>57875</v>
+        <v>75080</v>
       </c>
       <c r="H223" s="6" t="n">
-        <v>64500</v>
+        <v>76760</v>
       </c>
       <c r="I223" s="6" t="n">
-        <v>64500</v>
+        <v>78100</v>
       </c>
       <c r="J223" s="6" t="n">
-        <v>64500</v>
+        <v>78100</v>
       </c>
       <c r="K223" s="6" t="n">
-        <v>64500</v>
+        <v>79360</v>
       </c>
       <c r="L223" s="6" t="n">
-        <v>64500</v>
+        <v>79360</v>
       </c>
       <c r="M223" s="6" t="n">
-        <v>65760</v>
+        <v>82680</v>
       </c>
       <c r="N223" s="6" t="n">
-        <v>65360</v>
+        <v>82680</v>
       </c>
       <c r="O223" s="6" t="n">
-        <v>65360</v>
+        <v>82020</v>
       </c>
       <c r="P223" s="6" t="n">
-        <v>65360</v>
+        <v>82020</v>
       </c>
       <c r="Q223" s="6" t="n">
-        <v>70050</v>
+        <v>84360</v>
       </c>
       <c r="R223" s="6" t="n">
-        <v>70750</v>
+        <v>86080</v>
       </c>
       <c r="S223" s="6" t="n">
-        <v>70750</v>
+        <v>87620</v>
       </c>
       <c r="T223" s="6" t="n">
-        <v>71575</v>
+        <v>88080</v>
       </c>
       <c r="U223" s="6" t="n">
-        <v>71750</v>
+        <v>86480</v>
       </c>
       <c r="V223" s="6" t="n">
-        <v>71400</v>
+        <v>84020</v>
       </c>
       <c r="W223" s="6" t="n">
-        <v>69775</v>
+        <v>87020</v>
       </c>
       <c r="X223" s="6" t="n">
-        <v>69775</v>
+        <v>87020</v>
       </c>
       <c r="Y223" s="6" t="n">
-        <v>69775</v>
+        <v>86680</v>
       </c>
       <c r="Z223" s="6" t="n">
-        <v>69525</v>
+        <v>88020</v>
       </c>
       <c r="AA223" s="6" t="n">
-        <v>70150</v>
+        <v>85025</v>
       </c>
       <c r="AB223" s="6" t="n">
-        <v>70150</v>
+        <v>85450</v>
       </c>
       <c r="AC223" s="6" t="n">
-        <v>70150</v>
-      </c>
-      <c r="AD223" s="6" t="n">
-        <v>70150</v>
-      </c>
-      <c r="AE223" s="6" t="n">
-        <v>70150</v>
-      </c>
-      <c r="AF223" s="6" t="n">
-        <v>70150</v>
-      </c>
-      <c r="AG223" s="6" t="n">
-        <v>70150</v>
-      </c>
-      <c r="AH223" s="6" t="n">
-        <v>70150</v>
-      </c>
-      <c r="AI223" s="6" t="n">
-        <v>70150</v>
-      </c>
-      <c r="AJ223" s="6" t="n">
-        <v>71400</v>
-      </c>
-      <c r="AK223" s="6" t="n">
-        <v>71400</v>
-      </c>
-      <c r="AL223" s="6" t="n">
-        <v>71400</v>
-      </c>
-      <c r="AM223" s="6" t="n">
-        <v>72650</v>
-      </c>
-      <c r="AN223" s="6" t="n">
-        <v>72650</v>
-      </c>
-      <c r="AO223" s="6" t="n">
-        <v>73900</v>
-      </c>
-      <c r="AP223" s="6" t="n">
-        <v>77125</v>
-      </c>
-      <c r="AQ223" s="6" t="n">
-        <v>77125</v>
-      </c>
-      <c r="AR223" s="6" t="n">
-        <v>77125</v>
-      </c>
-      <c r="AS223" s="6" t="n">
-        <v>77125</v>
-      </c>
-      <c r="AT223" s="6" t="n">
-        <v>77875</v>
-      </c>
-      <c r="AU223" s="6" t="n">
-        <v>77875</v>
-      </c>
-      <c r="AV223" s="6" t="n">
-        <v>78250</v>
-      </c>
-      <c r="AW223" s="6" t="n">
-        <v>79250</v>
-      </c>
-      <c r="AX223" s="6" t="n">
-        <v>79250</v>
-      </c>
-      <c r="AY223" s="6" t="n">
-        <v>79750</v>
-      </c>
-      <c r="AZ223" s="6" t="n">
-        <v>81125</v>
-      </c>
-      <c r="BA223" s="6" t="n">
-        <v>81275</v>
-      </c>
-      <c r="BB223" s="6" t="n">
-        <v>81275</v>
-      </c>
-      <c r="BC223" s="6" t="n">
-        <v>79275</v>
-      </c>
-      <c r="BD223" s="6" t="n">
-        <v>79275</v>
-      </c>
-      <c r="BE223" s="6" t="n">
-        <v>78025</v>
-      </c>
-      <c r="BF223" s="6" t="n">
-        <v>78025</v>
-      </c>
-      <c r="BG223" s="6" t="n">
-        <v>73500</v>
-      </c>
-      <c r="BH223" s="6" t="n">
-        <v>72375</v>
-      </c>
-      <c r="BI223" s="6" t="n">
-        <v>72375</v>
-      </c>
-      <c r="BJ223" s="6" t="n">
-        <v>69625</v>
-      </c>
-      <c r="BK223" s="6" t="n">
-        <v>68375</v>
-      </c>
-      <c r="BL223" s="6" t="n">
-        <v>68375</v>
-      </c>
+        <v>95000</v>
+      </c>
+      <c r="AD223" s="6" t="n"/>
+      <c r="AE223" s="6" t="n"/>
+      <c r="AF223" s="6" t="n"/>
+      <c r="AG223" s="6" t="n"/>
+      <c r="AH223" s="6" t="n"/>
+      <c r="AI223" s="6" t="n"/>
+      <c r="AJ223" s="6" t="n"/>
+      <c r="AK223" s="6" t="n"/>
+      <c r="AL223" s="6" t="n"/>
+      <c r="AM223" s="6" t="n"/>
+      <c r="AN223" s="6" t="n"/>
+      <c r="AO223" s="6" t="n"/>
+      <c r="AP223" s="6" t="n"/>
+      <c r="AQ223" s="6" t="n"/>
+      <c r="AR223" s="6" t="n"/>
+      <c r="AS223" s="6" t="n"/>
+      <c r="AT223" s="6" t="n"/>
+      <c r="AU223" s="6" t="n"/>
+      <c r="AV223" s="6" t="n"/>
+      <c r="AW223" s="6" t="n"/>
+      <c r="AX223" s="6" t="n"/>
+      <c r="AY223" s="6" t="n"/>
+      <c r="AZ223" s="6" t="n"/>
+      <c r="BA223" s="6" t="n"/>
+      <c r="BB223" s="6" t="n"/>
+      <c r="BC223" s="6" t="n"/>
+      <c r="BD223" s="6" t="n"/>
+      <c r="BE223" s="6" t="n"/>
+      <c r="BF223" s="6" t="n"/>
+      <c r="BG223" s="6" t="n"/>
+      <c r="BH223" s="6" t="n"/>
+      <c r="BI223" s="6" t="n"/>
+      <c r="BJ223" s="6" t="n"/>
+      <c r="BK223" s="6" t="n"/>
+      <c r="BL223" s="6" t="n"/>
+      <c r="BM223" s="6" t="n"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -46707,7 +47177,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>망고</t>
+          <t>체리</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -46726,107 +47196,85 @@
         </is>
       </c>
       <c r="G224" s="6" t="n">
-        <v>45350</v>
+        <v>64350</v>
       </c>
       <c r="H224" s="6" t="n">
-        <v>52000</v>
+        <v>65900</v>
       </c>
       <c r="I224" s="6" t="n">
-        <v>52000</v>
+        <v>67100</v>
       </c>
       <c r="J224" s="6" t="n">
-        <v>52000</v>
+        <v>67100</v>
       </c>
       <c r="K224" s="6" t="n">
-        <v>52000</v>
+        <v>70850</v>
       </c>
       <c r="L224" s="6" t="n">
-        <v>52000</v>
+        <v>70850</v>
       </c>
       <c r="M224" s="6" t="n">
-        <v>53433</v>
+        <v>74000</v>
       </c>
       <c r="N224" s="6" t="n">
-        <v>52867</v>
+        <v>74500</v>
       </c>
       <c r="O224" s="6" t="n">
-        <v>52867</v>
+        <v>72000</v>
       </c>
       <c r="P224" s="6" t="n">
-        <v>52867</v>
+        <v>72000</v>
       </c>
       <c r="Q224" s="6" t="n">
-        <v>52000</v>
+        <v>75000</v>
       </c>
       <c r="R224" s="6" t="n">
-        <v>45500</v>
+        <v>75000</v>
       </c>
       <c r="S224" s="6" t="n">
-        <v>45500</v>
+        <v>75000</v>
       </c>
       <c r="T224" s="6" t="n">
-        <v>45500</v>
+        <v>75000</v>
       </c>
       <c r="U224" s="6" t="n">
-        <v>45500</v>
+        <v>71100</v>
       </c>
       <c r="V224" s="6" t="n">
-        <v>45500</v>
+        <v>71100</v>
       </c>
       <c r="W224" s="6" t="n">
-        <v>45500</v>
+        <v>71100</v>
       </c>
       <c r="X224" s="6" t="n">
-        <v>45500</v>
+        <v>71100</v>
       </c>
       <c r="Y224" s="6" t="n">
-        <v>49650</v>
+        <v>69850</v>
       </c>
       <c r="Z224" s="6" t="n">
-        <v>49650</v>
+        <v>77350</v>
       </c>
       <c r="AA224" s="6" t="n">
-        <v>46300</v>
+        <v>76100</v>
       </c>
       <c r="AB224" s="6" t="n">
-        <v>50500</v>
+        <v>76100</v>
       </c>
       <c r="AC224" s="6" t="n">
-        <v>50500</v>
-      </c>
-      <c r="AD224" s="6" t="n">
-        <v>46000</v>
-      </c>
-      <c r="AE224" s="6" t="n">
-        <v>46000</v>
-      </c>
-      <c r="AF224" s="6" t="n">
-        <v>46000</v>
-      </c>
-      <c r="AG224" s="6" t="n">
-        <v>46000</v>
-      </c>
-      <c r="AH224" s="6" t="n">
-        <v>46000</v>
-      </c>
-      <c r="AI224" s="6" t="n">
-        <v>46000</v>
-      </c>
-      <c r="AJ224" s="6" t="n">
-        <v>46000</v>
-      </c>
-      <c r="AK224" s="6" t="n">
-        <v>46000</v>
-      </c>
-      <c r="AL224" s="6" t="n">
-        <v>46000</v>
-      </c>
-      <c r="AM224" s="6" t="n">
-        <v>46000</v>
-      </c>
-      <c r="AN224" s="6" t="n">
-        <v>46000</v>
-      </c>
+        <v>90000</v>
+      </c>
+      <c r="AD224" s="6" t="n"/>
+      <c r="AE224" s="6" t="n"/>
+      <c r="AF224" s="6" t="n"/>
+      <c r="AG224" s="6" t="n"/>
+      <c r="AH224" s="6" t="n"/>
+      <c r="AI224" s="6" t="n"/>
+      <c r="AJ224" s="6" t="n"/>
+      <c r="AK224" s="6" t="n"/>
+      <c r="AL224" s="6" t="n"/>
+      <c r="AM224" s="6" t="n"/>
+      <c r="AN224" s="6" t="n"/>
       <c r="AO224" s="6" t="n"/>
       <c r="AP224" s="6" t="n"/>
       <c r="AQ224" s="6" t="n"/>
@@ -46851,6 +47299,7 @@
       <c r="BJ224" s="6" t="n"/>
       <c r="BK224" s="6" t="n"/>
       <c r="BL224" s="6" t="n"/>
+      <c r="BM224" s="6" t="n"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -46865,12 +47314,12 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>키위</t>
+          <t>망고</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>골드(5.7kg)</t>
+          <t>수입(5kg)</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -46880,122 +47329,185 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>5.7kg</t>
-        </is>
-      </c>
-      <c r="G225" s="6" t="n"/>
-      <c r="H225" s="6" t="n"/>
-      <c r="I225" s="6" t="n"/>
-      <c r="J225" s="6" t="n"/>
-      <c r="K225" s="6" t="n"/>
-      <c r="L225" s="6" t="n"/>
-      <c r="M225" s="6" t="n"/>
-      <c r="N225" s="6" t="n"/>
-      <c r="O225" s="6" t="n"/>
-      <c r="P225" s="6" t="n"/>
-      <c r="Q225" s="6" t="n"/>
-      <c r="R225" s="6" t="n"/>
-      <c r="S225" s="6" t="n"/>
-      <c r="T225" s="6" t="n"/>
-      <c r="U225" s="6" t="n"/>
-      <c r="V225" s="6" t="n"/>
-      <c r="W225" s="6" t="n"/>
-      <c r="X225" s="6" t="n"/>
-      <c r="Y225" s="6" t="n"/>
-      <c r="Z225" s="6" t="n"/>
-      <c r="AA225" s="6" t="n"/>
-      <c r="AB225" s="6" t="n"/>
-      <c r="AC225" s="6" t="n"/>
-      <c r="AD225" s="6" t="n"/>
-      <c r="AE225" s="6" t="n"/>
-      <c r="AF225" s="6" t="n"/>
-      <c r="AG225" s="6" t="n"/>
-      <c r="AH225" s="6" t="n"/>
-      <c r="AI225" s="6" t="n"/>
-      <c r="AJ225" s="6" t="n"/>
+          <t>5kg</t>
+        </is>
+      </c>
+      <c r="G225" s="6" t="n">
+        <v>57875</v>
+      </c>
+      <c r="H225" s="6" t="n">
+        <v>64500</v>
+      </c>
+      <c r="I225" s="6" t="n">
+        <v>64500</v>
+      </c>
+      <c r="J225" s="6" t="n">
+        <v>64500</v>
+      </c>
+      <c r="K225" s="6" t="n">
+        <v>64500</v>
+      </c>
+      <c r="L225" s="6" t="n">
+        <v>64500</v>
+      </c>
+      <c r="M225" s="6" t="n">
+        <v>65760</v>
+      </c>
+      <c r="N225" s="6" t="n">
+        <v>65360</v>
+      </c>
+      <c r="O225" s="6" t="n">
+        <v>65360</v>
+      </c>
+      <c r="P225" s="6" t="n">
+        <v>65360</v>
+      </c>
+      <c r="Q225" s="6" t="n">
+        <v>70050</v>
+      </c>
+      <c r="R225" s="6" t="n">
+        <v>70750</v>
+      </c>
+      <c r="S225" s="6" t="n">
+        <v>70750</v>
+      </c>
+      <c r="T225" s="6" t="n">
+        <v>71575</v>
+      </c>
+      <c r="U225" s="6" t="n">
+        <v>71750</v>
+      </c>
+      <c r="V225" s="6" t="n">
+        <v>71400</v>
+      </c>
+      <c r="W225" s="6" t="n">
+        <v>69775</v>
+      </c>
+      <c r="X225" s="6" t="n">
+        <v>69775</v>
+      </c>
+      <c r="Y225" s="6" t="n">
+        <v>69775</v>
+      </c>
+      <c r="Z225" s="6" t="n">
+        <v>69525</v>
+      </c>
+      <c r="AA225" s="6" t="n">
+        <v>70150</v>
+      </c>
+      <c r="AB225" s="6" t="n">
+        <v>70150</v>
+      </c>
+      <c r="AC225" s="6" t="n">
+        <v>70150</v>
+      </c>
+      <c r="AD225" s="6" t="n">
+        <v>70150</v>
+      </c>
+      <c r="AE225" s="6" t="n">
+        <v>70150</v>
+      </c>
+      <c r="AF225" s="6" t="n">
+        <v>70150</v>
+      </c>
+      <c r="AG225" s="6" t="n">
+        <v>70150</v>
+      </c>
+      <c r="AH225" s="6" t="n">
+        <v>70150</v>
+      </c>
+      <c r="AI225" s="6" t="n">
+        <v>70150</v>
+      </c>
+      <c r="AJ225" s="6" t="n">
+        <v>71400</v>
+      </c>
       <c r="AK225" s="6" t="n">
-        <v>41360</v>
+        <v>71400</v>
       </c>
       <c r="AL225" s="6" t="n">
-        <v>41360</v>
+        <v>71400</v>
       </c>
       <c r="AM225" s="6" t="n">
-        <v>41360</v>
+        <v>72650</v>
       </c>
       <c r="AN225" s="6" t="n">
-        <v>41360</v>
+        <v>72650</v>
       </c>
       <c r="AO225" s="6" t="n">
-        <v>41220</v>
+        <v>73900</v>
       </c>
       <c r="AP225" s="6" t="n">
-        <v>40520</v>
+        <v>77125</v>
       </c>
       <c r="AQ225" s="6" t="n">
-        <v>40420</v>
+        <v>77125</v>
       </c>
       <c r="AR225" s="6" t="n">
-        <v>40580</v>
+        <v>77125</v>
       </c>
       <c r="AS225" s="6" t="n">
-        <v>40440</v>
+        <v>77125</v>
       </c>
       <c r="AT225" s="6" t="n">
-        <v>40040</v>
+        <v>77875</v>
       </c>
       <c r="AU225" s="6" t="n">
-        <v>40380</v>
+        <v>77875</v>
       </c>
       <c r="AV225" s="6" t="n">
-        <v>40820</v>
+        <v>78250</v>
       </c>
       <c r="AW225" s="6" t="n">
-        <v>40220</v>
+        <v>79250</v>
       </c>
       <c r="AX225" s="6" t="n">
-        <v>40220</v>
+        <v>79250</v>
       </c>
       <c r="AY225" s="6" t="n">
-        <v>40820</v>
+        <v>79750</v>
       </c>
       <c r="AZ225" s="6" t="n">
-        <v>40620</v>
+        <v>81125</v>
       </c>
       <c r="BA225" s="6" t="n">
-        <v>40620</v>
+        <v>81275</v>
       </c>
       <c r="BB225" s="6" t="n">
-        <v>40620</v>
+        <v>81275</v>
       </c>
       <c r="BC225" s="6" t="n">
-        <v>40220</v>
+        <v>79275</v>
       </c>
       <c r="BD225" s="6" t="n">
-        <v>40220</v>
+        <v>79275</v>
       </c>
       <c r="BE225" s="6" t="n">
-        <v>40220</v>
+        <v>78025</v>
       </c>
       <c r="BF225" s="6" t="n">
-        <v>40220</v>
+        <v>78025</v>
       </c>
       <c r="BG225" s="6" t="n">
-        <v>39920</v>
+        <v>73500</v>
       </c>
       <c r="BH225" s="6" t="n">
-        <v>40260</v>
+        <v>72375</v>
       </c>
       <c r="BI225" s="6" t="n">
-        <v>40260</v>
+        <v>72375</v>
       </c>
       <c r="BJ225" s="6" t="n">
-        <v>41720</v>
+        <v>69625</v>
       </c>
       <c r="BK225" s="6" t="n">
-        <v>41860</v>
+        <v>68375</v>
       </c>
       <c r="BL225" s="6" t="n">
-        <v>41860</v>
+        <v>68375</v>
+      </c>
+      <c r="BM225" s="6" t="n">
+        <v>68375</v>
       </c>
     </row>
     <row r="226">
@@ -47011,136 +47523,447 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
+          <t>망고</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>수입(5kg)</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>중품</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>5kg</t>
+        </is>
+      </c>
+      <c r="G226" s="6" t="n">
+        <v>45350</v>
+      </c>
+      <c r="H226" s="6" t="n">
+        <v>52000</v>
+      </c>
+      <c r="I226" s="6" t="n">
+        <v>52000</v>
+      </c>
+      <c r="J226" s="6" t="n">
+        <v>52000</v>
+      </c>
+      <c r="K226" s="6" t="n">
+        <v>52000</v>
+      </c>
+      <c r="L226" s="6" t="n">
+        <v>52000</v>
+      </c>
+      <c r="M226" s="6" t="n">
+        <v>53433</v>
+      </c>
+      <c r="N226" s="6" t="n">
+        <v>52867</v>
+      </c>
+      <c r="O226" s="6" t="n">
+        <v>52867</v>
+      </c>
+      <c r="P226" s="6" t="n">
+        <v>52867</v>
+      </c>
+      <c r="Q226" s="6" t="n">
+        <v>52000</v>
+      </c>
+      <c r="R226" s="6" t="n">
+        <v>45500</v>
+      </c>
+      <c r="S226" s="6" t="n">
+        <v>45500</v>
+      </c>
+      <c r="T226" s="6" t="n">
+        <v>45500</v>
+      </c>
+      <c r="U226" s="6" t="n">
+        <v>45500</v>
+      </c>
+      <c r="V226" s="6" t="n">
+        <v>45500</v>
+      </c>
+      <c r="W226" s="6" t="n">
+        <v>45500</v>
+      </c>
+      <c r="X226" s="6" t="n">
+        <v>45500</v>
+      </c>
+      <c r="Y226" s="6" t="n">
+        <v>49650</v>
+      </c>
+      <c r="Z226" s="6" t="n">
+        <v>49650</v>
+      </c>
+      <c r="AA226" s="6" t="n">
+        <v>46300</v>
+      </c>
+      <c r="AB226" s="6" t="n">
+        <v>50500</v>
+      </c>
+      <c r="AC226" s="6" t="n">
+        <v>50500</v>
+      </c>
+      <c r="AD226" s="6" t="n">
+        <v>46000</v>
+      </c>
+      <c r="AE226" s="6" t="n">
+        <v>46000</v>
+      </c>
+      <c r="AF226" s="6" t="n">
+        <v>46000</v>
+      </c>
+      <c r="AG226" s="6" t="n">
+        <v>46000</v>
+      </c>
+      <c r="AH226" s="6" t="n">
+        <v>46000</v>
+      </c>
+      <c r="AI226" s="6" t="n">
+        <v>46000</v>
+      </c>
+      <c r="AJ226" s="6" t="n">
+        <v>46000</v>
+      </c>
+      <c r="AK226" s="6" t="n">
+        <v>46000</v>
+      </c>
+      <c r="AL226" s="6" t="n">
+        <v>46000</v>
+      </c>
+      <c r="AM226" s="6" t="n">
+        <v>46000</v>
+      </c>
+      <c r="AN226" s="6" t="n">
+        <v>46000</v>
+      </c>
+      <c r="AO226" s="6" t="n"/>
+      <c r="AP226" s="6" t="n"/>
+      <c r="AQ226" s="6" t="n"/>
+      <c r="AR226" s="6" t="n"/>
+      <c r="AS226" s="6" t="n"/>
+      <c r="AT226" s="6" t="n"/>
+      <c r="AU226" s="6" t="n"/>
+      <c r="AV226" s="6" t="n"/>
+      <c r="AW226" s="6" t="n"/>
+      <c r="AX226" s="6" t="n"/>
+      <c r="AY226" s="6" t="n"/>
+      <c r="AZ226" s="6" t="n"/>
+      <c r="BA226" s="6" t="n"/>
+      <c r="BB226" s="6" t="n"/>
+      <c r="BC226" s="6" t="n"/>
+      <c r="BD226" s="6" t="n"/>
+      <c r="BE226" s="6" t="n"/>
+      <c r="BF226" s="6" t="n"/>
+      <c r="BG226" s="6" t="n"/>
+      <c r="BH226" s="6" t="n"/>
+      <c r="BI226" s="6" t="n"/>
+      <c r="BJ226" s="6" t="n"/>
+      <c r="BK226" s="6" t="n"/>
+      <c r="BL226" s="6" t="n"/>
+      <c r="BM226" s="6" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>도매</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>과일류</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
           <t>키위</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr">
+      <c r="D227" t="inlineStr">
         <is>
           <t>골드(5.7kg)</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr">
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>5.7kg</t>
+        </is>
+      </c>
+      <c r="G227" s="6" t="n"/>
+      <c r="H227" s="6" t="n"/>
+      <c r="I227" s="6" t="n"/>
+      <c r="J227" s="6" t="n"/>
+      <c r="K227" s="6" t="n"/>
+      <c r="L227" s="6" t="n"/>
+      <c r="M227" s="6" t="n"/>
+      <c r="N227" s="6" t="n"/>
+      <c r="O227" s="6" t="n"/>
+      <c r="P227" s="6" t="n"/>
+      <c r="Q227" s="6" t="n"/>
+      <c r="R227" s="6" t="n"/>
+      <c r="S227" s="6" t="n"/>
+      <c r="T227" s="6" t="n"/>
+      <c r="U227" s="6" t="n"/>
+      <c r="V227" s="6" t="n"/>
+      <c r="W227" s="6" t="n"/>
+      <c r="X227" s="6" t="n"/>
+      <c r="Y227" s="6" t="n"/>
+      <c r="Z227" s="6" t="n"/>
+      <c r="AA227" s="6" t="n"/>
+      <c r="AB227" s="6" t="n"/>
+      <c r="AC227" s="6" t="n"/>
+      <c r="AD227" s="6" t="n"/>
+      <c r="AE227" s="6" t="n"/>
+      <c r="AF227" s="6" t="n"/>
+      <c r="AG227" s="6" t="n"/>
+      <c r="AH227" s="6" t="n"/>
+      <c r="AI227" s="6" t="n"/>
+      <c r="AJ227" s="6" t="n"/>
+      <c r="AK227" s="6" t="n">
+        <v>41360</v>
+      </c>
+      <c r="AL227" s="6" t="n">
+        <v>41360</v>
+      </c>
+      <c r="AM227" s="6" t="n">
+        <v>41360</v>
+      </c>
+      <c r="AN227" s="6" t="n">
+        <v>41360</v>
+      </c>
+      <c r="AO227" s="6" t="n">
+        <v>41220</v>
+      </c>
+      <c r="AP227" s="6" t="n">
+        <v>40520</v>
+      </c>
+      <c r="AQ227" s="6" t="n">
+        <v>40420</v>
+      </c>
+      <c r="AR227" s="6" t="n">
+        <v>40580</v>
+      </c>
+      <c r="AS227" s="6" t="n">
+        <v>40440</v>
+      </c>
+      <c r="AT227" s="6" t="n">
+        <v>40040</v>
+      </c>
+      <c r="AU227" s="6" t="n">
+        <v>40380</v>
+      </c>
+      <c r="AV227" s="6" t="n">
+        <v>40820</v>
+      </c>
+      <c r="AW227" s="6" t="n">
+        <v>40220</v>
+      </c>
+      <c r="AX227" s="6" t="n">
+        <v>40220</v>
+      </c>
+      <c r="AY227" s="6" t="n">
+        <v>40820</v>
+      </c>
+      <c r="AZ227" s="6" t="n">
+        <v>40620</v>
+      </c>
+      <c r="BA227" s="6" t="n">
+        <v>40620</v>
+      </c>
+      <c r="BB227" s="6" t="n">
+        <v>40620</v>
+      </c>
+      <c r="BC227" s="6" t="n">
+        <v>40220</v>
+      </c>
+      <c r="BD227" s="6" t="n">
+        <v>40220</v>
+      </c>
+      <c r="BE227" s="6" t="n">
+        <v>40220</v>
+      </c>
+      <c r="BF227" s="6" t="n">
+        <v>40220</v>
+      </c>
+      <c r="BG227" s="6" t="n">
+        <v>39920</v>
+      </c>
+      <c r="BH227" s="6" t="n">
+        <v>40260</v>
+      </c>
+      <c r="BI227" s="6" t="n">
+        <v>40260</v>
+      </c>
+      <c r="BJ227" s="6" t="n">
+        <v>41720</v>
+      </c>
+      <c r="BK227" s="6" t="n">
+        <v>41860</v>
+      </c>
+      <c r="BL227" s="6" t="n">
+        <v>41860</v>
+      </c>
+      <c r="BM227" s="6" t="n">
+        <v>41860</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>도매</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>과일류</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>키위</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>골드(5.7kg)</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
         <is>
           <t>중품</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr">
+      <c r="F228" t="inlineStr">
         <is>
           <t>5.7kg</t>
         </is>
       </c>
-      <c r="G226" s="6" t="n"/>
-      <c r="H226" s="6" t="n"/>
-      <c r="I226" s="6" t="n"/>
-      <c r="J226" s="6" t="n"/>
-      <c r="K226" s="6" t="n"/>
-      <c r="L226" s="6" t="n"/>
-      <c r="M226" s="6" t="n"/>
-      <c r="N226" s="6" t="n"/>
-      <c r="O226" s="6" t="n"/>
-      <c r="P226" s="6" t="n"/>
-      <c r="Q226" s="6" t="n"/>
-      <c r="R226" s="6" t="n"/>
-      <c r="S226" s="6" t="n"/>
-      <c r="T226" s="6" t="n"/>
-      <c r="U226" s="6" t="n"/>
-      <c r="V226" s="6" t="n"/>
-      <c r="W226" s="6" t="n"/>
-      <c r="X226" s="6" t="n"/>
-      <c r="Y226" s="6" t="n"/>
-      <c r="Z226" s="6" t="n"/>
-      <c r="AA226" s="6" t="n"/>
-      <c r="AB226" s="6" t="n"/>
-      <c r="AC226" s="6" t="n"/>
-      <c r="AD226" s="6" t="n"/>
-      <c r="AE226" s="6" t="n"/>
-      <c r="AF226" s="6" t="n"/>
-      <c r="AG226" s="6" t="n"/>
-      <c r="AH226" s="6" t="n"/>
-      <c r="AI226" s="6" t="n"/>
-      <c r="AJ226" s="6" t="n"/>
-      <c r="AK226" s="6" t="n">
+      <c r="G228" s="6" t="n"/>
+      <c r="H228" s="6" t="n"/>
+      <c r="I228" s="6" t="n"/>
+      <c r="J228" s="6" t="n"/>
+      <c r="K228" s="6" t="n"/>
+      <c r="L228" s="6" t="n"/>
+      <c r="M228" s="6" t="n"/>
+      <c r="N228" s="6" t="n"/>
+      <c r="O228" s="6" t="n"/>
+      <c r="P228" s="6" t="n"/>
+      <c r="Q228" s="6" t="n"/>
+      <c r="R228" s="6" t="n"/>
+      <c r="S228" s="6" t="n"/>
+      <c r="T228" s="6" t="n"/>
+      <c r="U228" s="6" t="n"/>
+      <c r="V228" s="6" t="n"/>
+      <c r="W228" s="6" t="n"/>
+      <c r="X228" s="6" t="n"/>
+      <c r="Y228" s="6" t="n"/>
+      <c r="Z228" s="6" t="n"/>
+      <c r="AA228" s="6" t="n"/>
+      <c r="AB228" s="6" t="n"/>
+      <c r="AC228" s="6" t="n"/>
+      <c r="AD228" s="6" t="n"/>
+      <c r="AE228" s="6" t="n"/>
+      <c r="AF228" s="6" t="n"/>
+      <c r="AG228" s="6" t="n"/>
+      <c r="AH228" s="6" t="n"/>
+      <c r="AI228" s="6" t="n"/>
+      <c r="AJ228" s="6" t="n"/>
+      <c r="AK228" s="6" t="n">
         <v>36533</v>
       </c>
-      <c r="AL226" s="6" t="n">
+      <c r="AL228" s="6" t="n">
         <v>36667</v>
       </c>
-      <c r="AM226" s="6" t="n">
+      <c r="AM228" s="6" t="n">
         <v>36667</v>
       </c>
-      <c r="AN226" s="6" t="n">
+      <c r="AN228" s="6" t="n">
         <v>36667</v>
       </c>
-      <c r="AO226" s="6" t="n">
+      <c r="AO228" s="6" t="n">
         <v>36667</v>
       </c>
-      <c r="AP226" s="6" t="n">
+      <c r="AP228" s="6" t="n">
         <v>36667</v>
       </c>
-      <c r="AQ226" s="6" t="n">
+      <c r="AQ228" s="6" t="n">
         <v>36667</v>
       </c>
-      <c r="AR226" s="6" t="n">
+      <c r="AR228" s="6" t="n">
         <v>37500</v>
       </c>
-      <c r="AS226" s="6" t="n">
+      <c r="AS228" s="6" t="n">
         <v>37500</v>
       </c>
-      <c r="AT226" s="6" t="n">
+      <c r="AT228" s="6" t="n">
         <v>37500</v>
       </c>
-      <c r="AU226" s="6" t="n">
+      <c r="AU228" s="6" t="n">
         <v>37500</v>
       </c>
-      <c r="AV226" s="6" t="n">
+      <c r="AV228" s="6" t="n">
         <v>38500</v>
       </c>
-      <c r="AW226" s="6" t="n">
+      <c r="AW228" s="6" t="n">
         <v>38333</v>
       </c>
-      <c r="AX226" s="6" t="n">
+      <c r="AX228" s="6" t="n">
         <v>38333</v>
       </c>
-      <c r="AY226" s="6" t="n">
+      <c r="AY228" s="6" t="n">
         <v>38333</v>
       </c>
-      <c r="AZ226" s="6" t="n">
+      <c r="AZ228" s="6" t="n">
         <v>38167</v>
       </c>
-      <c r="BA226" s="6" t="n">
+      <c r="BA228" s="6" t="n">
         <v>38167</v>
       </c>
-      <c r="BB226" s="6" t="n">
+      <c r="BB228" s="6" t="n">
         <v>38167</v>
       </c>
-      <c r="BC226" s="6" t="n">
+      <c r="BC228" s="6" t="n">
         <v>37750</v>
       </c>
-      <c r="BD226" s="6" t="n">
+      <c r="BD228" s="6" t="n">
         <v>37750</v>
       </c>
-      <c r="BE226" s="6" t="n">
+      <c r="BE228" s="6" t="n">
         <v>37750</v>
       </c>
-      <c r="BF226" s="6" t="n">
+      <c r="BF228" s="6" t="n">
         <v>37750</v>
       </c>
-      <c r="BG226" s="6" t="n">
+      <c r="BG228" s="6" t="n">
         <v>38250</v>
       </c>
-      <c r="BH226" s="6" t="n">
+      <c r="BH228" s="6" t="n">
         <v>38900</v>
       </c>
-      <c r="BI226" s="6" t="n">
+      <c r="BI228" s="6" t="n">
         <v>38900</v>
       </c>
-      <c r="BJ226" s="6" t="n">
+      <c r="BJ228" s="6" t="n">
         <v>38900</v>
       </c>
-      <c r="BK226" s="6" t="n">
+      <c r="BK228" s="6" t="n">
         <v>38900</v>
       </c>
-      <c r="BL226" s="6" t="n">
+      <c r="BL228" s="6" t="n">
+        <v>38900</v>
+      </c>
+      <c r="BM228" s="6" t="n">
         <v>38900</v>
       </c>
     </row>
